--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="M84" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M86" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="M88" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="M96" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="M103" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="M105" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="M106" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="M107" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="M112" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="M113" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="M114" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M115" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="M117" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="M119" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M120" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="M121" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="M122" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="M123" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="M124" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="M125" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="M126" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="M127" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="M128" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="M129" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="M130" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="M131" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="M132" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="M133" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="M134" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M135" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="M136" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="M137" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="M138" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="M139" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="M140" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="M141" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M142" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="M143" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="M144" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="M145" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="M146" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="M147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="M148" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10717,7 +10717,7 @@
       </c>
       <c r="M149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="M150" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="M151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="M152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="M153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="M154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="M156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="M157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="M158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="M160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="M161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="M162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="M163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="M164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="M165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="M166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="M167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="M168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="M169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="M171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="M172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="M173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="M174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="M175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="M176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="M177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
       </c>
       <c r="M178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="M179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="M181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="M182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12995,7 +12995,7 @@
       </c>
       <c r="M183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="M184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="M185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="M186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="M187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="M188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="M189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="M190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
       </c>
       <c r="M191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="M192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="M193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="M194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="M196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="M197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="M198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="M199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="M200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="M201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="M202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="M203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="M204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="M205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="M206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="M207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="M208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="M209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="M210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="M211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="M212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="M213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="M214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="M215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="M216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15273,7 +15273,7 @@
       </c>
       <c r="M217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="M218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15407,7 @@
       </c>
       <c r="M219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="M220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="M221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="M222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="M223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="M224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="M225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="M226" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="M227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="M228" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="M229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="M230" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16211,7 +16211,7 @@
       </c>
       <c r="M231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="M232" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16345,7 +16345,7 @@
       </c>
       <c r="M233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16412,7 +16412,7 @@
       </c>
       <c r="M234" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="M235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="M236" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="M237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="M238" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="M239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M240" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="M241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="M242" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="M243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="M244" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="M246" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="M247" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="M248" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="M249" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="M250" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="M251" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="M252" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="M253" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="M254" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17819,7 +17819,7 @@
       </c>
       <c r="M255" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="M256" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="M257" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="M258" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18087,7 +18087,7 @@
       </c>
       <c r="M259" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18154,7 @@
       </c>
       <c r="M260" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="M261" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="M262" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="M263" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="M264" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18489,7 @@
       </c>
       <c r="M265" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="M266" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="M267" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="M268" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="M269" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M270" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="M271" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -18958,7 +18958,7 @@
       </c>
       <c r="M272" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="M273" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19092,7 +19092,7 @@
       </c>
       <c r="M274" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="M275" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="M276" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19293,7 +19293,7 @@
       </c>
       <c r="M277" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="M278" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="M279" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="M280" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="M281" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="M282" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="M283" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19762,7 +19762,7 @@
       </c>
       <c r="M284" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="M285" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19896,7 +19896,7 @@
       </c>
       <c r="M286" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="M287" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="M288" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="M289" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="M290" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="M291" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="M292" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="M293" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20432,7 +20432,7 @@
       </c>
       <c r="M294" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="M295" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="M296" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20633,7 @@
       </c>
       <c r="M297" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="M298" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20767,7 +20767,7 @@
       </c>
       <c r="M299" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="M300" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="M301" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="M302" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="M303" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="M304" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="M305" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="M306" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="M307" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21370,7 +21370,7 @@
       </c>
       <c r="M308" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21437,7 +21437,7 @@
       </c>
       <c r="M309" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M310" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="M311" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="M312" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21705,7 +21705,7 @@
       </c>
       <c r="M313" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21772,7 +21772,7 @@
       </c>
       <c r="M314" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21839,7 +21839,7 @@
       </c>
       <c r="M315" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="M316" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="M317" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22040,7 @@
       </c>
       <c r="M318" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="M319" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="M320" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="M321" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22308,7 @@
       </c>
       <c r="M322" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22375,7 +22375,7 @@
       </c>
       <c r="M323" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="M324" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="M325" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22576,7 +22576,7 @@
       </c>
       <c r="M326" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="M327" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="M328" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="M329" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22844,7 @@
       </c>
       <c r="M330" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="M331" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="M332" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23045,7 +23045,7 @@
       </c>
       <c r="M333" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23112,7 +23112,7 @@
       </c>
       <c r="M334" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="M335" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23246,7 +23246,7 @@
       </c>
       <c r="M336" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="M337" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="M338" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23447,7 +23447,7 @@
       </c>
       <c r="M339" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23514,7 +23514,7 @@
       </c>
       <c r="M340" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="M341" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23648,7 +23648,7 @@
       </c>
       <c r="M342" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23715,7 +23715,7 @@
       </c>
       <c r="M343" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23782,7 +23782,7 @@
       </c>
       <c r="M344" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="M345" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23916,7 +23916,7 @@
       </c>
       <c r="M346" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="M347" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24050,7 +24050,7 @@
       </c>
       <c r="M348" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="M349" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24184,7 @@
       </c>
       <c r="M350" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24251,7 +24251,7 @@
       </c>
       <c r="M351" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="M352" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="M353" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24452,7 +24452,7 @@
       </c>
       <c r="M354" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24519,7 +24519,7 @@
       </c>
       <c r="M355" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24586,7 +24586,7 @@
       </c>
       <c r="M356" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24653,7 +24653,7 @@
       </c>
       <c r="M357" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24720,7 +24720,7 @@
       </c>
       <c r="M358" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="M359" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="M360" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24921,7 +24921,7 @@
       </c>
       <c r="M361" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -24988,7 +24988,7 @@
       </c>
       <c r="M362" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25055,7 +25055,7 @@
       </c>
       <c r="M363" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="M364" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25189,7 +25189,7 @@
       </c>
       <c r="M365" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="M366" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25323,7 +25323,7 @@
       </c>
       <c r="M367" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25390,7 +25390,7 @@
       </c>
       <c r="M368" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25457,7 +25457,7 @@
       </c>
       <c r="M369" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25524,7 +25524,7 @@
       </c>
       <c r="M370" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25591,7 @@
       </c>
       <c r="M371" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25658,7 +25658,7 @@
       </c>
       <c r="M372" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25725,7 +25725,7 @@
       </c>
       <c r="M373" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25792,7 +25792,7 @@
       </c>
       <c r="M374" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M375" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="M376" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="M377" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26060,7 +26060,7 @@
       </c>
       <c r="M378" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26127,7 +26127,7 @@
       </c>
       <c r="M379" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M380" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="M381" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="M382" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="M383" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26462,7 +26462,7 @@
       </c>
       <c r="M384" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="M385" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26596,7 @@
       </c>
       <c r="M386" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="M387" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26730,7 +26730,7 @@
       </c>
       <c r="M388" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26797,7 +26797,7 @@
       </c>
       <c r="M389" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26864,7 +26864,7 @@
       </c>
       <c r="M390" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="M391" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -26998,7 +26998,7 @@
       </c>
       <c r="M392" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27065,7 +27065,7 @@
       </c>
       <c r="M393" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="M394" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27199,7 +27199,7 @@
       </c>
       <c r="M395" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27266,7 +27266,7 @@
       </c>
       <c r="M396" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="M397" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
       </c>
       <c r="M398" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27467,7 +27467,7 @@
       </c>
       <c r="M399" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27534,7 +27534,7 @@
       </c>
       <c r="M400" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27601,7 +27601,7 @@
       </c>
       <c r="M401" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27668,7 +27668,7 @@
       </c>
       <c r="M402" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27735,7 +27735,7 @@
       </c>
       <c r="M403" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27802,7 +27802,7 @@
       </c>
       <c r="M404" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27869,7 +27869,7 @@
       </c>
       <c r="M405" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -27936,7 +27936,7 @@
       </c>
       <c r="M406" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="M407" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="M408" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28137,7 +28137,7 @@
       </c>
       <c r="M409" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="M410" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28271,7 +28271,7 @@
       </c>
       <c r="M411" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28338,7 +28338,7 @@
       </c>
       <c r="M412" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28405,7 +28405,7 @@
       </c>
       <c r="M413" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="M414" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28539,7 +28539,7 @@
       </c>
       <c r="M415" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28606,7 +28606,7 @@
       </c>
       <c r="M416" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="M417" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28740,7 +28740,7 @@
       </c>
       <c r="M418" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28807,7 +28807,7 @@
       </c>
       <c r="M419" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="M420" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="M421" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29008,7 +29008,7 @@
       </c>
       <c r="M422" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29075,7 +29075,7 @@
       </c>
       <c r="M423" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="M424" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="M425" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29276,7 +29276,7 @@
       </c>
       <c r="M426" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29343,7 +29343,7 @@
       </c>
       <c r="M427" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="M428" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="M429" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29544,7 +29544,7 @@
       </c>
       <c r="M430" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29611,7 +29611,7 @@
       </c>
       <c r="M431" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="M432" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29745,7 +29745,7 @@
       </c>
       <c r="M433" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29812,7 +29812,7 @@
       </c>
       <c r="M434" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29879,7 +29879,7 @@
       </c>
       <c r="M435" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -29946,7 +29946,7 @@
       </c>
       <c r="M436" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30013,7 +30013,7 @@
       </c>
       <c r="M437" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30080,7 +30080,7 @@
       </c>
       <c r="M438" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30147,7 +30147,7 @@
       </c>
       <c r="M439" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M440" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="M441" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30348,7 +30348,7 @@
       </c>
       <c r="M442" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="M443" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30482,7 +30482,7 @@
       </c>
       <c r="M444" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="M445" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="M446" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="M447" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="M448" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30817,7 +30817,7 @@
       </c>
       <c r="M449" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M450" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -30951,7 +30951,7 @@
       </c>
       <c r="M451" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31018,7 +31018,7 @@
       </c>
       <c r="M452" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
       </c>
       <c r="M453" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31152,7 +31152,7 @@
       </c>
       <c r="M454" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31219,7 +31219,7 @@
       </c>
       <c r="M455" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="M456" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31353,7 +31353,7 @@
       </c>
       <c r="M457" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31420,7 +31420,7 @@
       </c>
       <c r="M458" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="M459" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="M460" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31621,7 +31621,7 @@
       </c>
       <c r="M461" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31688,7 +31688,7 @@
       </c>
       <c r="M462" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="M463" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31822,7 +31822,7 @@
       </c>
       <c r="M464" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="M465" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -31956,7 +31956,7 @@
       </c>
       <c r="M466" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32023,7 +32023,7 @@
       </c>
       <c r="M467" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="M468" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32157,7 +32157,7 @@
       </c>
       <c r="M469" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32224,7 +32224,7 @@
       </c>
       <c r="M470" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32291,7 @@
       </c>
       <c r="M471" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="M472" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32425,7 +32425,7 @@
       </c>
       <c r="M473" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="M474" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="M475" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32626,7 +32626,7 @@
       </c>
       <c r="M476" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32693,7 +32693,7 @@
       </c>
       <c r="M477" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32760,7 +32760,7 @@
       </c>
       <c r="M478" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="M479" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="M480" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -32961,7 +32961,7 @@
       </c>
       <c r="M481" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="M482" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33095,7 +33095,7 @@
       </c>
       <c r="M483" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33162,7 +33162,7 @@
       </c>
       <c r="M484" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="M485" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33296,7 +33296,7 @@
       </c>
       <c r="M486" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33363,7 +33363,7 @@
       </c>
       <c r="M487" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="M488" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="M489" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33564,7 +33564,7 @@
       </c>
       <c r="M490" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33631,7 +33631,7 @@
       </c>
       <c r="M491" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="M492" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33765,7 +33765,7 @@
       </c>
       <c r="M493" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33832,7 +33832,7 @@
       </c>
       <c r="M494" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33899,7 +33899,7 @@
       </c>
       <c r="M495" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="M496" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="M497" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34100,7 +34100,7 @@
       </c>
       <c r="M498" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="M499" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34234,7 +34234,7 @@
       </c>
       <c r="M500" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="M501" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34368,7 @@
       </c>
       <c r="M502" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="M503" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="M504" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34569,7 +34569,7 @@
       </c>
       <c r="M505" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34636,7 +34636,7 @@
       </c>
       <c r="M506" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="M507" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34770,7 +34770,7 @@
       </c>
       <c r="M508" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34837,7 +34837,7 @@
       </c>
       <c r="M509" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34904,7 +34904,7 @@
       </c>
       <c r="M510" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -34971,7 +34971,7 @@
       </c>
       <c r="M511" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35038,7 +35038,7 @@
       </c>
       <c r="M512" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35105,7 +35105,7 @@
       </c>
       <c r="M513" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35172,7 +35172,7 @@
       </c>
       <c r="M514" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35239,7 +35239,7 @@
       </c>
       <c r="M515" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35306,7 +35306,7 @@
       </c>
       <c r="M516" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35373,7 +35373,7 @@
       </c>
       <c r="M517" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35440,7 +35440,7 @@
       </c>
       <c r="M518" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35507,7 +35507,7 @@
       </c>
       <c r="M519" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="M520" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35641,7 +35641,7 @@
       </c>
       <c r="M521" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35708,7 +35708,7 @@
       </c>
       <c r="M522" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35775,7 +35775,7 @@
       </c>
       <c r="M523" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="M524" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35909,7 +35909,7 @@
       </c>
       <c r="M525" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="M526" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36043,7 +36043,7 @@
       </c>
       <c r="M527" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36110,7 +36110,7 @@
       </c>
       <c r="M528" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36177,7 +36177,7 @@
       </c>
       <c r="M529" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36244,7 +36244,7 @@
       </c>
       <c r="M530" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36311,7 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36378,7 +36378,7 @@
       </c>
       <c r="M532" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36445,7 +36445,7 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36512,7 +36512,7 @@
       </c>
       <c r="M534" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36646,7 +36646,7 @@
       </c>
       <c r="M536" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36713,7 +36713,7 @@
       </c>
       <c r="M537" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36780,7 +36780,7 @@
       </c>
       <c r="M538" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="M539" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36914,7 +36914,7 @@
       </c>
       <c r="M540" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -36981,7 +36981,7 @@
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37048,7 +37048,7 @@
       </c>
       <c r="M542" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="M543" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37182,7 +37182,7 @@
       </c>
       <c r="M544" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37249,7 +37249,7 @@
       </c>
       <c r="M545" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37316,7 +37316,7 @@
       </c>
       <c r="M546" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37383,7 +37383,7 @@
       </c>
       <c r="M547" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37450,7 +37450,7 @@
       </c>
       <c r="M548" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37517,7 +37517,7 @@
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37584,7 +37584,7 @@
       </c>
       <c r="M550" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37651,7 +37651,7 @@
       </c>
       <c r="M551" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37718,7 +37718,7 @@
       </c>
       <c r="M552" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37785,7 +37785,7 @@
       </c>
       <c r="M553" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37852,7 +37852,7 @@
       </c>
       <c r="M554" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37919,7 +37919,7 @@
       </c>
       <c r="M555" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="M556" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38053,7 +38053,7 @@
       </c>
       <c r="M557" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38120,7 +38120,7 @@
       </c>
       <c r="M558" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="M559" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38254,7 +38254,7 @@
       </c>
       <c r="M560" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="M561" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38388,7 +38388,7 @@
       </c>
       <c r="M562" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38455,7 +38455,7 @@
       </c>
       <c r="M563" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="M564" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38589,7 +38589,7 @@
       </c>
       <c r="M565" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38656,7 +38656,7 @@
       </c>
       <c r="M566" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38723,7 +38723,7 @@
       </c>
       <c r="M567" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38790,7 +38790,7 @@
       </c>
       <c r="M568" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38857,7 +38857,7 @@
       </c>
       <c r="M569" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38924,7 +38924,7 @@
       </c>
       <c r="M570" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -38991,7 +38991,7 @@
       </c>
       <c r="M571" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39058,7 +39058,7 @@
       </c>
       <c r="M572" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39125,7 +39125,7 @@
       </c>
       <c r="M573" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39192,7 +39192,7 @@
       </c>
       <c r="M574" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="M575" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="M576" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="M577" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39460,7 +39460,7 @@
       </c>
       <c r="M578" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39527,7 +39527,7 @@
       </c>
       <c r="M579" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39594,7 +39594,7 @@
       </c>
       <c r="M580" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39661,7 +39661,7 @@
       </c>
       <c r="M581" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39728,7 +39728,7 @@
       </c>
       <c r="M582" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39795,7 +39795,7 @@
       </c>
       <c r="M583" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39862,7 +39862,7 @@
       </c>
       <c r="M584" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39929,7 +39929,7 @@
       </c>
       <c r="M585" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -39996,7 +39996,7 @@
       </c>
       <c r="M586" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40063,7 +40063,7 @@
       </c>
       <c r="M587" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40130,7 +40130,7 @@
       </c>
       <c r="M588" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40197,7 +40197,7 @@
       </c>
       <c r="M589" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40264,7 +40264,7 @@
       </c>
       <c r="M590" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40331,7 +40331,7 @@
       </c>
       <c r="M591" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40398,7 +40398,7 @@
       </c>
       <c r="M592" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40465,7 +40465,7 @@
       </c>
       <c r="M593" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40532,7 +40532,7 @@
       </c>
       <c r="M594" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40599,7 +40599,7 @@
       </c>
       <c r="M595" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40666,7 +40666,7 @@
       </c>
       <c r="M596" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40733,7 @@
       </c>
       <c r="M597" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="M598" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40867,7 +40867,7 @@
       </c>
       <c r="M599" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -40934,7 +40934,7 @@
       </c>
       <c r="M600" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41001,7 +41001,7 @@
       </c>
       <c r="M601" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41068,7 +41068,7 @@
       </c>
       <c r="M602" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="M603" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41202,7 +41202,7 @@
       </c>
       <c r="M604" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41269,7 +41269,7 @@
       </c>
       <c r="M605" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41336,7 +41336,7 @@
       </c>
       <c r="M606" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41403,7 +41403,7 @@
       </c>
       <c r="M607" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41470,7 +41470,7 @@
       </c>
       <c r="M608" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41537,7 +41537,7 @@
       </c>
       <c r="M609" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41604,7 +41604,7 @@
       </c>
       <c r="M610" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41671,7 +41671,7 @@
       </c>
       <c r="M611" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41738,7 +41738,7 @@
       </c>
       <c r="M612" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41805,7 +41805,7 @@
       </c>
       <c r="M613" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41872,7 +41872,7 @@
       </c>
       <c r="M614" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -41939,7 +41939,7 @@
       </c>
       <c r="M615" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42006,7 +42006,7 @@
       </c>
       <c r="M616" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42073,7 +42073,7 @@
       </c>
       <c r="M617" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42140,7 +42140,7 @@
       </c>
       <c r="M618" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42207,7 +42207,7 @@
       </c>
       <c r="M619" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42274,7 +42274,7 @@
       </c>
       <c r="M620" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42341,7 +42341,7 @@
       </c>
       <c r="M621" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42408,7 +42408,7 @@
       </c>
       <c r="M622" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42475,7 +42475,7 @@
       </c>
       <c r="M623" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42542,7 +42542,7 @@
       </c>
       <c r="M624" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="M625" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42676,7 +42676,7 @@
       </c>
       <c r="M626" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42743,7 +42743,7 @@
       </c>
       <c r="M627" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42810,7 +42810,7 @@
       </c>
       <c r="M628" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42877,7 +42877,7 @@
       </c>
       <c r="M629" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -42944,7 +42944,7 @@
       </c>
       <c r="M630" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43011,7 +43011,7 @@
       </c>
       <c r="M631" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43078,7 +43078,7 @@
       </c>
       <c r="M632" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43145,7 +43145,7 @@
       </c>
       <c r="M633" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43212,7 +43212,7 @@
       </c>
       <c r="M634" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43279,7 +43279,7 @@
       </c>
       <c r="M635" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43346,7 +43346,7 @@
       </c>
       <c r="M636" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43413,7 +43413,7 @@
       </c>
       <c r="M637" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43480,7 +43480,7 @@
       </c>
       <c r="M638" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43547,7 +43547,7 @@
       </c>
       <c r="M639" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="M640" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
       </c>
       <c r="M641" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43748,7 +43748,7 @@
       </c>
       <c r="M642" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43815,7 +43815,7 @@
       </c>
       <c r="M643" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43882,7 +43882,7 @@
       </c>
       <c r="M644" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -43949,7 +43949,7 @@
       </c>
       <c r="M645" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="M646" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -44083,7 +44083,7 @@
       </c>
       <c r="M647" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -44150,7 +44150,7 @@
       </c>
       <c r="M648" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -44217,7 +44217,7 @@
       </c>
       <c r="M649" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -44284,7 +44284,7 @@
       </c>
       <c r="M650" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -44351,7 +44351,7 @@
       </c>
       <c r="M651" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$M$652</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$M$652</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="M84" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M86" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="M88" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="M96" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="M103" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="M105" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="M106" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="M107" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="M112" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="M113" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="M114" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M115" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="M117" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="M119" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M120" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="M121" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="M122" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="M123" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="M124" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="M125" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="M126" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="M127" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="M128" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="M129" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="M130" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="M131" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="M132" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="M133" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="M134" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M135" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="M136" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="M137" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="M138" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="M139" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="M140" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="M141" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M142" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="M143" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="M144" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="M145" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="M146" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="M147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="M148" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10717,7 +10717,7 @@
       </c>
       <c r="M149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="M150" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="M151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="M152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="M153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="M154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="M156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="M157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="M158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="M160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="M161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="M162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="M163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="M164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="M165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="M166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="M167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="M168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="M169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="M171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="M172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="M173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="M174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="M175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="M176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="M177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
       </c>
       <c r="M178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="M179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="M181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="M182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -12995,7 +12995,7 @@
       </c>
       <c r="M183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="M184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="M185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="M186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="M187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="M188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="M189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="M190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
       </c>
       <c r="M191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="M192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="M193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="M194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="M196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="M197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="M198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="M199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="M200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="M201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="M202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="M203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="M204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="M205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="M206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="M207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="M208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="M209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="M210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="M211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="M212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="M213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="M214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="M215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="M216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15273,7 +15273,7 @@
       </c>
       <c r="M217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="M218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15407,7 @@
       </c>
       <c r="M219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="M220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="M221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="M222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="M223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="M224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="M225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="M226" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="M227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="M228" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="M229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="M230" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16211,7 +16211,7 @@
       </c>
       <c r="M231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="M232" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16345,7 +16345,7 @@
       </c>
       <c r="M233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16412,7 +16412,7 @@
       </c>
       <c r="M234" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="M235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="M236" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="M237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="M238" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="M239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M240" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="M241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="M242" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="M243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="M244" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="M246" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="M247" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="M248" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="M249" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="M250" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="M251" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="M252" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="M253" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="M254" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17819,7 +17819,7 @@
       </c>
       <c r="M255" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="M256" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="M257" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="M258" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18087,7 +18087,7 @@
       </c>
       <c r="M259" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18154,7 @@
       </c>
       <c r="M260" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="M261" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="M262" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="M263" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="M264" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18489,7 @@
       </c>
       <c r="M265" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="M266" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="M267" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="M268" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="M269" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M270" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="M271" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -18958,7 +18958,7 @@
       </c>
       <c r="M272" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="M273" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19092,7 +19092,7 @@
       </c>
       <c r="M274" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="M275" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="M276" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19293,7 +19293,7 @@
       </c>
       <c r="M277" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="M278" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="M279" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="M280" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="M281" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="M282" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="M283" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19762,7 +19762,7 @@
       </c>
       <c r="M284" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="M285" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19896,7 +19896,7 @@
       </c>
       <c r="M286" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="M287" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="M288" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="M289" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="M290" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="M291" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="M292" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="M293" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20432,7 +20432,7 @@
       </c>
       <c r="M294" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="M295" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="M296" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20633,7 @@
       </c>
       <c r="M297" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="M298" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20767,7 +20767,7 @@
       </c>
       <c r="M299" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="M300" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="M301" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="M302" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="M303" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="M304" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="M305" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="M306" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="M307" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21370,7 +21370,7 @@
       </c>
       <c r="M308" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21437,7 +21437,7 @@
       </c>
       <c r="M309" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M310" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="M311" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="M312" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21705,7 +21705,7 @@
       </c>
       <c r="M313" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21772,7 +21772,7 @@
       </c>
       <c r="M314" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21839,7 +21839,7 @@
       </c>
       <c r="M315" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="M316" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="M317" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22040,7 @@
       </c>
       <c r="M318" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="M319" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="M320" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="M321" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22308,7 @@
       </c>
       <c r="M322" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22375,7 +22375,7 @@
       </c>
       <c r="M323" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="M324" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="M325" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22576,7 +22576,7 @@
       </c>
       <c r="M326" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="M327" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="M328" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="M329" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22844,7 @@
       </c>
       <c r="M330" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="M331" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="M332" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23045,7 +23045,7 @@
       </c>
       <c r="M333" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23112,7 +23112,7 @@
       </c>
       <c r="M334" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="M335" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23246,7 +23246,7 @@
       </c>
       <c r="M336" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="M337" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="M338" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23447,7 +23447,7 @@
       </c>
       <c r="M339" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23514,7 +23514,7 @@
       </c>
       <c r="M340" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="M341" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23648,7 +23648,7 @@
       </c>
       <c r="M342" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23715,7 +23715,7 @@
       </c>
       <c r="M343" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23782,7 +23782,7 @@
       </c>
       <c r="M344" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="M345" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23916,7 +23916,7 @@
       </c>
       <c r="M346" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="M347" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24050,7 +24050,7 @@
       </c>
       <c r="M348" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="M349" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24184,7 @@
       </c>
       <c r="M350" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24251,7 +24251,7 @@
       </c>
       <c r="M351" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="M352" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="M353" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24452,7 +24452,7 @@
       </c>
       <c r="M354" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24519,7 +24519,7 @@
       </c>
       <c r="M355" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24586,7 +24586,7 @@
       </c>
       <c r="M356" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24653,7 +24653,7 @@
       </c>
       <c r="M357" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24720,7 +24720,7 @@
       </c>
       <c r="M358" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="M359" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="M360" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24921,7 +24921,7 @@
       </c>
       <c r="M361" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -24988,7 +24988,7 @@
       </c>
       <c r="M362" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25055,7 +25055,7 @@
       </c>
       <c r="M363" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="M364" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25189,7 +25189,7 @@
       </c>
       <c r="M365" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="M366" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25323,7 +25323,7 @@
       </c>
       <c r="M367" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25390,7 +25390,7 @@
       </c>
       <c r="M368" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25457,7 +25457,7 @@
       </c>
       <c r="M369" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25524,7 +25524,7 @@
       </c>
       <c r="M370" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25591,7 @@
       </c>
       <c r="M371" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25658,7 +25658,7 @@
       </c>
       <c r="M372" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25725,7 +25725,7 @@
       </c>
       <c r="M373" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25792,7 +25792,7 @@
       </c>
       <c r="M374" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M375" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="M376" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="M377" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26060,7 +26060,7 @@
       </c>
       <c r="M378" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26127,7 +26127,7 @@
       </c>
       <c r="M379" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M380" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="M381" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="M382" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="M383" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26462,7 +26462,7 @@
       </c>
       <c r="M384" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="M385" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26596,7 @@
       </c>
       <c r="M386" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="M387" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26730,7 +26730,7 @@
       </c>
       <c r="M388" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26797,7 +26797,7 @@
       </c>
       <c r="M389" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26864,7 +26864,7 @@
       </c>
       <c r="M390" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="M391" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -26998,7 +26998,7 @@
       </c>
       <c r="M392" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27065,7 +27065,7 @@
       </c>
       <c r="M393" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="M394" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27199,7 +27199,7 @@
       </c>
       <c r="M395" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27266,7 +27266,7 @@
       </c>
       <c r="M396" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="M397" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
       </c>
       <c r="M398" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27467,7 +27467,7 @@
       </c>
       <c r="M399" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27534,7 +27534,7 @@
       </c>
       <c r="M400" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27601,7 +27601,7 @@
       </c>
       <c r="M401" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27668,7 +27668,7 @@
       </c>
       <c r="M402" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27735,7 +27735,7 @@
       </c>
       <c r="M403" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27802,7 +27802,7 @@
       </c>
       <c r="M404" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27869,7 +27869,7 @@
       </c>
       <c r="M405" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -27936,7 +27936,7 @@
       </c>
       <c r="M406" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="M407" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="M408" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28137,7 +28137,7 @@
       </c>
       <c r="M409" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="M410" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28271,7 +28271,7 @@
       </c>
       <c r="M411" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28338,7 +28338,7 @@
       </c>
       <c r="M412" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28405,7 +28405,7 @@
       </c>
       <c r="M413" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="M414" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28539,7 +28539,7 @@
       </c>
       <c r="M415" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28606,7 +28606,7 @@
       </c>
       <c r="M416" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="M417" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28740,7 +28740,7 @@
       </c>
       <c r="M418" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28807,7 +28807,7 @@
       </c>
       <c r="M419" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="M420" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="M421" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29008,7 +29008,7 @@
       </c>
       <c r="M422" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29075,7 +29075,7 @@
       </c>
       <c r="M423" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="M424" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="M425" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29276,7 +29276,7 @@
       </c>
       <c r="M426" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29343,7 +29343,7 @@
       </c>
       <c r="M427" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="M428" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="M429" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29544,7 +29544,7 @@
       </c>
       <c r="M430" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29611,7 +29611,7 @@
       </c>
       <c r="M431" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="M432" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29745,7 +29745,7 @@
       </c>
       <c r="M433" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29812,7 +29812,7 @@
       </c>
       <c r="M434" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29879,7 +29879,7 @@
       </c>
       <c r="M435" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -29946,7 +29946,7 @@
       </c>
       <c r="M436" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30013,7 +30013,7 @@
       </c>
       <c r="M437" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30080,7 +30080,7 @@
       </c>
       <c r="M438" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30147,7 +30147,7 @@
       </c>
       <c r="M439" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M440" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="M441" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30348,7 +30348,7 @@
       </c>
       <c r="M442" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="M443" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30482,7 +30482,7 @@
       </c>
       <c r="M444" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="M445" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="M446" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="M447" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="M448" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30817,7 +30817,7 @@
       </c>
       <c r="M449" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M450" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -30951,7 +30951,7 @@
       </c>
       <c r="M451" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31018,7 +31018,7 @@
       </c>
       <c r="M452" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
       </c>
       <c r="M453" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31152,7 +31152,7 @@
       </c>
       <c r="M454" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31219,7 +31219,7 @@
       </c>
       <c r="M455" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="M456" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31353,7 +31353,7 @@
       </c>
       <c r="M457" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31420,7 +31420,7 @@
       </c>
       <c r="M458" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="M459" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="M460" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31621,7 +31621,7 @@
       </c>
       <c r="M461" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31688,7 +31688,7 @@
       </c>
       <c r="M462" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="M463" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31822,7 +31822,7 @@
       </c>
       <c r="M464" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="M465" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -31956,7 +31956,7 @@
       </c>
       <c r="M466" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32023,7 +32023,7 @@
       </c>
       <c r="M467" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="M468" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32157,7 +32157,7 @@
       </c>
       <c r="M469" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32224,7 +32224,7 @@
       </c>
       <c r="M470" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32291,7 @@
       </c>
       <c r="M471" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="M472" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32425,7 +32425,7 @@
       </c>
       <c r="M473" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="M474" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="M475" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32626,7 +32626,7 @@
       </c>
       <c r="M476" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32693,7 +32693,7 @@
       </c>
       <c r="M477" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32760,7 +32760,7 @@
       </c>
       <c r="M478" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="M479" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="M480" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -32961,7 +32961,7 @@
       </c>
       <c r="M481" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="M482" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33095,7 +33095,7 @@
       </c>
       <c r="M483" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33162,7 +33162,7 @@
       </c>
       <c r="M484" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="M485" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33296,7 +33296,7 @@
       </c>
       <c r="M486" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33363,7 +33363,7 @@
       </c>
       <c r="M487" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="M488" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="M489" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33564,7 +33564,7 @@
       </c>
       <c r="M490" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33631,7 +33631,7 @@
       </c>
       <c r="M491" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="M492" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33765,7 +33765,7 @@
       </c>
       <c r="M493" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33832,7 +33832,7 @@
       </c>
       <c r="M494" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33899,7 +33899,7 @@
       </c>
       <c r="M495" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="M496" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="M497" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34100,7 +34100,7 @@
       </c>
       <c r="M498" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="M499" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34234,7 +34234,7 @@
       </c>
       <c r="M500" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="M501" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34368,7 @@
       </c>
       <c r="M502" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="M503" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="M504" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34569,7 +34569,7 @@
       </c>
       <c r="M505" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34636,7 +34636,7 @@
       </c>
       <c r="M506" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="M507" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34770,7 +34770,7 @@
       </c>
       <c r="M508" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34837,7 +34837,7 @@
       </c>
       <c r="M509" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34904,7 +34904,7 @@
       </c>
       <c r="M510" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -34971,7 +34971,7 @@
       </c>
       <c r="M511" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35038,7 +35038,7 @@
       </c>
       <c r="M512" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35105,7 +35105,7 @@
       </c>
       <c r="M513" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35172,7 +35172,7 @@
       </c>
       <c r="M514" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35239,7 +35239,7 @@
       </c>
       <c r="M515" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35306,7 +35306,7 @@
       </c>
       <c r="M516" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35373,7 +35373,7 @@
       </c>
       <c r="M517" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35440,7 +35440,7 @@
       </c>
       <c r="M518" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35507,7 +35507,7 @@
       </c>
       <c r="M519" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="M520" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35641,7 +35641,7 @@
       </c>
       <c r="M521" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35708,7 +35708,7 @@
       </c>
       <c r="M522" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35775,7 +35775,7 @@
       </c>
       <c r="M523" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="M524" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35909,7 +35909,7 @@
       </c>
       <c r="M525" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="M526" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36043,7 +36043,7 @@
       </c>
       <c r="M527" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36110,7 +36110,7 @@
       </c>
       <c r="M528" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36177,7 +36177,7 @@
       </c>
       <c r="M529" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36244,7 +36244,7 @@
       </c>
       <c r="M530" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36311,7 @@
       </c>
       <c r="M531" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36378,7 +36378,7 @@
       </c>
       <c r="M532" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36445,7 +36445,7 @@
       </c>
       <c r="M533" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36512,7 +36512,7 @@
       </c>
       <c r="M534" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36646,7 +36646,7 @@
       </c>
       <c r="M536" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36713,7 +36713,7 @@
       </c>
       <c r="M537" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36780,7 +36780,7 @@
       </c>
       <c r="M538" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="M539" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36914,7 +36914,7 @@
       </c>
       <c r="M540" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -36981,7 +36981,7 @@
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37048,7 +37048,7 @@
       </c>
       <c r="M542" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="M543" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37182,7 +37182,7 @@
       </c>
       <c r="M544" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37249,7 +37249,7 @@
       </c>
       <c r="M545" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37316,7 +37316,7 @@
       </c>
       <c r="M546" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37383,7 +37383,7 @@
       </c>
       <c r="M547" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37450,7 +37450,7 @@
       </c>
       <c r="M548" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37517,7 +37517,7 @@
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37584,7 +37584,7 @@
       </c>
       <c r="M550" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37651,7 +37651,7 @@
       </c>
       <c r="M551" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37718,7 +37718,7 @@
       </c>
       <c r="M552" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37785,7 +37785,7 @@
       </c>
       <c r="M553" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37852,7 +37852,7 @@
       </c>
       <c r="M554" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37919,7 +37919,7 @@
       </c>
       <c r="M555" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="M556" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38053,7 +38053,7 @@
       </c>
       <c r="M557" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38120,7 +38120,7 @@
       </c>
       <c r="M558" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="M559" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38254,7 +38254,7 @@
       </c>
       <c r="M560" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="M561" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38388,7 +38388,7 @@
       </c>
       <c r="M562" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38455,7 +38455,7 @@
       </c>
       <c r="M563" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="M564" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38589,7 +38589,7 @@
       </c>
       <c r="M565" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38656,7 +38656,7 @@
       </c>
       <c r="M566" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38723,7 +38723,7 @@
       </c>
       <c r="M567" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38790,7 +38790,7 @@
       </c>
       <c r="M568" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38857,7 +38857,7 @@
       </c>
       <c r="M569" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38924,7 +38924,7 @@
       </c>
       <c r="M570" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -38991,7 +38991,7 @@
       </c>
       <c r="M571" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39058,7 +39058,7 @@
       </c>
       <c r="M572" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39125,7 +39125,7 @@
       </c>
       <c r="M573" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39192,7 +39192,7 @@
       </c>
       <c r="M574" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="M575" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="M576" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="M577" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39460,7 +39460,7 @@
       </c>
       <c r="M578" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39527,7 +39527,7 @@
       </c>
       <c r="M579" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39594,7 +39594,7 @@
       </c>
       <c r="M580" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39661,7 +39661,7 @@
       </c>
       <c r="M581" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39728,7 +39728,7 @@
       </c>
       <c r="M582" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39795,7 +39795,7 @@
       </c>
       <c r="M583" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39862,7 +39862,7 @@
       </c>
       <c r="M584" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39929,7 +39929,7 @@
       </c>
       <c r="M585" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -39996,7 +39996,7 @@
       </c>
       <c r="M586" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40063,7 +40063,7 @@
       </c>
       <c r="M587" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40130,7 +40130,7 @@
       </c>
       <c r="M588" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40197,7 +40197,7 @@
       </c>
       <c r="M589" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40264,7 +40264,7 @@
       </c>
       <c r="M590" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40331,7 +40331,7 @@
       </c>
       <c r="M591" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40398,7 +40398,7 @@
       </c>
       <c r="M592" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40465,7 +40465,7 @@
       </c>
       <c r="M593" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40532,7 +40532,7 @@
       </c>
       <c r="M594" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40599,7 +40599,7 @@
       </c>
       <c r="M595" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40666,7 +40666,7 @@
       </c>
       <c r="M596" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40733,7 @@
       </c>
       <c r="M597" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="M598" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40867,7 +40867,7 @@
       </c>
       <c r="M599" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -40934,7 +40934,7 @@
       </c>
       <c r="M600" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41001,7 +41001,7 @@
       </c>
       <c r="M601" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41068,7 +41068,7 @@
       </c>
       <c r="M602" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="M603" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41202,7 +41202,7 @@
       </c>
       <c r="M604" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41269,7 +41269,7 @@
       </c>
       <c r="M605" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41336,7 +41336,7 @@
       </c>
       <c r="M606" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41403,7 +41403,7 @@
       </c>
       <c r="M607" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41470,7 +41470,7 @@
       </c>
       <c r="M608" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41537,7 +41537,7 @@
       </c>
       <c r="M609" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41604,7 +41604,7 @@
       </c>
       <c r="M610" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41671,7 +41671,7 @@
       </c>
       <c r="M611" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41738,7 +41738,7 @@
       </c>
       <c r="M612" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41805,7 +41805,7 @@
       </c>
       <c r="M613" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41872,7 +41872,7 @@
       </c>
       <c r="M614" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -41939,7 +41939,7 @@
       </c>
       <c r="M615" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42006,7 +42006,7 @@
       </c>
       <c r="M616" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42073,7 +42073,7 @@
       </c>
       <c r="M617" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42140,7 +42140,7 @@
       </c>
       <c r="M618" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42207,7 +42207,7 @@
       </c>
       <c r="M619" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42274,7 +42274,7 @@
       </c>
       <c r="M620" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42341,7 +42341,7 @@
       </c>
       <c r="M621" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42408,7 +42408,7 @@
       </c>
       <c r="M622" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42475,7 +42475,7 @@
       </c>
       <c r="M623" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42542,7 +42542,7 @@
       </c>
       <c r="M624" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="M625" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42676,7 +42676,7 @@
       </c>
       <c r="M626" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42743,7 +42743,7 @@
       </c>
       <c r="M627" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42810,7 +42810,7 @@
       </c>
       <c r="M628" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42877,7 +42877,7 @@
       </c>
       <c r="M629" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -42944,7 +42944,7 @@
       </c>
       <c r="M630" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43011,7 +43011,7 @@
       </c>
       <c r="M631" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43078,7 +43078,7 @@
       </c>
       <c r="M632" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43145,7 +43145,7 @@
       </c>
       <c r="M633" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43212,7 +43212,7 @@
       </c>
       <c r="M634" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43279,7 +43279,7 @@
       </c>
       <c r="M635" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43346,7 +43346,7 @@
       </c>
       <c r="M636" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43413,7 +43413,7 @@
       </c>
       <c r="M637" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43480,7 +43480,7 @@
       </c>
       <c r="M638" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43547,7 +43547,7 @@
       </c>
       <c r="M639" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="M640" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
       </c>
       <c r="M641" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43748,7 +43748,7 @@
       </c>
       <c r="M642" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43815,7 +43815,7 @@
       </c>
       <c r="M643" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43882,7 +43882,7 @@
       </c>
       <c r="M644" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -43949,7 +43949,7 @@
       </c>
       <c r="M645" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="M646" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -44083,7 +44083,7 @@
       </c>
       <c r="M647" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -44150,7 +44150,7 @@
       </c>
       <c r="M648" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -44217,7 +44217,7 @@
       </c>
       <c r="M649" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -44284,7 +44284,7 @@
       </c>
       <c r="M650" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -44351,7 +44351,7 @@
       </c>
       <c r="M651" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -44418,7 +44418,7 @@
       </c>
       <c r="M652" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$O$652</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -12405,7 +12405,7 @@
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>Your second-favorite member.</t>
+          <t>你的第二喜歡的成員，副本命。</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="L152" s="10" t="inlineStr">
         <is>
-          <t>I can't decide my ultimate bias, but my second bias is clear.</t>
+          <t>最愛決定不了，但副本命很確定。</t>
         </is>
       </c>
       <c r="M152" s="10" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>The moment you officially fall into a fandom.</t>
+          <t>正式入坑成為某個粉絲圈一員的那個瞬間。</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L153" s="10" t="inlineStr">
         <is>
-          <t>I became a fan after watching this stage.</t>
+          <t>看了這個舞台後入坑了。</t>
         </is>
       </c>
       <c r="M153" s="10" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>Stopping fan activities for a group; the opposite of 입덕.</t>
+          <t>停止對某個團體的追星活動，是입덕的反義詞，脫飯。</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="L154" s="10" t="inlineStr">
         <is>
-          <t>I heard he left the fandom for good.</t>
+          <t>聽說他最後脫飯了。</t>
         </is>
       </c>
       <c r="M154" s="10" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>A temporary break from fan activities.</t>
+          <t>暫時停止追星活動一段時間，休飯。</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="L155" s="10" t="inlineStr">
         <is>
-          <t>I'm on a fandom hiatus for exam season.</t>
+          <t>考試期間先休飯一下。</t>
         </is>
       </c>
       <c r="M155" s="10" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>Someone deeply devoted to a hobby or fandom (from the Japanese "otaku").</t>
+          <t>對某個興趣或圈子極度投入的人，源自日文「御宅族」。</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L157" s="10" t="inlineStr">
         <is>
-          <t>I'm a total idol nerd.</t>
+          <t>我是不折不扣的偶像宅。</t>
         </is>
       </c>
       <c r="M157" s="10" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>An organized fandom-wide effort — streaming, hashtags, voting — done together at a set time.</t>
+          <t>粉絲圈有組織地在特定時間一起進行刷榜、標籤宣傳、投票等活動，總攻。</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="L159" s="10" t="inlineStr">
         <is>
-          <t>We're doing a coordinated push at 8 PM tonight!</t>
+          <t>今晚八點開始總攻！</t>
         </is>
       </c>
       <c r="M159" s="10" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>Idols interacting directly with fans through live broadcasts or comments.</t>
+          <t>偶像透過直播或留言直接與粉絲互動。</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="L161" s="10" t="inlineStr">
         <is>
-          <t>They suddenly went live to communicate with fans today!</t>
+          <t>今天突然開了互動直播！</t>
         </is>
       </c>
       <c r="M161" s="10" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>Stubbornly enduring or waiting something out, even when it's hard.</t>
+          <t>即使很辛苦也頑固地堅持撐下去、等待下去。</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="L162" s="10" t="inlineStr">
         <is>
-          <t>I'm hanging in there until the comeback.</t>
+          <t>撐到回歸為止。</t>
         </is>
       </c>
       <c r="M162" s="10" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>Hiding your fan status from people around you ("cosplaying as a normal person").</t>
+          <t>向身邊的人隱藏自己的粉絲身分，「偽裝成正常人」。</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="L163" s="10" t="inlineStr">
         <is>
-          <t>I keep my fan status hidden at work.</t>
+          <t>在公司都隱藏飯籍。</t>
         </is>
       </c>
       <c r="M163" s="10" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>Visually stunning content — "eye candy."</t>
+          <t>視覺上非常享受、賞心悅目的內容，眼福。</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="L164" s="10" t="inlineStr">
         <is>
-          <t>Today's fancam was a total feast for the eyes.</t>
+          <t>今天的直拍完全是眼福。</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>A fan whose dream — like meeting their idol — actually came true.</t>
+          <t>夢想成真的粉絲——像是真的見到偶像本人。</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="L165" s="10" t="inlineStr">
         <is>
-          <t>I finally got picked for a fansign! I'm a successful fan now.</t>
+          <t>終於抽中簽名會！我圓夢了。</t>
         </is>
       </c>
       <c r="M165" s="10" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>A genuine, dedicated fan, as opposed to a casual one.</t>
+          <t>真心投入、忠實的粉絲，相對於一般路人粉。</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="L166" s="10" t="inlineStr">
         <is>
-          <t>That person is a real, die-hard fan.</t>
+          <t>那個人真的是鐵粉。</t>
         </is>
       </c>
       <c r="M166" s="10" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>A pre-order sale for an album, held before the official release.</t>
+          <t>正式發售前開放的專輯預購。</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L167" s="10" t="inlineStr">
         <is>
-          <t>Pre-orders just opened, let's buy fast!</t>
+          <t>預購開始了，快搶！</t>
         </is>
       </c>
       <c r="M167" s="10" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>A "couple item" — matching merch that fans buy to feel paired with their bias or each other.</t>
+          <t>「情侶物品」——粉絲購買來與本命或彼此配對的周邊商品。</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="L169" s="10" t="inlineStr">
         <is>
-          <t>I got a matching couple item with my bias.</t>
+          <t>跟本命買了情侶小物。</t>
         </is>
       </c>
       <c r="M169" s="10" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>A random lucky-draw event tied to album purchases, often giving out extra photocards.</t>
+          <t>與購買專輯綁定的隨機抽獎活動，通常會抽到額外的小卡。</t>
         </is>
       </c>
       <c r="I170" s="10" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="L170" s="10" t="inlineStr">
         <is>
-          <t>I got my bias's photocard from the lucky draw!</t>
+          <t>幸運抽獎抽到本命小卡了！</t>
         </is>
       </c>
       <c r="M170" s="10" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>A paid event where fans get a brief one-on-one photo op with an idol.</t>
+          <t>付費活動，粉絲可以獲得與偶像簡短的一對一拍照機會。</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="L171" s="10" t="inlineStr">
         <is>
-          <t>I totally couldn't get a ticket to the photo event.</t>
+          <t>完全搶不到拍照會的票。</t>
         </is>
       </c>
       <c r="M171" s="10" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>Short for "sorry I couldn't protect you" — used to console over a controversy or hardship an idol faced.</t>
+          <t>「對不起沒能保護你」的簡稱——用來安慰偶像遭遇爭議或困境時的心情。</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="L172" s="10" t="inlineStr">
         <is>
-          <t>That controversy must have felt so unfair, I'm sorry we couldn't protect you.</t>
+          <t>那個爭議一定很委屈，沒能保護你QQ</t>
         </is>
       </c>
       <c r="M172" s="10" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>"Type sniped" — something that perfectly matches your personal taste.</t>
+          <t>「正中喜好」——完全符合個人品味的事物。</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="L173" s="10" t="inlineStr">
         <is>
-          <t>This concept totally hits my exact type.</t>
+          <t>這次的概念完全戳中我的點。</t>
         </is>
       </c>
       <c r="M173" s="10" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>Fan-written fiction featuring idols or characters.</t>
+          <t>粉絲創作、以偶像或角色為主角的小說，同人小說。</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="L174" s="10" t="inlineStr">
         <is>
-          <t>I cried for days because of that fanfic's ending.</t>
+          <t>那篇同人小說的結局讓我哭了好幾天。</t>
         </is>
       </c>
       <c r="M174" s="10" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>Fan-created artwork of idols or characters.</t>
+          <t>粉絲創作的偶像或角色相關畫作，同人圖。</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="L175" s="10" t="inlineStr">
         <is>
-          <t>This fanart looks exactly like them in real life.</t>
+          <t>這張同人圖跟本人一模一樣。</t>
         </is>
       </c>
       <c r="M175" s="10" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>A "belly comment" — a witty first comment posted right under an official account's post.</t>
+          <t>「肚子留言」——搶在官方帳號貼文下第一時間發的機智留言。</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="L176" s="10" t="inlineStr">
         <is>
-          <t>The belly comment was so funny I took a screenshot.</t>
+          <t>那則神留言太好笑了，我截圖了。</t>
         </is>
       </c>
       <c r="M176" s="10" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>Retweet — sharing a post to your own followers on X/Twitter.</t>
+          <t>轉推——把貼文分享給自己在X（推特）上的追蹤者。</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="L177" s="10" t="inlineStr">
         <is>
-          <t>Please retweet this tweet.</t>
+          <t>幫我轉推這則推文。</t>
         </is>
       </c>
       <c r="M177" s="10" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>Short for "like, comment, subscribe, and turn on notifications" — a common YouTube support request.</t>
+          <t>「按讚、留言、訂閱、開啟小鈴鐺」的簡稱——YouTube上常見的支持請求。</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="L178" s="10" t="inlineStr">
         <is>
-          <t>New video is up, please like, comment, subscribe, and turn on notifications!</t>
+          <t>新影片上線了，記得按讚留言訂閱開小鈴鐺！</t>
         </is>
       </c>
       <c r="M178" s="10" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>"Pilgrimage" — visiting a real-world place connected to your idol, like a filming location or hometown spot.</t>
+          <t>「朝聖」——造訪與偶像有關的實際地點，例如拍攝地或家鄉景點。</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="L179" s="10" t="inlineStr">
         <is>
-          <t>This cafe is my bias's regular spot, so I came on a pilgrimage.</t>
+          <t>這間咖啡廳是本命常去的店，所以來朝聖了。</t>
         </is>
       </c>
       <c r="M179" s="10" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>A fandom's official name, given by the agency or group (like ARMY or BLINK).</t>
+          <t>由經紀公司或團體正式賦予的粉絲圈名稱，如ARMY或BLINK。</t>
         </is>
       </c>
       <c r="I180" s="10" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="L180" s="10" t="inlineStr">
         <is>
-          <t>They announced our fandom name!</t>
+          <t>我們的粉絲名稱公布了！</t>
         </is>
       </c>
       <c r="M180" s="10" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>Short for "fans don't win the lottery" — meaning fans rarely get the lucky chance to actually meet their idol.</t>
+          <t>「粉絲不會中樂透」的簡稱——意指粉絲很難真正抽中與偶像見面的機會。</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="L181" s="10" t="inlineStr">
         <is>
-          <t>I've lost the fansign lottery over ten times, guess fans really don't win.</t>
+          <t>簽名會已經連續十次沒中了，果然粉絲很難中獎。</t>
         </is>
       </c>
       <c r="M181" s="10" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
-          <t>"Fan + coming out" — publicly revealing your fan status to people around you.</t>
+          <t>「飯圈＋出櫃」——向身邊的人公開自己的粉絲身分。</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="L182" s="10" t="inlineStr">
         <is>
-          <t>I finally came out as a fan at work.</t>
+          <t>終於在公司公開飯籍了。</t>
         </is>
       </c>
       <c r="M182" s="10" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>Short for "since you're going to be a fan anyway, be a happy one" — embracing your fandom fully.</t>
+          <t>「反正都要追星了，就開心地追」的簡稱——全心投入自己的粉絲身分。</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="L183" s="10" t="inlineStr">
         <is>
-          <t>It costs money, but might as well fan happily, right?</t>
+          <t>雖然花錢，但既然要追星就要開心地追嘛。</t>
         </is>
       </c>
       <c r="M183" s="10" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>"Breath-stopping member" — a member so good-looking they take your breath away.</t>
+          <t>「讓人屏息的成員」——長相帥氣到令人屏息的成員。</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="L184" s="10" t="inlineStr">
         <is>
-          <t>Watch this fancam and you'll know who the breath-stopping member is.</t>
+          <t>看這支直拍你就知道誰是帥到讓人窒息的成員。</t>
         </is>
       </c>
       <c r="M184" s="10" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>Borrowed from Harry Potter — a non-fan, an ordinary person outside the fandom.</t>
+          <t>借用自哈利波特——非粉絲，飯圈外的一般人，麻瓜。</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="L185" s="10" t="inlineStr">
         <is>
-          <t>I played this song for my muggle friend and they liked it.</t>
+          <t>放這首歌給麻瓜朋友聽，他也很喜歡。</t>
         </is>
       </c>
       <c r="M185" s="10" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>"Homepage master" — a fan who takes and shares high-quality photos of an idol.</t>
+          <t>「主頁站長」——拍攝並分享偶像高畫質照片的粉絲攝影師，站姊。</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="L186" s="10" t="inlineStr">
         <is>
-          <t>This fancam was shot by a well-known fan photographer.</t>
+          <t>這支直拍是知名站姊拍的。</t>
         </is>
       </c>
       <c r="M186" s="10" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>"Migratory bird" — a fan who fickle-hops between different idols or groups following trends.</t>
+          <t>「候鳥」——追隨潮流在不同偶像或團體間搖擺不定的粉絲，牆頭草。</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="L187" s="10" t="inlineStr">
         <is>
-          <t>That fan hops fandoms so much I don't trust their loyalty.</t>
+          <t>那個人是牆頭草粉絲，讓人不太放心。</t>
         </is>
       </c>
       <c r="M187" s="10" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>"Fandom mate" — a friend you share your fan activities with.</t>
+          <t>「飯圈夥伴」——一起分享追星活動的朋友，飯友。</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="L188" s="10" t="inlineStr">
         <is>
-          <t>I went to the concert with my fandom mate.</t>
+          <t>跟飯友一起去了演唱會。</t>
         </is>
       </c>
       <c r="M188" s="10" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>A fan who follows and supports many different groups or idols at once, rather than just one.</t>
+          <t>同時支持、追隨多個團體或偶像的粉絲，而非只追一個，雜食飯。</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="L189" s="10" t="inlineStr">
         <is>
-          <t>I'm a multi-fandom fan so I have several biases.</t>
+          <t>我是雜食粉絲，本命有好幾個。</t>
         </is>
       </c>
       <c r="M189" s="10" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>Short for "individual fan" — a fan who supports one specific member rather than the group as a whole.</t>
+          <t>「個人粉絲」的簡稱——支持團體中特定一位成員、而非整個團體的粉絲。</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="L190" s="10" t="inlineStr">
         <is>
-          <t>I'm more of an individual-member fan than a group fan.</t>
+          <t>比起團飯，我更偏向個人飯。</t>
         </is>
       </c>
       <c r="M190" s="10" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>A toxic individual-member fan who favors one member while badmouthing the others in the group.</t>
+          <t>偏袒某一位成員、同時貶低其他成員的毒性個人粉絲，毒唯。</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="L191" s="10" t="inlineStr">
         <is>
-          <t>The group's image got hurt because of toxic solo-stans.</t>
+          <t>因為毒唯，團體形象受損了。</t>
         </is>
       </c>
       <c r="M191" s="10" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>Someone who buys concert or event tickets and resells them at a marked-up price.</t>
+          <t>購買演唱會或活動門票後加價轉賣的人，黃牛。</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="L192" s="10" t="inlineStr">
         <is>
-          <t>Scalpers tripled the ticket price.</t>
+          <t>因為黃牛，票價漲了三倍。</t>
         </is>
       </c>
       <c r="M192" s="10" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>"Cannon" — the large professional telephoto camera lens fan photographers use to shoot idols from a distance.</t>
+          <t>「大砲」——粉絲攝影師用來遠距離拍攝偶像的大型專業長焦鏡頭。</t>
         </is>
       </c>
       <c r="I193" s="10" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="L193" s="10" t="inlineStr">
         <is>
-          <t>That fan photographer's telephoto lens is huge.</t>
+          <t>那個站姊的大砲鏡頭真的很大。</t>
         </is>
       </c>
       <c r="M193" s="10" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>The set of organized chants and calls fans shout together during a song at concerts.</t>
+          <t>演唱會上粉絲們配合歌曲一起喊出的固定應援口號組合。</t>
         </is>
       </c>
       <c r="I194" s="10" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="L194" s="10" t="inlineStr">
         <is>
-          <t>I memorized all the fan chants for this song.</t>
+          <t>這首歌的應援口號我全都背下來了。</t>
         </is>
       </c>
       <c r="M194" s="10" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="H195" s="10" t="inlineStr">
         <is>
-          <t>The whole audience singing loudly together at a concert.</t>
+          <t>演唱會全場觀眾一起大聲合唱。</t>
         </is>
       </c>
       <c r="I195" s="10" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="L195" s="10" t="inlineStr">
         <is>
-          <t>Hearing the crowd singalong gave me chills.</t>
+          <t>聽到全場大合唱起雞皮疙瘩。</t>
         </is>
       </c>
       <c r="M195" s="10" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>A fan social media account made specifically for chatting and connecting with other fans.</t>
+          <t>粉絲專門用來與其他粉絲聊天、互動的社群帳號。</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="L196" s="10" t="inlineStr">
         <is>
-          <t>I made an interaction account to find fandom mates.</t>
+          <t>開了互動帳號在找飯友。</t>
         </is>
       </c>
       <c r="M196" s="10" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>A fan social media account dedicated to sharing news and updates, rather than casual chat.</t>
+          <t>專門分享消息、更新資訊、而非閒聊互動的粉絲社群帳號。</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="L197" s="10" t="inlineStr">
         <is>
-          <t>If you follow an info account, you'll never miss a schedule update.</t>
+          <t>追蹤情報帳號就不會錯過行程。</t>
         </is>
       </c>
       <c r="M197" s="10" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>A screenshot posted to prove you streamed a song, often shared during a total-effort campaign.</t>
+          <t>為證明自己有刷榜串流而張貼的截圖，常見於總攻活動期間。</t>
         </is>
       </c>
       <c r="I198" s="10" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L198" s="10" t="inlineStr">
         <is>
-          <t>I posted my streaming proof, please check it.</t>
+          <t>我發了刷榜證明，麻煩確認一下。</t>
         </is>
       </c>
       <c r="M198" s="10" t="inlineStr">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>An announcement post organizing a fandom-wide coordinated streaming or voting push.</t>
+          <t>號召粉絲圈一起進行協同刷榜或投票行動的公告貼文。</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="L199" s="10" t="inlineStr">
         <is>
-          <t>The coordinated-push notice is up, everyone please join in.</t>
+          <t>總攻公告出來了，大家一起參與！</t>
         </is>
       </c>
       <c r="M199" s="10" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>The yearly anniversary of a group's official debut date.</t>
+          <t>團體正式出道日期的年度紀念日。</t>
         </is>
       </c>
       <c r="I200" s="10" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="L200" s="10" t="inlineStr">
         <is>
-          <t>There's an event today for their debut anniversary.</t>
+          <t>今天是出道紀念日，辦了活動。</t>
         </is>
       </c>
       <c r="M200" s="10" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>The birthday of one's ultimate bias, often celebrated with fan projects.</t>
+          <t>本命偶像的生日，常會舉辦粉絲應援活動慶祝。</t>
         </is>
       </c>
       <c r="I201" s="10" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="L201" s="10" t="inlineStr">
         <is>
-          <t>I already booked tickets for the birthday cafe event for my bias.</t>
+          <t>已經預約了本命生日咖啡廳活動。</t>
         </is>
       </c>
       <c r="M201" s="10" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>A fan-funded project — like subway ads or coffee trucks — done to celebrate or support an idol.</t>
+          <t>粉絲集資進行的應援企劃，例如地鐵廣告或咖啡車，用來慶祝或支持偶像。</t>
         </is>
       </c>
       <c r="I202" s="10" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="L202" s="10" t="inlineStr">
         <is>
-          <t>I heard a support ad went up in the subway station!</t>
+          <t>聽說地鐵站掛了應援廣告！</t>
         </is>
       </c>
       <c r="M202" s="10" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>Voting done by fans to help an artist win an award or chart position.</t>
+          <t>粉絲進行投票，幫助藝人贏得獎項或排行榜名次。</t>
         </is>
       </c>
       <c r="I203" s="10" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="L203" s="10" t="inlineStr">
         <is>
-          <t>Fan voting closes soon, vote quickly!</t>
+          <t>粉絲投票快截止了，快去投票！</t>
         </is>
       </c>
       <c r="M203" s="10" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>Short for "watching directly" — attending and watching a performance or event live, in person.</t>
+          <t>「直接觀看」的簡稱——親自到現場觀看演出或活動。</t>
         </is>
       </c>
       <c r="I204" s="10" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="L204" s="10" t="inlineStr">
         <is>
-          <t>I successfully got to see this concert live!</t>
+          <t>這次演唱會成功現場觀看了！</t>
         </is>
       </c>
       <c r="M204" s="10" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>Attending and watching a concert in person, as opposed to via livestream.</t>
+          <t>親自到現場觀看演唱會，而非透過線上直播。</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="L205" s="10" t="inlineStr">
         <is>
-          <t>I finally got a ticket to watch the concert live!</t>
+          <t>終於搶到演唱會現場觀看的票了！</t>
         </is>
       </c>
       <c r="M205" s="10" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>Attending multiple rounds/performances of the same concert or musical run.</t>
+          <t>觀看同一場巡演或音樂劇的多個場次。</t>
         </is>
       </c>
       <c r="I206" s="10" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="L206" s="10" t="inlineStr">
         <is>
-          <t>I'm planning to catch multiple shows on this tour.</t>
+          <t>這次巡演打算看多場次。</t>
         </is>
       </c>
       <c r="M206" s="10" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>A handwritten letter fans write to their idol, often sent through the agency or at events.</t>
+          <t>粉絲親手寫給偶像的信，通常透過經紀公司或活動遞送。</t>
         </is>
       </c>
       <c r="I207" s="10" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="L207" s="10" t="inlineStr">
         <is>
-          <t>It took me three hours to write my fan letter.</t>
+          <t>寫粉絲信花了三小時。</t>
         </is>
       </c>
       <c r="M207" s="10" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>A spreadsheet or guide fans share to coordinate what and how to stream during a campaign.</t>
+          <t>粉絲們分享用來協調刷榜活動內容與方式的表格或指南。</t>
         </is>
       </c>
       <c r="I208" s="10" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="L208" s="10" t="inlineStr">
         <is>
-          <t>I followed the streaming guide sheet exactly.</t>
+          <t>照著刷榜指南表做了。</t>
         </is>
       </c>
       <c r="M208" s="10" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="H209" s="10" t="inlineStr">
         <is>
-          <t>A photo taken as proof of something, like a purchase, attendance, or completed task.</t>
+          <t>拍下作為證明的照片，例如購買紀錄、出席證明或完成任務。</t>
         </is>
       </c>
       <c r="I209" s="10" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="L209" s="10" t="inlineStr">
         <is>
-          <t>I posted my proof photo of the album.</t>
+          <t>上傳了專輯認證照。</t>
         </is>
       </c>
       <c r="M209" s="10" t="inlineStr">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>"Album crushing" — opening many copies of an album at once to sort and collect photocards.</t>
+          <t>「拆專輯」——一次拆開大量專輯以整理、收集小卡。</t>
         </is>
       </c>
       <c r="I210" s="10" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="L210" s="10" t="inlineStr">
         <is>
-          <t>Ripping open all my albums took three hours.</t>
+          <t>拆專花了三小時。</t>
         </is>
       </c>
       <c r="M210" s="10" t="inlineStr">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>The process of reserving tickets for a concert.</t>
+          <t>預訂演唱會門票的過程。</t>
         </is>
       </c>
       <c r="I211" s="10" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="L211" s="10" t="inlineStr">
         <is>
-          <t>Did you manage to book concert tickets?</t>
+          <t>演唱會訂票成功了嗎？</t>
         </is>
       </c>
       <c r="M211" s="10" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>"Ticketing" — the fiercely competitive process of buying tickets online the moment they go on sale.</t>
+          <t>「搶票」——門票開賣瞬間激烈競爭搶購的過程。</t>
         </is>
       </c>
       <c r="I212" s="10" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="L212" s="10" t="inlineStr">
         <is>
-          <t>I failed at ticketing, it sold out.</t>
+          <t>搶票失敗，已經賣完了。</t>
         </is>
       </c>
       <c r="M212" s="10" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>"Blood + ticketing" — an extremely fierce, high-stakes ticketing battle for a hugely popular event.</t>
+          <t>「血＋搶票」——形容超級熱門活動搶票競爭極度激烈、猶如血戰。</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="L213" s="10" t="inlineStr">
         <is>
-          <t>This concert's ticketing was a total bloodbath.</t>
+          <t>這次演唱會根本是血戰搶票。</t>
         </is>
       </c>
       <c r="M213" s="10" t="inlineStr">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>"Insane clicking" — clicking as fast and repeatedly as possible to win a ticketing race.</t>
+          <t>「瘋狂點擊」——在搶票時盡可能快速反覆點擊。</t>
         </is>
       </c>
       <c r="I214" s="10" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="L214" s="10" t="inlineStr">
         <is>
-          <t>I clicked like crazy but it still all sold out.</t>
+          <t>瘋狂點擊了還是全部賣完了。</t>
         </is>
       </c>
       <c r="M214" s="10" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>A virtual waiting line on a ticketing site before you can access the purchase page.</t>
+          <t>進入購票頁面前的線上虛擬排隊隊伍。</t>
         </is>
       </c>
       <c r="I215" s="10" t="inlineStr">
@@ -17276,7 +17276,7 @@
       </c>
       <c r="L215" s="10" t="inlineStr">
         <is>
-          <t>There were 30,000 people in the waiting queue.</t>
+          <t>等候佇列有三萬人。</t>
         </is>
       </c>
       <c r="M215" s="10" t="inlineStr">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="H216" s="10" t="inlineStr">
         <is>
-          <t>"Fan heart" — a fan's devoted feelings and loyalty toward their idol.</t>
+          <t>「粉絲之心」——粉絲對偶像投入的忠誠與情感，飯魂。</t>
         </is>
       </c>
       <c r="I216" s="10" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="L216" s="10" t="inlineStr">
         <is>
-          <t>At this point, you have to admit that's real fan devotion.</t>
+          <t>這樣的話一定要承認這是真愛飯魂。</t>
         </is>
       </c>
       <c r="M216" s="10" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="H217" s="10" t="inlineStr">
         <is>
-          <t>Idol behaviors — like winks, hearts, or greetings — specifically meant to please fans.</t>
+          <t>偶像特地為取悅粉絲而做出的行為，如眨眼、比愛心或打招呼。</t>
         </is>
       </c>
       <c r="I217" s="10" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="L217" s="10" t="inlineStr">
         <is>
-          <t>Their fan service was really great.</t>
+          <t>粉絲福利真的很棒。</t>
         </is>
       </c>
       <c r="M217" s="10" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>A website run by fans dedicated to an idol or group.</t>
+          <t>粉絲自行架設、專門介紹偶像或團體的網站。</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="L218" s="10" t="inlineStr">
         <is>
-          <t>This fan site has a ton of material.</t>
+          <t>這個粉絲網站資料真的很多。</t>
         </is>
       </c>
       <c r="M218" s="10" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>An organized fan account, often on X/Twitter, that runs projects and campaigns for a group.</t>
+          <t>有組織地經營應援企劃與活動的粉絲帳號，常見於X（推特）。</t>
         </is>
       </c>
       <c r="I219" s="10" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="L219" s="10" t="inlineStr">
         <is>
-          <t>The fanbase account posted a coordinated-push notice.</t>
+          <t>應援站發布了總攻公告。</t>
         </is>
       </c>
       <c r="M219" s="10" t="inlineStr">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>"Domestic half" — the portion of a fandom based within Korea, as opposed to overseas.</t>
+          <t>「國內組」——粉絲圈中位於韓國國內的部分，相對於海外組。</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="L220" s="10" t="inlineStr">
         <is>
-          <t>The domestic and overseas fandoms are reacting differently.</t>
+          <t>國內飯跟海外飯反應不太一樣。</t>
         </is>
       </c>
       <c r="M220" s="10" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>"Overseas half" — the portion of a fandom based outside Korea.</t>
+          <t>「海外組」——粉絲圈中位於韓國以外地區的部分。</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="L221" s="10" t="inlineStr">
         <is>
-          <t>The overseas fandom streams really hard.</t>
+          <t>海外飯刷榜真的很認真。</t>
         </is>
       </c>
       <c r="M221" s="10" t="inlineStr">
@@ -17795,7 +17795,7 @@
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>Short for "spoiler" — revealing plot details before others have seen them.</t>
+          <t>「劇透」的簡稱——在其他人看之前先透露劇情細節。</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="L222" s="10" t="inlineStr">
         <is>
-          <t>Don't spoil it, I haven't watched yet!</t>
+          <t>別劇透，我還沒看！</t>
         </is>
       </c>
       <c r="M222" s="10" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>"No spoiler" — content or a comment guaranteed not to reveal plot details.</t>
+          <t>「無劇透」——保證不會洩漏劇情細節的內容或留言。</t>
         </is>
       </c>
       <c r="I223" s="10" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="L223" s="10" t="inlineStr">
         <is>
-          <t>I'll write the review spoiler-free.</t>
+          <t>我會寫無劇透心得。</t>
         </is>
       </c>
       <c r="M223" s="10" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>The specific video or clip that caused someone to fall into a fandom.</t>
+          <t>讓某人正式入坑成為粉絲的那支特定影片或片段。</t>
         </is>
       </c>
       <c r="I224" s="10" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="L224" s="10" t="inlineStr">
         <is>
-          <t>This is the video that made me a fan.</t>
+          <t>這就是我的入坑影片。</t>
         </is>
       </c>
       <c r="M224" s="10" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
-          <t>A tag or note warning that a post contains spoilers.</t>
+          <t>提醒貼文內含劇情透露的標記或提示。</t>
         </is>
       </c>
       <c r="I225" s="10" t="inlineStr">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="L225" s="10" t="inlineStr">
         <is>
-          <t>Spoiler warning! If you haven't watched yet, skip this.</t>
+          <t>劇透注意！還沒看的人先跳過。</t>
         </is>
       </c>
       <c r="M225" s="10" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="H226" s="10" t="inlineStr">
         <is>
-          <t>The list of songs performed during a concert.</t>
+          <t>演唱會上演出的歌曲清單。</t>
         </is>
       </c>
       <c r="I226" s="10" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="L226" s="10" t="inlineStr">
         <is>
-          <t>I heard the concert setlist leaked.</t>
+          <t>聽說演唱會歌單外流了。</t>
         </is>
       </c>
       <c r="M226" s="10" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="H227" s="10" t="inlineStr">
         <is>
-          <t>An idol's personal, everyday clothing style, as opposed to stage costumes.</t>
+          <t>偶像私下、日常穿著的個人風格，相對於舞台服裝。</t>
         </is>
       </c>
       <c r="I227" s="10" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="L227" s="10" t="inlineStr">
         <is>
-          <t>Their casual off-stage style is seriously my taste.</t>
+          <t>私服穿搭真的很對我的胃口。</t>
         </is>
       </c>
       <c r="M227" s="10" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="H228" s="10" t="inlineStr">
         <is>
-          <t>What idols wear specifically at the airport, a closely followed fan-fashion topic.</t>
+          <t>偶像在機場的穿著打扮，是粉絲密切關注的時尚話題。</t>
         </is>
       </c>
       <c r="I228" s="10" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="L228" s="10" t="inlineStr">
         <is>
-          <t>Today's airport fashion was so clean and put-together.</t>
+          <t>今天的機場穿搭超級俐落。</t>
         </is>
       </c>
       <c r="M228" s="10" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="H229" s="10" t="inlineStr">
         <is>
-          <t>A re-released version of an album with new tracks added to the original tracklist.</t>
+          <t>在原專輯曲目基礎上新增歌曲後重新發行的版本。</t>
         </is>
       </c>
       <c r="I229" s="10" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="L229" s="10" t="inlineStr">
         <is>
-          <t>The repackage added two new songs.</t>
+          <t>改版專輯裡新增了兩首歌。</t>
         </is>
       </c>
       <c r="M229" s="10" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>A one-off album release outside a group's regular album cycle, often tied to an anniversary or season.</t>
+          <t>在團體正規專輯週期之外發行的特別專輯，常配合週年或季節推出。</t>
         </is>
       </c>
       <c r="I230" s="10" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="L230" s="10" t="inlineStr">
         <is>
-          <t>I heard a special album is coming out this winter.</t>
+          <t>聽說這個冬天會出特別專輯。</t>
         </is>
       </c>
       <c r="M230" s="10" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="H231" s="10" t="inlineStr">
         <is>
-          <t>Expressing admiration or respect for someone's skill or achievement, from the English "respect."</t>
+          <t>源自英文「respect」——對某人技術或成就表達敬佩與尊重。</t>
         </is>
       </c>
       <c r="I231" s="10" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="L231" s="10" t="inlineStr">
         <is>
-          <t>That level of skill really deserves respect.</t>
+          <t>那個實力真的值得敬佩。</t>
         </is>
       </c>
       <c r="M231" s="10" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>"Life song" — a song that stands as someone's all-time favorite.</t>
+          <t>「人生歌曲」——某人心目中永遠的第一名歌曲。</t>
         </is>
       </c>
       <c r="I232" s="10" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="L232" s="10" t="inlineStr">
         <is>
-          <t>This song is truly my all-time favorite.</t>
+          <t>這首歌真的是我的人生歌曲。</t>
         </is>
       </c>
       <c r="M232" s="10" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="H233" s="10" t="inlineStr">
         <is>
-          <t>A fan's favorite song by a particular artist or from a particular album.</t>
+          <t>粉絲在特定藝人或專輯中最喜歡的一首歌。</t>
         </is>
       </c>
       <c r="I233" s="10" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="L233" s="10" t="inlineStr">
         <is>
-          <t>My favorite song from this album is this one.</t>
+          <t>這張專輯裡我最喜歡的歌就是這首。</t>
         </is>
       </c>
       <c r="M233" s="10" t="inlineStr">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>The message written on a fan banner or sign brought to a concert or event.</t>
+          <t>粉絲帶到演唱會或活動現場的應援手幅、看板上寫的文字。</t>
         </is>
       </c>
       <c r="I234" s="10" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="L234" s="10" t="inlineStr">
         <is>
-          <t>I still haven't decided what to write on my support banner.</t>
+          <t>還沒決定應援標語要寫什麼。</t>
         </is>
       </c>
       <c r="M234" s="10" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="H235" s="10" t="inlineStr">
         <is>
-          <t>A themed cafe fans rent out and decorate to celebrate an idol's birthday, often with free merch for visitors.</t>
+          <t>粉絲租下並布置成主題咖啡廳，用來慶祝偶像生日，常提供來客免費周邊。</t>
         </is>
       </c>
       <c r="I235" s="10" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="L235" s="10" t="inlineStr">
         <is>
-          <t>I went to the birthday cafe and it was so pretty.</t>
+          <t>去了生日咖啡廳，真的很漂亮。</t>
         </is>
       </c>
       <c r="M235" s="10" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="H236" s="10" t="inlineStr">
         <is>
-          <t>A photo of an idol taken by a fan, as opposed to an official promotional photo.</t>
+          <t>由粉絲拍攝的偶像照片，相對於官方宣傳照。</t>
         </is>
       </c>
       <c r="I236" s="10" t="inlineStr">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="L236" s="10" t="inlineStr">
         <is>
-          <t>Is the quality of this fan-taken photo even real?</t>
+          <t>這張粉絲拍的照片畫質也太好了吧。</t>
         </is>
       </c>
       <c r="M236" s="10" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="H237" s="10" t="inlineStr">
         <is>
-          <t>"Gallery" — an online forum board dedicated to a specific topic, idol, or group, like those on DC Inside.</t>
+          <t>「畫廊」——專門討論特定主題、偶像或團體的網路論壇板，如DC Inside的版面。</t>
         </is>
       </c>
       <c r="I237" s="10" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="L237" s="10" t="inlineStr">
         <is>
-          <t>I saw this info on the community board.</t>
+          <t>在討論版上看到這個消息。</t>
         </is>
       </c>
       <c r="M237" s="10" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="H238" s="10" t="inlineStr">
         <is>
-          <t>"Wave riding" — chaining through a series of related fan accounts, liking or following each one in turn.</t>
+          <t>「衝浪」——依序追蹤、按讚一連串相關粉絲帳號。</t>
         </is>
       </c>
       <c r="I238" s="10" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="L238" s="10" t="inlineStr">
         <is>
-          <t>I made a lot of new friends doing a follow train.</t>
+          <t>玩接力追蹤認識了很多新朋友。</t>
         </is>
       </c>
       <c r="M238" s="10" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="H239" s="10" t="inlineStr">
         <is>
-          <t>"Matching follow" — following someone back after they follow you, so you follow each other.</t>
+          <t>「互相追蹤」——回追對方，達成彼此互相追蹤的狀態。</t>
         </is>
       </c>
       <c r="I239" s="10" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="L239" s="10" t="inlineStr">
         <is>
-          <t>Let's mutual follow!</t>
+          <t>互追一下！</t>
         </is>
       </c>
       <c r="M239" s="10" t="inlineStr">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="H240" s="10" t="inlineStr">
         <is>
-          <t>A mystery merch box sold without revealing exactly which items are inside.</t>
+          <t>不事先公開內容物、隨機出貨的神秘周邊福袋。</t>
         </is>
       </c>
       <c r="I240" s="10" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="L240" s="10" t="inlineStr">
         <is>
-          <t>I got an amazing photocard pull from the lucky box!</t>
+          <t>福袋裡抽到了超讚的小卡！</t>
         </is>
       </c>
       <c r="M240" s="10" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="H241" s="10" t="inlineStr">
         <is>
-          <t>A large glossy poster of an idol, a popular type of official merch.</t>
+          <t>大尺寸的偶像光面海報，是常見的官方周邊商品之一。</t>
         </is>
       </c>
       <c r="I241" s="10" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="L241" s="10" t="inlineStr">
         <is>
-          <t>I put this poster up in my room.</t>
+          <t>把這張海報貼在房間了。</t>
         </is>
       </c>
       <c r="M241" s="10" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="H242" s="10" t="inlineStr">
         <is>
-          <t>"Life photocard" — the single best photocard someone has ever pulled, their all-time favorite.</t>
+          <t>「人生小卡」——某人此生抽到過最好的一張小卡。</t>
         </is>
       </c>
       <c r="I242" s="10" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="L242" s="10" t="inlineStr">
         <is>
-          <t>I finally pulled my best-ever photocard!</t>
+          <t>終於抽到人生小卡了！</t>
         </is>
       </c>
       <c r="M242" s="10" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="H243" s="10" t="inlineStr">
         <is>
-          <t>A thin plastic protective sleeve used to keep a photocard safe from scratches.</t>
+          <t>用來保護小卡不被刮傷的透明薄塑膠套，卡套。</t>
         </is>
       </c>
       <c r="I243" s="10" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="L243" s="10" t="inlineStr">
         <is>
-          <t>You have to put photocards straight into a sleeve.</t>
+          <t>小卡要馬上放進卡套裡。</t>
         </is>
       </c>
       <c r="M243" s="10" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="H244" s="10" t="inlineStr">
         <is>
-          <t>A rigid, hard plastic case used to protect a photocard from bending.</t>
+          <t>用來保護小卡不被折損的硬式透明塑膠夾。</t>
         </is>
       </c>
       <c r="I244" s="10" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L244" s="10" t="inlineStr">
         <is>
-          <t>I keep my precious photocards stored in toploaders.</t>
+          <t>珍貴的小卡要用硬卡夾保存。</t>
         </is>
       </c>
       <c r="M244" s="10" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="H245" s="10" t="inlineStr">
         <is>
-          <t>Buying, selling, or trading photocards with other fans, usually to complete a collection.</t>
+          <t>與其他粉絲買賣、交換小卡，通常是為了集齊收藏。</t>
         </is>
       </c>
       <c r="I245" s="10" t="inlineStr">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="L245" s="10" t="inlineStr">
         <is>
-          <t>I collected all my bias's photocards through trading.</t>
+          <t>靠小卡交易收集齊了本命的小卡。</t>
         </is>
       </c>
       <c r="M245" s="10" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="H246" s="10" t="inlineStr">
         <is>
-          <t>Short for 생일카페 (birthday cafe) — the commonly used, shortened way fans refer to it.</t>
+          <t>생일카페（生日咖啡廳）的簡稱，粉絲常用的簡短說法，生咖。</t>
         </is>
       </c>
       <c r="I246" s="10" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="L246" s="10" t="inlineStr">
         <is>
-          <t>We decided to go to the birthday cafe this weekend.</t>
+          <t>這個週末決定要去生咖。</t>
         </is>
       </c>
       <c r="M246" s="10" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="H247" s="10" t="inlineStr">
         <is>
-          <t>"Real life" — a fan's actual daily life (school, work) as distinct from their online fandom life.</t>
+          <t>「現實生活」——粉絲實際的日常生活（學業、工作），與線上追星生活相對。</t>
         </is>
       </c>
       <c r="I247" s="10" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="L247" s="10" t="inlineStr">
         <is>
-          <t>I've been so busy with real life that I couldn't keep up with fandom stuff.</t>
+          <t>最近現實生活太忙沒辦法追星。</t>
         </is>
       </c>
       <c r="M247" s="10" t="inlineStr">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="H248" s="10" t="inlineStr">
         <is>
-          <t>A branded backdrop set up at fan events for taking souvenir photos.</t>
+          <t>粉絲活動現場設置、印有品牌設計的拍照背板。</t>
         </is>
       </c>
       <c r="I248" s="10" t="inlineStr">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="L248" s="10" t="inlineStr">
         <is>
-          <t>I took a photo in front of the photo wall.</t>
+          <t>在拍照牆前拍了照。</t>
         </is>
       </c>
       <c r="M248" s="10" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="H249" s="10" t="inlineStr">
         <is>
-          <t>"High touch" — a fan event where fans briefly touch hands with idols while passing through a line.</t>
+          <t>「高觸碰」——粉絲排隊經過時與偶像短暫碰手的活動。</t>
         </is>
       </c>
       <c r="I249" s="10" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="L249" s="10" t="inlineStr">
         <is>
-          <t>The high-touch was only three seconds but I was truly happy.</t>
+          <t>雖然碰手會只有三秒，但真的很幸福。</t>
         </is>
       </c>
       <c r="M249" s="10" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H250" s="10" t="inlineStr">
         <is>
-          <t>A fan-signing event held physically in person, as opposed to over video call.</t>
+          <t>實體面對面舉行的簽名會，相對於視訊簽名會。</t>
         </is>
       </c>
       <c r="I250" s="10" t="inlineStr">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="L250" s="10" t="inlineStr">
         <is>
-          <t>I finally got selected for an in-person fan sign!</t>
+          <t>終於抽中面對面簽名會了！</t>
         </is>
       </c>
       <c r="M250" s="10" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="H251" s="10" t="inlineStr">
         <is>
-          <t>A fan-signing event conducted over video call rather than in person.</t>
+          <t>透過視訊通話進行、而非實體面對面的簽名會。</t>
         </is>
       </c>
       <c r="I251" s="10" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="L251" s="10" t="inlineStr">
         <is>
-          <t>The one minute of the video-call fan sign flew by instantly.</t>
+          <t>視訊簽名會的一分鐘瞬間就過去了。</t>
         </is>
       </c>
       <c r="M251" s="10" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="H252" s="10" t="inlineStr">
         <is>
-          <t>"Reply play" — when an idol personally responds to fan comments online, delighting fans.</t>
+          <t>「回覆遊戲」——偶像親自回覆粉絲留言，讓粉絲感到驚喜開心。</t>
         </is>
       </c>
       <c r="I252" s="10" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="L252" s="10" t="inlineStr">
         <is>
-          <t>My bias replied to comments and I've been happy all day because of it.</t>
+          <t>本命回覆了留言，讓我整天都很開心。</t>
         </is>
       </c>
       <c r="M252" s="10" t="inlineStr">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="H253" s="10" t="inlineStr">
         <is>
-          <t>"Love call" — an idol affectionately reaching out or calling out to fans during a broadcast.</t>
+          <t>「愛的呼喚」——偶像在直播中親切地呼喚、招呼粉絲。</t>
         </is>
       </c>
       <c r="I253" s="10" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="L253" s="10" t="inlineStr">
         <is>
-          <t>My heart feels like it'll burst every time they do a love call.</t>
+          <t>每次做愛的呼喚我的心都要跳出來了。</t>
         </is>
       </c>
       <c r="M253" s="10" t="inlineStr">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="H254" s="10" t="inlineStr">
         <is>
-          <t>"Picking up pics" — casually browsing and saving fan-taken photos or gifs online.</t>
+          <t>「撿圖」——隨意瀏覽並收藏粉絲拍攝的照片或動圖。</t>
         </is>
       </c>
       <c r="I254" s="10" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="L254" s="10" t="inlineStr">
         <is>
-          <t>I lost track of time just picking up photos online.</t>
+          <t>撿圖撿到忘記時間。</t>
         </is>
       </c>
       <c r="M254" s="10" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="H255" s="10" t="inlineStr">
         <is>
-          <t>"Bias time" — the moment or segment in a show or stage focused on your particular bias.</t>
+          <t>「本命時間」——節目或舞台中聚焦在自己本命身上的那個片段。</t>
         </is>
       </c>
       <c r="I255" s="10" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="L255" s="10" t="inlineStr">
         <is>
-          <t>My bias time is finally here!</t>
+          <t>終於到本命時間了！</t>
         </is>
       </c>
       <c r="M255" s="10" t="inlineStr">
@@ -20413,7 +20413,7 @@
       </c>
       <c r="H256" s="10" t="inlineStr">
         <is>
-          <t>Short for "culture loser" — someone who can't keep up with current trends and pop culture.</t>
+          <t>「文化魯蛇」的簡稱——跟不上當前潮流與流行文化的人。</t>
         </is>
       </c>
       <c r="I256" s="10" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="L256" s="10" t="inlineStr">
         <is>
-          <t>You don't know this meme either? Totally out of touch.</t>
+          <t>連這個梗都不知道？真的跟不上潮流。</t>
         </is>
       </c>
       <c r="M256" s="10" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="H257" s="10" t="inlineStr">
         <is>
-          <t>"Living-room fan" — a fan who does their fandom activities from home rather than attending events in person.</t>
+          <t>「客廳粉絲」——在家進行追星活動、較少親自到現場參加活動的粉絲。</t>
         </is>
       </c>
       <c r="I257" s="10" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="L257" s="10" t="inlineStr">
         <is>
-          <t>I'm an armchair fan, so I rarely make it to concerts.</t>
+          <t>我是居家飯，比較少去演唱會。</t>
         </is>
       </c>
       <c r="M257" s="10" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="H258" s="10" t="inlineStr">
         <is>
-          <t>The opposite of 잡덕 — a fan devoted to just one single fandom, not spread across several.</t>
+          <t>잡덕的反義詞——只專一投入單一粉絲圈、不分散心力的粉絲。</t>
         </is>
       </c>
       <c r="I258" s="10" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="L258" s="10" t="inlineStr">
         <is>
-          <t>I'm a one-fandom fan, so I don't know much about other groups.</t>
+          <t>我是專一飯，不太了解其他團體。</t>
         </is>
       </c>
       <c r="M258" s="10" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="H259" s="10" t="inlineStr">
         <is>
-          <t>A fan photographer ranked among the most popular and highest-quality in the fandom.</t>
+          <t>在粉絲圈中被公認為人氣最高、拍攝品質最好的頂級粉絲攝影師。</t>
         </is>
       </c>
       <c r="I259" s="10" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="L259" s="10" t="inlineStr">
         <is>
-          <t>I heard this photo was taken by a top-tier fan photographer.</t>
+          <t>聽說這張照片是頂級站姊拍的。</t>
         </is>
       </c>
       <c r="M259" s="10" t="inlineStr">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="H260" s="10" t="inlineStr">
         <is>
-          <t>The official color associated with a specific fandom, often used for lightsticks and merch.</t>
+          <t>與特定粉絲圈連結的官方顏色，常用於應援棒與周邊商品，應援色。</t>
         </is>
       </c>
       <c r="I260" s="10" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="L260" s="10" t="inlineStr">
         <is>
-          <t>Our fandom color is blue.</t>
+          <t>我們的應援色是藍色。</t>
         </is>
       </c>
       <c r="M260" s="10" t="inlineStr">
@@ -20798,7 +20798,7 @@
       </c>
       <c r="H261" s="10" t="inlineStr">
         <is>
-          <t>A song closely associated with a fandom's cheering and rallying at events.</t>
+          <t>與粉絲圈應援、集氣活動緊密相關的一首歌。</t>
         </is>
       </c>
       <c r="I261" s="10" t="inlineStr">
@@ -20818,7 +20818,7 @@
       </c>
       <c r="L261" s="10" t="inlineStr">
         <is>
-          <t>This song is our fandom's anthem.</t>
+          <t>這首歌是我們飯圈的應援曲。</t>
         </is>
       </c>
       <c r="M261" s="10" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="H262" s="10" t="inlineStr">
         <is>
-          <t>Someone's very first time attending a concert for a particular artist — a memorable fan milestone.</t>
+          <t>某人第一次到現場觀看特定藝人的演唱會，是難忘的追星里程碑。</t>
         </is>
       </c>
       <c r="I262" s="10" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="L262" s="10" t="inlineStr">
         <is>
-          <t>I finally went to my first concert!</t>
+          <t>終於去了初次演唱會！</t>
         </is>
       </c>
       <c r="M262" s="10" t="inlineStr">
@@ -20952,7 +20952,7 @@
       </c>
       <c r="H263" s="10" t="inlineStr">
         <is>
-          <t>"Open run" — rushing to be first in line the moment a store or pop-up opens, common in merch culture.</t>
+          <t>「開店衝刺」——店家或快閃店開門瞬間搶著排第一位，常見於周邊搶購文化。</t>
         </is>
       </c>
       <c r="I263" s="10" t="inlineStr">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="L263" s="10" t="inlineStr">
         <is>
-          <t>I won the opening rush and got all the merch!</t>
+          <t>開店搶購成功，買到全部周邊了！</t>
         </is>
       </c>
       <c r="M263" s="10" t="inlineStr">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="H264" s="10" t="inlineStr">
         <is>
-          <t>A special, limited-run version of a product, like an album or piece of merch.</t>
+          <t>數量有限、僅推出一次的特別版商品，例如專輯或周邊，限定版。</t>
         </is>
       </c>
       <c r="I264" s="10" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="L264" s="10" t="inlineStr">
         <is>
-          <t>You'll regret it if you miss this limited edition.</t>
+          <t>錯過這個限定版你會後悔的。</t>
         </is>
       </c>
       <c r="M264" s="10" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H265" s="10" t="inlineStr">
         <is>
-          <t>Short for "trading card" — another common term for a photocard.</t>
+          <t>「trading card」的簡稱——小卡的另一種常見說法。</t>
         </is>
       </c>
       <c r="I265" s="10" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="L265" s="10" t="inlineStr">
         <is>
-          <t>This trading card turned out so pretty.</t>
+          <t>這張小卡真的拍得很美。</t>
         </is>
       </c>
       <c r="M265" s="10" t="inlineStr">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="H266" s="10" t="inlineStr">
         <is>
-          <t>A bag heavily decorated on the outside with badges, plushies, and acrylic stands of a favorite character or idol.</t>
+          <t>外側掛滿最愛角色或偶像徽章、玩偶、壓克力立牌等裝飾的包包，痛包。</t>
         </is>
       </c>
       <c r="I266" s="10" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="L266" s="10" t="inlineStr">
         <is>
-          <t>It took me days to put together my character bag.</t>
+          <t>做痛包花了好幾天。</t>
         </is>
       </c>
       <c r="M266" s="10" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="H267" s="10" t="inlineStr">
         <is>
-          <t>A laughing style where fans add their bias group's consonant initials after "ㅋㅋㅋ" — started with CORTIS fans (ㄹㅌㅅ = 코르티스's initials) and spread to K-pop fandom broadly, with fans swapping in their own group's initials.</t>
+          <t>粉絲在「ㅋㅋㅋ」笑聲後面加上本命團體子音縮寫的一種笑法——源自CORTIS飯（ㄹㅌㅅ即코르티스的子音縮寫），後來擴散到整個K-pop飯圈，大家會替換成自己團體的縮寫。</t>
         </is>
       </c>
       <c r="I267" s="10" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="L267" s="10" t="inlineStr">
         <is>
-          <t>I saw that video and genuinely laughed while shouting out my bias group.</t>
+          <t>看完那支影片後真的邊喊本命團名邊笑了。</t>
         </is>
       </c>
       <c r="M267" s="10" t="inlineStr">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="H268" s="10" t="inlineStr">
         <is>
-          <t>A fandom meme where fans jokingly "dare" their bias to do something silly through fan messaging apps, and it becomes a viral fandom moment if the idol actually follows through — named after an idol who really drank mango juice on a dare.</t>
+          <t>一個粉絲圈迷因，粉絲透過應援訊息App開玩笑「試探」本命去做些無傷大雅的小事，如果偶像真的照做就會爆紅——源自一位真的因挑戰喝下芒果汁的偶像。</t>
         </is>
       </c>
       <c r="I268" s="10" t="inlineStr">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="L268" s="10" t="inlineStr">
         <is>
-          <t>What silly dare should we try this time?</t>
+          <t>這次要試探本命做什麼呢？</t>
         </is>
       </c>
       <c r="M268" s="10" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="H270" s="12" t="inlineStr">
         <is>
-          <t>A moment that feels satisfying — a comeback, a blunt truth spoken, karma landing.</t>
+          <t>讓人感到痛快的瞬間——逆襲、直言不諱的真相、因果報應降臨。</t>
         </is>
       </c>
       <c r="I270" s="12" t="inlineStr">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="L270" s="12" t="inlineStr">
         <is>
-          <t>That scene was so satisfying.</t>
+          <t>那個場面真的太爽快了。</t>
         </is>
       </c>
       <c r="M270" s="12" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="H271" s="12" t="inlineStr">
         <is>
-          <t>A stifling, frustrating feeling — the opposite of 사이다 — like a sweet potato stuck in your throat.</t>
+          <t>令人憋屈、鬱悶的感覺，跟사이다相反，像喉嚨卡了一顆地瓜。</t>
         </is>
       </c>
       <c r="I271" s="12" t="inlineStr">
@@ -21588,7 +21588,7 @@
       </c>
       <c r="L271" s="12" t="inlineStr">
         <is>
-          <t>This drama's plot is so frustrating.</t>
+          <t>這部劇的劇情發展也太讓人鬱悶了。</t>
         </is>
       </c>
       <c r="M271" s="12" t="inlineStr">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="H272" s="12" t="inlineStr">
         <is>
-          <t>Describes an unforgettable, iconic moment.</t>
+          <t>形容令人難忘、經典的瞬間，傳奇。</t>
         </is>
       </c>
       <c r="I272" s="12" t="inlineStr">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="L272" s="12" t="inlineStr">
         <is>
-          <t>This stage will go down as legendary.</t>
+          <t>這個舞台會被稱為傳奇留下來。</t>
         </is>
       </c>
       <c r="M272" s="12" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="H273" s="12" t="inlineStr">
         <is>
-          <t>A challenge or game where the outcome depends purely on luck.</t>
+          <t>結果完全取決於運氣的挑戰或遊戲。</t>
         </is>
       </c>
       <c r="I273" s="12" t="inlineStr">
@@ -21742,7 +21742,7 @@
       </c>
       <c r="L273" s="12" t="inlineStr">
         <is>
-          <t>I totally lost at today's luck-based game.</t>
+          <t>今天全憑運氣的遊戲完全輸了。</t>
         </is>
       </c>
       <c r="M273" s="12" t="inlineStr">
@@ -21799,7 +21799,7 @@
       </c>
       <c r="H274" s="12" t="inlineStr">
         <is>
-          <t>An emphatic way of saying "none at all."</t>
+          <t>強調「完全沒有」的誇張說法。</t>
         </is>
       </c>
       <c r="I274" s="12" t="inlineStr">
@@ -21819,7 +21819,7 @@
       </c>
       <c r="L274" s="12" t="inlineStr">
         <is>
-          <t>I have zero interest, not even a bit.</t>
+          <t>一點興趣都沒有。</t>
         </is>
       </c>
       <c r="M274" s="12" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="H275" s="12" t="inlineStr">
         <is>
-          <t>Literally "eyes moist" — describes something pitiful or embarrassing.</t>
+          <t>字面意思是「眼睛濕了」——形容可憐或尷尬的事，淚目。</t>
         </is>
       </c>
       <c r="I275" s="12" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="L275" s="12" t="inlineStr">
         <is>
-          <t>That mistake was really cringe-worthy.</t>
+          <t>那個失誤真的讓人淚目。</t>
         </is>
       </c>
       <c r="M275" s="12" t="inlineStr">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="H276" s="12" t="inlineStr">
         <is>
-          <t>An embarrassing past moment you'd rather forget.</t>
+          <t>令人想遺忘的尷尬過去，黑歷史。</t>
         </is>
       </c>
       <c r="I276" s="12" t="inlineStr">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="L276" s="12" t="inlineStr">
         <is>
-          <t>That hairstyle is a total black-history moment for me.</t>
+          <t>那個髮型完全是我的黑歷史。</t>
         </is>
       </c>
       <c r="M276" s="12" t="inlineStr">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="H277" s="12" t="inlineStr">
         <is>
-          <t>On-screen text used for emphasis or humor on broadcasts.</t>
+          <t>廣播節目中為強調或製造笑點而加的螢幕文字，字幕。</t>
         </is>
       </c>
       <c r="I277" s="12" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="L277" s="12" t="inlineStr">
         <is>
-          <t>The caption humor is really funny.</t>
+          <t>字幕的幽默感真的很好笑。</t>
         </is>
       </c>
       <c r="M277" s="12" t="inlineStr">
@@ -22107,7 +22107,7 @@
       </c>
       <c r="H278" s="12" t="inlineStr">
         <is>
-          <t>The natural rapport between cast members or co-stars.</t>
+          <t>演員或共演者之間自然流露的默契與化學反應。</t>
         </is>
       </c>
       <c r="I278" s="12" t="inlineStr">
@@ -22127,7 +22127,7 @@
       </c>
       <c r="L278" s="12" t="inlineStr">
         <is>
-          <t>Those two have such great chemistry.</t>
+          <t>那兩個人默契真的很好。</t>
         </is>
       </c>
       <c r="M278" s="12" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="H279" s="12" t="inlineStr">
         <is>
-          <t>A natural sense of humor and timing suited for variety shows.</t>
+          <t>適合綜藝節目、天生的幽默感與節奏感，綜藝感。</t>
         </is>
       </c>
       <c r="I279" s="12" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="L279" s="12" t="inlineStr">
         <is>
-          <t>That idol has really outstanding comedic talent.</t>
+          <t>那個偶像綜藝感真的很出色。</t>
         </is>
       </c>
       <c r="M279" s="12" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="H280" s="12" t="inlineStr">
         <is>
-          <t>A "national rule" — a universally understood standard or default choice.</t>
+          <t>「國民規則」——大家普遍認同的標準做法或預設選擇。</t>
         </is>
       </c>
       <c r="I280" s="12" t="inlineStr">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="L280" s="12" t="inlineStr">
         <is>
-          <t>Coke with fried chicken is just the unspoken rule.</t>
+          <t>炸雞配可樂是全民共識。</t>
         </is>
       </c>
       <c r="M280" s="12" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="H281" s="12" t="inlineStr">
         <is>
-          <t>Hints or content dropped to build hype or speculation.</t>
+          <t>為炒熱話題或引發揣測而釋出的線索或內容，爆料。</t>
         </is>
       </c>
       <c r="I281" s="12" t="inlineStr">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="L281" s="12" t="inlineStr">
         <is>
-          <t>New teaser content dropped, did everyone see it?</t>
+          <t>新的爆料出來了，大家都看了嗎？</t>
         </is>
       </c>
       <c r="M281" s="12" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="H282" s="12" t="inlineStr">
         <is>
-          <t>Short for "suddenly the mood turns cold" — an abrupt awkward moment.</t>
+          <t>「氣氛突然變冷」的簡稱——突如其來的尷尬瞬間。</t>
         </is>
       </c>
       <c r="I282" s="12" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="L282" s="12" t="inlineStr">
         <is>
-          <t>That one joke made things suddenly awkward.</t>
+          <t>因為那句玩笑瞬間冷場了。</t>
         </is>
       </c>
       <c r="M282" s="12" t="inlineStr">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="H283" s="12" t="inlineStr">
         <is>
-          <t>"No fun" — describes something boring or unentertaining.</t>
+          <t>「沒有樂趣」——形容無聊、不有趣的事物。</t>
         </is>
       </c>
       <c r="I283" s="12" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="L283" s="12" t="inlineStr">
         <is>
-          <t>That variety show was totally boring.</t>
+          <t>那個綜藝完全沒意思。</t>
         </is>
       </c>
       <c r="M283" s="12" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="H284" s="12" t="inlineStr">
         <is>
-          <t>"Honey fun" — describes something extremely entertaining.</t>
+          <t>「蜂蜜般的樂趣」——形容極度好玩、有趣的事物。</t>
         </is>
       </c>
       <c r="I284" s="12" t="inlineStr">
@@ -22589,7 +22589,7 @@
       </c>
       <c r="L284" s="12" t="inlineStr">
         <is>
-          <t>This episode was so much fun.</t>
+          <t>這一集真的超好玩。</t>
         </is>
       </c>
       <c r="M284" s="12" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="H285" s="12" t="inlineStr">
         <is>
-          <t>Raw, unedited footage released as-is.</t>
+          <t>未經剪輯、原始釋出的畫面。</t>
         </is>
       </c>
       <c r="I285" s="12" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="L285" s="12" t="inlineStr">
         <is>
-          <t>The full unedited version just dropped.</t>
+          <t>未剪輯完整版上線了。</t>
         </is>
       </c>
       <c r="M285" s="12" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="H286" s="12" t="inlineStr">
         <is>
-          <t>Captions a content creator or fan adds themselves, separate from official broadcast subtitles.</t>
+          <t>創作者或粉絲自行加上的字幕，有別於官方字幕。</t>
         </is>
       </c>
       <c r="I286" s="12" t="inlineStr">
@@ -22743,7 +22743,7 @@
       </c>
       <c r="L286" s="12" t="inlineStr">
         <is>
-          <t>The fan-made captions on this clip have great comedic timing.</t>
+          <t>這支影片的自製字幕真的很有梗。</t>
         </is>
       </c>
       <c r="M286" s="12" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="H287" s="12" t="inlineStr">
         <is>
-          <t>A funny reaction image or meme picture shared in comments and chats.</t>
+          <t>在留言或聊天中分享的搞笑反應圖或迷因圖。</t>
         </is>
       </c>
       <c r="I287" s="12" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="L287" s="12" t="inlineStr">
         <is>
-          <t>This reaction image is exactly the situation.</t>
+          <t>這張迷因圖完全就是這個情況。</t>
         </is>
       </c>
       <c r="M287" s="12" t="inlineStr">
@@ -22877,7 +22877,7 @@
       </c>
       <c r="H288" s="12" t="inlineStr">
         <is>
-          <t>A "moving picture" — a short looping GIF.</t>
+          <t>「動態圖片」——短篇循環播放的GIF動圖。</t>
         </is>
       </c>
       <c r="I288" s="12" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="L288" s="12" t="inlineStr">
         <is>
-          <t>I've lost count of how many times I've replayed this GIF.</t>
+          <t>這張動圖不知道重播了幾次。</t>
         </is>
       </c>
       <c r="M288" s="12" t="inlineStr">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="H289" s="12" t="inlineStr">
         <is>
-          <t>A joke or running bit that's been dragged on for far too long.</t>
+          <t>拖得太久、玩過頭的梗或橋段。</t>
         </is>
       </c>
       <c r="I289" s="12" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="L289" s="12" t="inlineStr">
         <is>
-          <t>That joke has gone on way too long now, stop.</t>
+          <t>那個梗已經玩過頭了，該停了。</t>
         </is>
       </c>
       <c r="M289" s="12" t="inlineStr">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="H290" s="12" t="inlineStr">
         <is>
-          <t>"Max level" — the highest possible level of skill or mastery (from gaming).</t>
+          <t>「滿等」——某項技能或熟練度達到最高等級，源自遊戲用語。</t>
         </is>
       </c>
       <c r="I290" s="12" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L290" s="12" t="inlineStr">
         <is>
-          <t>That person's editing skills are maxed out.</t>
+          <t>那個人剪片實力已經滿級了。</t>
         </is>
       </c>
       <c r="M290" s="12" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="H291" s="12" t="inlineStr">
         <is>
-          <t>To cringe — feel secondhand embarrassment.</t>
+          <t>感到尷尬、渾身不自在，尷尬癌發作。</t>
         </is>
       </c>
       <c r="I291" s="12" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="L291" s="12" t="inlineStr">
         <is>
-          <t>That line was seriously cringe.</t>
+          <t>那句台詞真的尷尬癌發作。</t>
         </is>
       </c>
       <c r="M291" s="12" t="inlineStr">
@@ -23185,7 +23185,7 @@
       </c>
       <c r="H292" s="12" t="inlineStr">
         <is>
-          <t>"The abyss" — used when someone's reputation or career crashes badly.</t>
+          <t>「深淵」——用於某人的名聲或事業急劇崩壞時。</t>
         </is>
       </c>
       <c r="I292" s="12" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="L292" s="12" t="inlineStr">
         <is>
-          <t>I heard their career went straight to the abyss because of that comment.</t>
+          <t>聽說因為那句發言人氣一落千丈。</t>
         </is>
       </c>
       <c r="M292" s="12" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="H293" s="12" t="inlineStr">
         <is>
-          <t>To suddenly skyrocket in popularity, views, or value.</t>
+          <t>人氣、觀看數或價值突然暴漲。</t>
         </is>
       </c>
       <c r="I293" s="12" t="inlineStr">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="L293" s="12" t="inlineStr">
         <is>
-          <t>This video's views totally skyrocketed.</t>
+          <t>這支影片觀看數完全暴漲。</t>
         </is>
       </c>
       <c r="M293" s="12" t="inlineStr">
@@ -23339,7 +23339,7 @@
       </c>
       <c r="H294" s="12" t="inlineStr">
         <is>
-          <t>To suddenly plummet in popularity, views, or value — the opposite of 떡상.</t>
+          <t>人氣、觀看數或價值突然暴跌，떡상的反義詞。</t>
         </is>
       </c>
       <c r="I294" s="12" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="L294" s="12" t="inlineStr">
         <is>
-          <t>Their popularity plummeted after that meme.</t>
+          <t>那個迷因之後人氣暴跌。</t>
         </is>
       </c>
       <c r="M294" s="12" t="inlineStr">
@@ -23416,7 +23416,7 @@
       </c>
       <c r="H295" s="12" t="inlineStr">
         <is>
-          <t>"Aggro" (from gaming) — attention-baiting or provocative behavior meant to draw reactions.</t>
+          <t>源自遊戲用語「aggro」——刻意引戰或博取關注的挑釁行為。</t>
         </is>
       </c>
       <c r="I295" s="12" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="L295" s="12" t="inlineStr">
         <is>
-          <t>That title is total ragebait.</t>
+          <t>那個標題完全是在博關注。</t>
         </is>
       </c>
       <c r="M295" s="12" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="H296" s="12" t="inlineStr">
         <is>
-          <t>"Eating broadcast" — a video of someone eating, often a large quantity, for viewers.</t>
+          <t>「吃的直播」——記錄某人吃東西（常是大量）供觀眾觀看的影片，吃播。</t>
         </is>
       </c>
       <c r="I296" s="12" t="inlineStr">
@@ -23513,7 +23513,7 @@
       </c>
       <c r="L296" s="12" t="inlineStr">
         <is>
-          <t>I get vicarious satisfaction watching that person's mukbang.</t>
+          <t>看那個人的吃播獲得替代性滿足。</t>
         </is>
       </c>
       <c r="M296" s="12" t="inlineStr">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="H297" s="12" t="inlineStr">
         <is>
-          <t>A reality format that follows a cast member's daily life with minimal scripted intervention.</t>
+          <t>以最少劇本介入、跟拍藝人日常生活的實境綜藝形式。</t>
         </is>
       </c>
       <c r="I297" s="12" t="inlineStr">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="L297" s="12" t="inlineStr">
         <is>
-          <t>Observational variety shows are the trend right now.</t>
+          <t>最近觀察類綜藝是主流。</t>
         </is>
       </c>
       <c r="M297" s="12" t="inlineStr">
@@ -23647,7 +23647,7 @@
       </c>
       <c r="H298" s="12" t="inlineStr">
         <is>
-          <t>"Sub-character" — an alter-ego persona a celebrity performs as, separate from their main identity.</t>
+          <t>「副角色」——藝人塑造、與本人身分分開的另一個人設。</t>
         </is>
       </c>
       <c r="I298" s="12" t="inlineStr">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="L298" s="12" t="inlineStr">
         <is>
-          <t>This character is that actor's alter ego.</t>
+          <t>這個角色是那個藝人的副角色人設。</t>
         </is>
       </c>
       <c r="M298" s="12" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="H299" s="12" t="inlineStr">
         <is>
-          <t>"Main character" — a person's original identity, as opposed to their 부캐 (alter ego).</t>
+          <t>「本角色」——一個人原本的身分，相對於부캐（副角色）而言。</t>
         </is>
       </c>
       <c r="I299" s="12" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="L299" s="12" t="inlineStr">
         <is>
-          <t>They said it felt weird going back to their main persona.</t>
+          <t>聽說回歸本尊人設覺得很不自在。</t>
         </is>
       </c>
       <c r="M299" s="12" t="inlineStr">
@@ -23801,7 +23801,7 @@
       </c>
       <c r="H300" s="12" t="inlineStr">
         <is>
-          <t>"Real variety" — a semi-scripted variety format built around cast members' real reactions.</t>
+          <t>「真實綜藝」——圍繞出演者真實反應、半劇本形式的綜藝節目。</t>
         </is>
       </c>
       <c r="I300" s="12" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="L300" s="12" t="inlineStr">
         <is>
-          <t>Old-school real variety shows used to be so much fun.</t>
+          <t>以前的真人實境綜藝真的很好看。</t>
         </is>
       </c>
       <c r="M300" s="12" t="inlineStr">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="H301" s="12" t="inlineStr">
         <is>
-          <t>"Healing variety" — a slow-paced, low-stress variety show format meant to feel relaxing.</t>
+          <t>「療癒綜藝」——節奏緩慢、低壓力、讓人放鬆的綜藝節目形式。</t>
         </is>
       </c>
       <c r="I301" s="12" t="inlineStr">
@@ -23898,7 +23898,7 @@
       </c>
       <c r="L301" s="12" t="inlineStr">
         <is>
-          <t>Lately I only end up watching healing variety shows.</t>
+          <t>最近只想看療癒系綜藝。</t>
         </is>
       </c>
       <c r="M301" s="12" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="H302" s="12" t="inlineStr">
         <is>
-          <t>"Eating champion" — someone known for eating huge amounts of food on camera.</t>
+          <t>「大胃王」——以在鏡頭前吃下大量食物聞名的人。</t>
         </is>
       </c>
       <c r="I302" s="12" t="inlineStr">
@@ -23975,7 +23975,7 @@
       </c>
       <c r="L302" s="12" t="inlineStr">
         <is>
-          <t>That person is famous as the eating champion of variety shows.</t>
+          <t>那個人是綜藝圈公認的大胃王。</t>
         </is>
       </c>
       <c r="M302" s="12" t="inlineStr">
@@ -24032,7 +24032,7 @@
       </c>
       <c r="H303" s="12" t="inlineStr">
         <is>
-          <t>"Body gag" — slapstick, physical comedy performed for laughs.</t>
+          <t>「肢體笑料」——透過肢體動作表演的搞笑橋段。</t>
         </is>
       </c>
       <c r="I303" s="12" t="inlineStr">
@@ -24052,7 +24052,7 @@
       </c>
       <c r="L303" s="12" t="inlineStr">
         <is>
-          <t>That comedian is famous for physical comedy.</t>
+          <t>那個諧星以肢體笑料聞名。</t>
         </is>
       </c>
       <c r="M303" s="12" t="inlineStr">
@@ -24109,7 +24109,7 @@
       </c>
       <c r="H304" s="12" t="inlineStr">
         <is>
-          <t>An unscripted, improvised line or reaction during a broadcast.</t>
+          <t>廣播節目中未經排練、臨場即興的台詞或反應。</t>
         </is>
       </c>
       <c r="I304" s="12" t="inlineStr">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="L304" s="12" t="inlineStr">
         <is>
-          <t>That ad-lib was hilarious.</t>
+          <t>那段即興演出真的太好笑了。</t>
         </is>
       </c>
       <c r="M304" s="12" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="H305" s="12" t="inlineStr">
         <is>
-          <t>A short comedy sketch performed on a variety or comedy show.</t>
+          <t>綜藝或喜劇節目中演出的短篇喜劇小品。</t>
         </is>
       </c>
       <c r="I305" s="12" t="inlineStr">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="L305" s="12" t="inlineStr">
         <is>
-          <t>This comedy skit was so fresh.</t>
+          <t>這次的短劇真的很新鮮。</t>
         </is>
       </c>
       <c r="M305" s="12" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="H306" s="12" t="inlineStr">
         <is>
-          <t>"Back advertising" — sponsored content presented as if it were an honest, unpaid review.</t>
+          <t>「幕後廣告」——把業配內容包裝成誠實、非贊助評測的爭議行為。</t>
         </is>
       </c>
       <c r="I306" s="12" t="inlineStr">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="L306" s="12" t="inlineStr">
         <is>
-          <t>That YouTuber caused a big stir with an undisclosed-sponsorship controversy.</t>
+          <t>那個YouTuber因為業配爭議鬧得沸沸揚揚。</t>
         </is>
       </c>
       <c r="M306" s="12" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="H307" s="12" t="inlineStr">
         <is>
-          <t>Eating a meal by yourself, often at a restaurant, without feeling awkward about it.</t>
+          <t>自己一個人用餐，常在餐廳，且不會感到尷尬。</t>
         </is>
       </c>
       <c r="I307" s="12" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="L307" s="12" t="inlineStr">
         <is>
-          <t>I just ate alone today.</t>
+          <t>今天就一個人吃飯了。</t>
         </is>
       </c>
       <c r="M307" s="12" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="H308" s="12" t="inlineStr">
         <is>
-          <t>Having a drink by yourself, often at a bar or at home.</t>
+          <t>自己一個人喝酒，常在酒吧或家裡。</t>
         </is>
       </c>
       <c r="I308" s="12" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="L308" s="12" t="inlineStr">
         <is>
-          <t>I had a solo drink after work.</t>
+          <t>下班後自己一個人喝了一杯。</t>
         </is>
       </c>
       <c r="M308" s="12" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="H309" s="12" t="inlineStr">
         <is>
-          <t>Enjoying leisure time or hanging out by yourself, without feeling lonely about it.</t>
+          <t>自己一個人享受休閒時光或出去玩，且不覺得孤單。</t>
         </is>
       </c>
       <c r="I309" s="12" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="L309" s="12" t="inlineStr">
         <is>
-          <t>Hanging out alone on the weekend isn't bad either.</t>
+          <t>週末一個人玩也不錯。</t>
         </is>
       </c>
       <c r="M309" s="12" t="inlineStr">
@@ -24571,7 +24571,7 @@
       </c>
       <c r="H310" s="12" t="inlineStr">
         <is>
-          <t>"Solo tribe" — people who prefer doing everyday activities like eating, shopping, or traveling alone.</t>
+          <t>「獨行族」——偏好獨自進行吃飯、購物、旅行等日常活動的人。</t>
         </is>
       </c>
       <c r="I310" s="12" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="L310" s="12" t="inlineStr">
         <is>
-          <t>There are a lot more services for solo-lifestyle people these days.</t>
+          <t>最近針對獨行族的服務變多了。</t>
         </is>
       </c>
       <c r="M310" s="12" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H311" s="12" t="inlineStr">
         <is>
-          <t>Living on your own, away from your family — a very common young-adult experience and drama setting.</t>
+          <t>離開家人獨自生活，是很常見的青年生活型態與戲劇場景設定。</t>
         </is>
       </c>
       <c r="I311" s="12" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="L311" s="12" t="inlineStr">
         <is>
-          <t>It's been a year since I started living on my own.</t>
+          <t>開始自己住已經一年了。</t>
         </is>
       </c>
       <c r="M311" s="12" t="inlineStr">
@@ -24725,7 +24725,7 @@
       </c>
       <c r="H312" s="12" t="inlineStr">
         <is>
-          <t>"Reversal charm" — an unexpected, contrasting trait that makes someone even more charming.</t>
+          <t>「反轉魅力」——出乎意料、形成反差感的特質，讓人更有魅力，反差萌。</t>
         </is>
       </c>
       <c r="I312" s="12" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="L312" s="12" t="inlineStr">
         <is>
-          <t>They seem cool but have this reversal charm of being secretly super affectionate.</t>
+          <t>看起來很酷卻意外很會撒嬌，有種反差萌。</t>
         </is>
       </c>
       <c r="M312" s="12" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="H313" s="12" t="inlineStr">
         <is>
-          <t>A live broadcast, especially one streamed directly to fans online.</t>
+          <t>直播，尤其是直接串流給粉絲觀看的形式。</t>
         </is>
       </c>
       <c r="I313" s="12" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="L313" s="12" t="inlineStr">
         <is>
-          <t>What time is today's livestream?</t>
+          <t>今天幾點開直播？</t>
         </is>
       </c>
       <c r="M313" s="12" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="H314" s="12" t="inlineStr">
         <is>
-          <t>"Defending the original broadcast" — watching a show live as it airs, rather than later.</t>
+          <t>「死守正式播出」——準時收看首播，而非之後補看。</t>
         </is>
       </c>
       <c r="I314" s="12" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="L314" s="12" t="inlineStr">
         <is>
-          <t>I absolutely have to watch this live tonight.</t>
+          <t>今天一定要準時收看。</t>
         </is>
       </c>
       <c r="M314" s="12" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="H315" s="12" t="inlineStr">
         <is>
-          <t>A repeat broadcast of a show that already aired.</t>
+          <t>已播出節目的重播。</t>
         </is>
       </c>
       <c r="I315" s="12" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="L315" s="12" t="inlineStr">
         <is>
-          <t>I watched it again through the rerun.</t>
+          <t>透過重播又看了一次。</t>
         </is>
       </c>
       <c r="M315" s="12" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="H316" s="12" t="inlineStr">
         <is>
-          <t>The percentage of TVs tuned to a broadcast — a show's audience rating.</t>
+          <t>收看該節目的電視比例，即收視率。</t>
         </is>
       </c>
       <c r="I316" s="12" t="inlineStr">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="L316" s="12" t="inlineStr">
         <is>
-          <t>This drama's viewership rating keeps climbing.</t>
+          <t>這部劇收視率持續上升。</t>
         </is>
       </c>
       <c r="M316" s="12" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="H317" s="12" t="inlineStr">
         <is>
-          <t>"Topic-ness" — how much a show, person, or moment is being talked about online and in the media.</t>
+          <t>「話題性」——一個節目、人物或瞬間在網路與媒體上被討論的程度。</t>
         </is>
       </c>
       <c r="I317" s="12" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="L317" s="12" t="inlineStr">
         <is>
-          <t>This drama's buzzworthiness is seriously huge.</t>
+          <t>這部劇的話題性真的很驚人。</t>
         </is>
       </c>
       <c r="M317" s="12" t="inlineStr">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="H318" s="12" t="inlineStr">
         <is>
-          <t>"Chemistry explosion" — incredible, undeniable on-screen chemistry between cast members.</t>
+          <t>「化學反應爆發」——演員之間展現出令人無法否認的絕佳默契。</t>
         </is>
       </c>
       <c r="I318" s="12" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="L318" s="12" t="inlineStr">
         <is>
-          <t>This couple has total chemistry explosion.</t>
+          <t>這對CP默契爆棚。</t>
         </is>
       </c>
       <c r="M318" s="12" t="inlineStr">
@@ -25264,7 +25264,7 @@
       </c>
       <c r="H319" s="12" t="inlineStr">
         <is>
-          <t>The written script for a drama, film, or show.</t>
+          <t>戲劇、電影或節目的書面劇本。</t>
         </is>
       </c>
       <c r="I319" s="12" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="L319" s="12" t="inlineStr">
         <is>
-          <t>I heard this episode's script leaked.</t>
+          <t>聽說這集劇本外流了。</t>
         </is>
       </c>
       <c r="M319" s="12" t="inlineStr">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="H320" s="12" t="inlineStr">
         <is>
-          <t>Someone's primary profession or craft, as opposed to a side activity.</t>
+          <t>一個人的主要職業或專長，相對於副業活動。</t>
         </is>
       </c>
       <c r="I320" s="12" t="inlineStr">
@@ -25361,7 +25361,7 @@
       </c>
       <c r="L320" s="12" t="inlineStr">
         <is>
-          <t>Their main career is acting, but they're great at singing too.</t>
+          <t>本業是演員，但唱歌也很厲害。</t>
         </is>
       </c>
       <c r="M320" s="12" t="inlineStr">
@@ -25418,7 +25418,7 @@
       </c>
       <c r="H321" s="12" t="inlineStr">
         <is>
-          <t>A supporting actor or role in a drama or film, as opposed to the lead.</t>
+          <t>戲劇或電影中的配角，相對於主角而言。</t>
         </is>
       </c>
       <c r="I321" s="12" t="inlineStr">
@@ -25438,7 +25438,7 @@
       </c>
       <c r="L321" s="12" t="inlineStr">
         <is>
-          <t>That supporting actor's performance is seriously good.</t>
+          <t>那位配角演技真的很好。</t>
         </is>
       </c>
       <c r="M321" s="12" t="inlineStr">
@@ -25495,7 +25495,7 @@
       </c>
       <c r="H322" s="12" t="inlineStr">
         <is>
-          <t>An overly sentimental, tearjerker style of storytelling common in older Korean dramas and films.</t>
+          <t>過度煽情、催淚的敘事風格，常見於較早期的韓國電影與戲劇。</t>
         </is>
       </c>
       <c r="I322" s="12" t="inlineStr">
@@ -25515,7 +25515,7 @@
       </c>
       <c r="L322" s="12" t="inlineStr">
         <is>
-          <t>The back half of this movie is total melodrama.</t>
+          <t>這部電影後半段完全是煽情戲碼。</t>
         </is>
       </c>
       <c r="M322" s="12" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="H323" s="12" t="inlineStr">
         <is>
-          <t>A predictable, overused plot device or trope.</t>
+          <t>可預測、被過度使用的劇情套路或橋段，老梗。</t>
         </is>
       </c>
       <c r="I323" s="12" t="inlineStr">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="L323" s="12" t="inlineStr">
         <is>
-          <t>This drama is a pile of clichés.</t>
+          <t>這部劇滿滿都是老梗。</t>
         </is>
       </c>
       <c r="M323" s="12" t="inlineStr">
@@ -25649,7 +25649,7 @@
       </c>
       <c r="H324" s="12" t="inlineStr">
         <is>
-          <t>A hint planted early in a story that sets up a later plot development.</t>
+          <t>故事前段埋下、為後續劇情發展鋪路的線索，伏筆。</t>
         </is>
       </c>
       <c r="I324" s="12" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="L324" s="12" t="inlineStr">
         <is>
-          <t>That scene was foreshadowing!</t>
+          <t>這個畫面就是伏筆！</t>
         </is>
       </c>
       <c r="M324" s="12" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="H325" s="12" t="inlineStr">
         <is>
-          <t>"Collecting the teased bait" — when a previously foreshadowed plot point finally pays off.</t>
+          <t>「回收拋出的餌」——先前埋下的伏筆最終得到回應。</t>
         </is>
       </c>
       <c r="I325" s="12" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="L325" s="12" t="inlineStr">
         <is>
-          <t>The foreshadowing finally paid off!</t>
+          <t>終於伏筆回收了！</t>
         </is>
       </c>
       <c r="M325" s="12" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H326" s="12" t="inlineStr">
         <is>
-          <t>An ending that leaves the story's resolution ambiguous or up to interpretation.</t>
+          <t>結局留下模糊空間、任觀眾自行解讀的收尾方式。</t>
         </is>
       </c>
       <c r="I326" s="12" t="inlineStr">
@@ -25823,7 +25823,7 @@
       </c>
       <c r="L326" s="12" t="inlineStr">
         <is>
-          <t>It was an open ending, so everyone's interpretation differed.</t>
+          <t>因為是開放式結局，大家解讀都不一樣。</t>
         </is>
       </c>
       <c r="M326" s="12" t="inlineStr">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="H327" s="12" t="inlineStr">
         <is>
-          <t>A story that ends unhappily or tragically.</t>
+          <t>以不幸或悲劇收場的故事結局。</t>
         </is>
       </c>
       <c r="I327" s="12" t="inlineStr">
@@ -25900,7 +25900,7 @@
       </c>
       <c r="L327" s="12" t="inlineStr">
         <is>
-          <t>I can't bring myself to watch in case it's a sad ending.</t>
+          <t>怕是悲傷結局所以不敢看。</t>
         </is>
       </c>
       <c r="M327" s="12" t="inlineStr">
@@ -25957,7 +25957,7 @@
       </c>
       <c r="H328" s="12" t="inlineStr">
         <is>
-          <t>A story that ends happily.</t>
+          <t>以幸福收場的故事結局。</t>
         </is>
       </c>
       <c r="I328" s="12" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="L328" s="12" t="inlineStr">
         <is>
-          <t>I'm relieved this one has a happy ending.</t>
+          <t>這次是幸福結局真是太好了。</t>
         </is>
       </c>
       <c r="M328" s="12" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="H329" s="12" t="inlineStr">
         <is>
-          <t>An unexpected, surprising turn in a story.</t>
+          <t>故事中出乎意料的驚喜轉折。</t>
         </is>
       </c>
       <c r="I329" s="12" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="L329" s="12" t="inlineStr">
         <is>
-          <t>I really didn't see this drama's plot twist coming.</t>
+          <t>這部劇的反轉真的完全沒料到。</t>
         </is>
       </c>
       <c r="M329" s="12" t="inlineStr">
@@ -26111,7 +26111,7 @@
       </c>
       <c r="H330" s="12" t="inlineStr">
         <is>
-          <t>A famous, widely quoted line of dialogue from a show or movie.</t>
+          <t>戲劇或電影中廣為流傳、經常被引用的經典台詞。</t>
         </is>
       </c>
       <c r="I330" s="12" t="inlineStr">
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L330" s="12" t="inlineStr">
         <is>
-          <t>This drama has so many iconic lines.</t>
+          <t>這部劇經典台詞真的很多。</t>
         </is>
       </c>
       <c r="M330" s="12" t="inlineStr">
@@ -26188,7 +26188,7 @@
       </c>
       <c r="H331" s="12" t="inlineStr">
         <is>
-          <t>A famous, memorable scene from a show or movie.</t>
+          <t>戲劇或電影中令人難忘的經典畫面。</t>
         </is>
       </c>
       <c r="I331" s="12" t="inlineStr">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="L331" s="12" t="inlineStr">
         <is>
-          <t>This scene will go down as an iconic one.</t>
+          <t>這個畫面會成為經典場景留下來。</t>
         </is>
       </c>
       <c r="M331" s="12" t="inlineStr">
@@ -26265,7 +26265,7 @@
       </c>
       <c r="H332" s="12" t="inlineStr">
         <is>
-          <t>A drama format released across multiple seasons rather than as one continuous run.</t>
+          <t>以多個季度形式發行、而非一次連續播完的戲劇形式。</t>
         </is>
       </c>
       <c r="I332" s="12" t="inlineStr">
@@ -26285,7 +26285,7 @@
       </c>
       <c r="L332" s="12" t="inlineStr">
         <is>
-          <t>I heard this drama is going the season format route.</t>
+          <t>聽說這部劇要走季播制。</t>
         </is>
       </c>
       <c r="M332" s="12" t="inlineStr">
@@ -26342,7 +26342,7 @@
       </c>
       <c r="H333" s="12" t="inlineStr">
         <is>
-          <t>The novel, webtoon, or other work a drama or film is adapted from.</t>
+          <t>戲劇或電影所改編的原著小說、網漫或其他作品。</t>
         </is>
       </c>
       <c r="I333" s="12" t="inlineStr">
@@ -26362,7 +26362,7 @@
       </c>
       <c r="L333" s="12" t="inlineStr">
         <is>
-          <t>The original webtoon this drama is based on is much better.</t>
+          <t>這部劇的原作網漫好看多了。</t>
         </is>
       </c>
       <c r="M333" s="12" t="inlineStr">
@@ -26419,7 +26419,7 @@
       </c>
       <c r="H334" s="12" t="inlineStr">
         <is>
-          <t>"Destroying the original" — an adaptation that strays badly from its source material's quality or spirit.</t>
+          <t>「毀了原作」——改編作品嚴重偏離原著的品質或精神。</t>
         </is>
       </c>
       <c r="I334" s="12" t="inlineStr">
@@ -26439,7 +26439,7 @@
       </c>
       <c r="L334" s="12" t="inlineStr">
         <is>
-          <t>This drama is a total butchered adaptation.</t>
+          <t>這部劇完全是魔改原作。</t>
         </is>
       </c>
       <c r="M334" s="12" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="H335" s="12" t="inlineStr">
         <is>
-          <t>The process of adapting a script from existing source material.</t>
+          <t>將既有原著改編成劇本的過程。</t>
         </is>
       </c>
       <c r="I335" s="12" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="L335" s="12" t="inlineStr">
         <is>
-          <t>Some say the adaptation turned out even better than the original.</t>
+          <t>也有人說改編比原作還好。</t>
         </is>
       </c>
       <c r="M335" s="12" t="inlineStr">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="H336" s="12" t="inlineStr">
         <is>
-          <t>The primary episode or content, as distinct from extras or bonus footage.</t>
+          <t>主要正式的內容，相對於花絮或額外片段。</t>
         </is>
       </c>
       <c r="I336" s="12" t="inlineStr">
@@ -26593,7 +26593,7 @@
       </c>
       <c r="L336" s="12" t="inlineStr">
         <is>
-          <t>The behind-the-scenes is funnier than the main content.</t>
+          <t>幕後花絮比正片還好笑。</t>
         </is>
       </c>
       <c r="M336" s="12" t="inlineStr">
@@ -26650,7 +26650,7 @@
       </c>
       <c r="H337" s="12" t="inlineStr">
         <is>
-          <t>A show set in the same universe as an original, but following different characters or storylines.</t>
+          <t>設定在同一世界觀中、但聚焦不同角色或劇情線的衍生作品。</t>
         </is>
       </c>
       <c r="I337" s="12" t="inlineStr">
@@ -26670,7 +26670,7 @@
       </c>
       <c r="L337" s="12" t="inlineStr">
         <is>
-          <t>I wish this character got their own spin-off.</t>
+          <t>真希望這個角色能出衍生作品。</t>
         </is>
       </c>
       <c r="M337" s="12" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="H338" s="12" t="inlineStr">
         <is>
-          <t>A story set before the events of an original work.</t>
+          <t>設定在原作事件發生之前的前傳故事。</t>
         </is>
       </c>
       <c r="I338" s="12" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="L338" s="12" t="inlineStr">
         <is>
-          <t>If a prequel comes out, I'll definitely watch it.</t>
+          <t>如果出前傳我一定會看。</t>
         </is>
       </c>
       <c r="M338" s="12" t="inlineStr">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="H339" s="12" t="inlineStr">
         <is>
-          <t>Watching a show, drama, or webtoon straight through from beginning to end in one go.</t>
+          <t>從頭到尾一口氣看完一部戲劇、電視劇或網漫。</t>
         </is>
       </c>
       <c r="I339" s="12" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="L339" s="12" t="inlineStr">
         <is>
-          <t>I've been saving it to binge-watch over the weekend.</t>
+          <t>週末打算一次追完。</t>
         </is>
       </c>
       <c r="M339" s="12" t="inlineStr">
@@ -26881,7 +26881,7 @@
       </c>
       <c r="H340" s="12" t="inlineStr">
         <is>
-          <t>A drama, webtoon, or novel that has finished airing or publishing.</t>
+          <t>戲劇、網漫或小說已經播畢或連載完結。</t>
         </is>
       </c>
       <c r="I340" s="12" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="L340" s="12" t="inlineStr">
         <is>
-          <t>This webtoon finally reached its ending.</t>
+          <t>這部漫畫終於完結了。</t>
         </is>
       </c>
       <c r="M340" s="12" t="inlineStr">
@@ -26958,7 +26958,7 @@
       </c>
       <c r="H341" s="12" t="inlineStr">
         <is>
-          <t>A webtoon or web novel that is still actively being published in ongoing installments.</t>
+          <t>網漫或網路小說仍持續定期更新中。</t>
         </is>
       </c>
       <c r="I341" s="12" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="L341" s="12" t="inlineStr">
         <is>
-          <t>This series is still currently being serialized.</t>
+          <t>這部作品還在連載中。</t>
         </is>
       </c>
       <c r="M341" s="12" t="inlineStr">
@@ -27035,7 +27035,7 @@
       </c>
       <c r="H342" s="12" t="inlineStr">
         <is>
-          <t>A webtoon or web novel temporarily pausing its regular update schedule.</t>
+          <t>網漫或網路小說暫停原定的更新排程。</t>
         </is>
       </c>
       <c r="I342" s="12" t="inlineStr">
@@ -27055,7 +27055,7 @@
       </c>
       <c r="L342" s="12" t="inlineStr">
         <is>
-          <t>It's on hiatus this week, what a bummer.</t>
+          <t>這禮拜休載，好可惜。</t>
         </is>
       </c>
       <c r="M342" s="12" t="inlineStr">
@@ -27112,7 +27112,7 @@
       </c>
       <c r="H343" s="12" t="inlineStr">
         <is>
-          <t>"Munchkin" — a story protagonist with overwhelmingly strong abilities compared to everyone else.</t>
+          <t>「無雙主角」——能力遠遠強過其他人的故事主角。</t>
         </is>
       </c>
       <c r="I343" s="12" t="inlineStr">
@@ -27132,7 +27132,7 @@
       </c>
       <c r="L343" s="12" t="inlineStr">
         <is>
-          <t>This protagonist is a total overpowered munchkin.</t>
+          <t>這個主角完全是開外掛等級。</t>
         </is>
       </c>
       <c r="M343" s="12" t="inlineStr">
@@ -27189,7 +27189,7 @@
       </c>
       <c r="H344" s="12" t="inlineStr">
         <is>
-          <t>A genre label combining "regression, possession, and reincarnation" — stories where the protagonist wakes up in a past life, someone else's body, or a fictional world.</t>
+          <t>結合「倒退（回歸）、附身、轉生」的類型標籤——主角在過去、他人身體或虛構世界中甦醒的故事。</t>
         </is>
       </c>
       <c r="I344" s="12" t="inlineStr">
@@ -27209,7 +27209,7 @@
       </c>
       <c r="L344" s="12" t="inlineStr">
         <is>
-          <t>Regression/possession/reincarnation stories are the trend in web novels these days.</t>
+          <t>最近網路小說流行穿越重生附身題材。</t>
         </is>
       </c>
       <c r="M344" s="12" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="H345" s="12" t="inlineStr">
         <is>
-          <t>Short for a relationship that starts with mutual dislike between characters before turning into romance.</t>
+          <t>角色之間先互相厭惡、後來轉為戀愛關係的劇情套路簡稱，先厭後愛。</t>
         </is>
       </c>
       <c r="I345" s="12" t="inlineStr">
@@ -27286,7 +27286,7 @@
       </c>
       <c r="L345" s="12" t="inlineStr">
         <is>
-          <t>I really love the hate-to-love trope.</t>
+          <t>我真的很喜歡先厭後愛的劇情套路。</t>
         </is>
       </c>
       <c r="M345" s="12" t="inlineStr">
@@ -27343,7 +27343,7 @@
       </c>
       <c r="H346" s="12" t="inlineStr">
         <is>
-          <t>An officially licensed release or translation of a work in another region or language.</t>
+          <t>作品在其他地區或語言中取得官方授權發行、翻譯的版本。</t>
         </is>
       </c>
       <c r="I346" s="12" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="L346" s="12" t="inlineStr">
         <is>
-          <t>The official English release is finally out!</t>
+          <t>終於出英文版正版代理了！</t>
         </is>
       </c>
       <c r="M346" s="12" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="H347" s="12" t="inlineStr">
         <is>
-          <t>A novel published serially online, often the source material for webtoons and dramas.</t>
+          <t>在網路上連載發表的小說，常是網漫與戲劇的原著來源。</t>
         </is>
       </c>
       <c r="I347" s="12" t="inlineStr">
@@ -27440,7 +27440,7 @@
       </c>
       <c r="L347" s="12" t="inlineStr">
         <is>
-          <t>I heard the web novel this drama is based on is even better.</t>
+          <t>聽說這部劇的原作網路小說更好看。</t>
         </is>
       </c>
       <c r="M347" s="12" t="inlineStr">
@@ -27497,7 +27497,7 @@
       </c>
       <c r="H348" s="12" t="inlineStr">
         <is>
-          <t>A brief guest appearance by a well-known actor or celebrity in a drama or film.</t>
+          <t>知名演員或名人在戲劇或電影中的短暫客串演出。</t>
         </is>
       </c>
       <c r="I348" s="12" t="inlineStr">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="L348" s="12" t="inlineStr">
         <is>
-          <t>It was such a nice surprise seeing that actor's cameo.</t>
+          <t>那位演員的客串真的很驚喜。</t>
         </is>
       </c>
       <c r="M348" s="12" t="inlineStr">
@@ -27574,7 +27574,7 @@
       </c>
       <c r="H349" s="12" t="inlineStr">
         <is>
-          <t>A one-off special episode outside a show's usual format.</t>
+          <t>跳脫節目一般形式播出的單集特別節目。</t>
         </is>
       </c>
       <c r="I349" s="12" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="L349" s="12" t="inlineStr">
         <is>
-          <t>This week is a Chuseok holiday special episode.</t>
+          <t>這禮拜是中秋特輯。</t>
         </is>
       </c>
       <c r="M349" s="12" t="inlineStr">
@@ -27651,7 +27651,7 @@
       </c>
       <c r="H350" s="12" t="inlineStr">
         <is>
-          <t>An idiom meaning someone's reputation or fame is well and truly deserved.</t>
+          <t>成語，意指某人的名聲或名氣完全實至名歸。</t>
         </is>
       </c>
       <c r="I350" s="12" t="inlineStr">
@@ -27671,7 +27671,7 @@
       </c>
       <c r="L350" s="12" t="inlineStr">
         <is>
-          <t>This actor's acting skill truly lives up to the hype.</t>
+          <t>這位演員的演技真的名不虛傳。</t>
         </is>
       </c>
       <c r="M350" s="12" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="H351" s="12" t="inlineStr">
         <is>
-          <t>"Super luxurious casting" — a lineup of major, well-known actors all cast in the same production.</t>
+          <t>「超豪華選角」——多位知名主要演員同時參演一部作品的陣容。</t>
         </is>
       </c>
       <c r="I351" s="12" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="L351" s="12" t="inlineStr">
         <is>
-          <t>This drama has a total all-star cast.</t>
+          <t>這部劇是豪華卡司陣容。</t>
         </is>
       </c>
       <c r="M351" s="12" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="H352" s="12" t="inlineStr">
         <is>
-          <t>Short for "working hard" — hustling nonstop, often used to praise a busy celebrity's packed schedule.</t>
+          <t>「努力工作」的簡稱——不停歇地拚命工作，常用來稱讚藝人滿檔的行程。</t>
         </is>
       </c>
       <c r="I352" s="12" t="inlineStr">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="L352" s="12" t="inlineStr">
         <is>
-          <t>They're working hard lately, their schedule is completely packed.</t>
+          <t>最近拚命工作，行程滿滿。</t>
         </is>
       </c>
       <c r="M352" s="12" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="H353" s="12" t="inlineStr">
         <is>
-          <t>"Comeback angle" — signs or hints suggesting a comeback is imminent.</t>
+          <t>「回歸角度」——暗示即將回歸的跡象或線索。</t>
         </is>
       </c>
       <c r="I353" s="12" t="inlineStr">
@@ -27902,7 +27902,7 @@
       </c>
       <c r="L353" s="12" t="inlineStr">
         <is>
-          <t>Looking at social media, this is total comeback-incoming energy.</t>
+          <t>看社群媒體感覺完全是回歸徵兆。</t>
         </is>
       </c>
       <c r="M353" s="12" t="inlineStr">
@@ -27959,7 +27959,7 @@
       </c>
       <c r="H354" s="12" t="inlineStr">
         <is>
-          <t>Korean Lunar New Year, one of the biggest traditional holidays, often featured in special drama/variety episodes.</t>
+          <t>韓國農曆新年，是最重要的傳統節日之一，常有特別戲劇、綜藝節目播出。</t>
         </is>
       </c>
       <c r="I354" s="12" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="L354" s="12" t="inlineStr">
         <is>
-          <t>Did you watch the Lunar New Year special broadcast?</t>
+          <t>有看農曆新年特別節目嗎？</t>
         </is>
       </c>
       <c r="M354" s="12" t="inlineStr">
@@ -28036,7 +28036,7 @@
       </c>
       <c r="H355" s="12" t="inlineStr">
         <is>
-          <t>A major Korean harvest holiday, similar in spirit to Thanksgiving, often the setting for family-drama episodes.</t>
+          <t>韓國重要的秋收節日，精神類似感恩節，常是家庭劇情節的舞台背景。</t>
         </is>
       </c>
       <c r="I355" s="12" t="inlineStr">
@@ -28056,7 +28056,7 @@
       </c>
       <c r="L355" s="12" t="inlineStr">
         <is>
-          <t>We all gathered together for the Chuseok holiday.</t>
+          <t>中秋連假大家都聚在一起了。</t>
         </is>
       </c>
       <c r="M355" s="12" t="inlineStr">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="H356" s="12" t="inlineStr">
         <is>
-          <t>Money given to children by elders during Lunar New Year, after they perform a formal bow.</t>
+          <t>農曆新年時晚輩向長輩行禮後，長輩給予的紅包錢，壓歲錢。</t>
         </is>
       </c>
       <c r="I356" s="12" t="inlineStr">
@@ -28133,7 +28133,7 @@
       </c>
       <c r="L356" s="12" t="inlineStr">
         <is>
-          <t>How much New Year's money did you get?</t>
+          <t>領了多少壓歲錢？</t>
         </is>
       </c>
       <c r="M356" s="12" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="H357" s="12" t="inlineStr">
         <is>
-          <t>A rice cake soup traditionally eaten on Lunar New Year's Day, said to make you a year older.</t>
+          <t>農曆新年當天傳統會吃的年糕湯，據說吃了就長一歲。</t>
         </is>
       </c>
       <c r="I357" s="12" t="inlineStr">
@@ -28210,7 +28210,7 @@
       </c>
       <c r="L357" s="12" t="inlineStr">
         <is>
-          <t>Since I ate rice cake soup, I'm officially a year older now.</t>
+          <t>吃了年糕湯，代表又長一歲了。</t>
         </is>
       </c>
       <c r="M357" s="12" t="inlineStr">
@@ -28267,7 +28267,7 @@
       </c>
       <c r="H358" s="12" t="inlineStr">
         <is>
-          <t>Traditional Korean clothing, often worn during holidays, historical dramas, or special photoshoots.</t>
+          <t>韓國傳統服飾，常在節日、時代劇或特別寫真拍攝時穿著。</t>
         </is>
       </c>
       <c r="I358" s="12" t="inlineStr">
@@ -28287,7 +28287,7 @@
       </c>
       <c r="L358" s="12" t="inlineStr">
         <is>
-          <t>They looked so beautiful wearing hanbok.</t>
+          <t>穿韓服的樣子真的很美。</t>
         </is>
       </c>
       <c r="M358" s="12" t="inlineStr">
@@ -28344,7 +28344,7 @@
       </c>
       <c r="H359" s="12" t="inlineStr">
         <is>
-          <t>Visiting and tending to ancestors' graves, a traditional holiday practice.</t>
+          <t>造訪並整理祖先墓地的傳統節日習俗，掃墓。</t>
         </is>
       </c>
       <c r="I359" s="12" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="L359" s="12" t="inlineStr">
         <is>
-          <t>We went to visit the ancestral graves this Chuseok.</t>
+          <t>這次中秋去掃墓了。</t>
         </is>
       </c>
       <c r="M359" s="12" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="H360" s="12" t="inlineStr">
         <is>
-          <t>A trial episode or short run of a show, made to test audience reaction before a full series is greenlit.</t>
+          <t>為測試觀眾反應而製作的試播集或短篇節目，正式開播前的試驗。</t>
         </is>
       </c>
       <c r="I360" s="12" t="inlineStr">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="L360" s="12" t="inlineStr">
         <is>
-          <t>I heard this was originally just a pilot program.</t>
+          <t>聽說這個原本是試播節目。</t>
         </is>
       </c>
       <c r="M360" s="12" t="inlineStr">
@@ -28498,7 +28498,7 @@
       </c>
       <c r="H361" s="12" t="inlineStr">
         <is>
-          <t>A show getting approved for a full regular season after a successful pilot.</t>
+          <t>試播集反應良好後，節目正式獲得常態播出的機會。</t>
         </is>
       </c>
       <c r="I361" s="12" t="inlineStr">
@@ -28518,7 +28518,7 @@
       </c>
       <c r="L361" s="12" t="inlineStr">
         <is>
-          <t>The pilot got such a good response that it got picked up as a full series.</t>
+          <t>因為試播反應好，變成正式節目了。</t>
         </is>
       </c>
       <c r="M361" s="12" t="inlineStr">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="H362" s="12" t="inlineStr">
         <is>
-          <t>A drama or show's final episode airing, marking the end of its run.</t>
+          <t>戲劇或節目播出最終集，正式結束該系列的播映。</t>
         </is>
       </c>
       <c r="I362" s="12" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="L362" s="12" t="inlineStr">
         <is>
-          <t>I heard this drama's series finale airs next week.</t>
+          <t>這部劇下週完結。</t>
         </is>
       </c>
       <c r="M362" s="12" t="inlineStr">
@@ -28652,7 +28652,7 @@
       </c>
       <c r="H363" s="12" t="inlineStr">
         <is>
-          <t>The very first episode of a new show airing.</t>
+          <t>新節目播出的第一集，首播。</t>
         </is>
       </c>
       <c r="I363" s="12" t="inlineStr">
@@ -28672,7 +28672,7 @@
       </c>
       <c r="L363" s="12" t="inlineStr">
         <is>
-          <t>I heard the premiere's ratings were a huge hit.</t>
+          <t>聽說首播收視率超好。</t>
         </is>
       </c>
       <c r="M363" s="12" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="H364" s="12" t="inlineStr">
         <is>
-          <t>Positive reviews or favorable critical reception.</t>
+          <t>正面、獲得好評的評論。</t>
         </is>
       </c>
       <c r="I364" s="12" t="inlineStr">
@@ -28749,7 +28749,7 @@
       </c>
       <c r="L364" s="12" t="inlineStr">
         <is>
-          <t>This work is receiving nothing but praise.</t>
+          <t>這部作品得到一致好評。</t>
         </is>
       </c>
       <c r="M364" s="12" t="inlineStr">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="H365" s="12" t="inlineStr">
         <is>
-          <t>Negative, critical reviews.</t>
+          <t>負面、嚴厲批評的評論。</t>
         </is>
       </c>
       <c r="I365" s="12" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="L365" s="12" t="inlineStr">
         <is>
-          <t>Despite the harsh reviews, it's still really popular.</t>
+          <t>儘管惡評不斷，人氣還是很高。</t>
         </is>
       </c>
       <c r="M365" s="12" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="H366" s="12" t="inlineStr">
         <is>
-          <t>Commercial success, especially strong ticket sales or viewership.</t>
+          <t>商業上的成功，尤其指票房或收視表現亮眼。</t>
         </is>
       </c>
       <c r="I366" s="12" t="inlineStr">
@@ -28903,7 +28903,7 @@
       </c>
       <c r="L366" s="12" t="inlineStr">
         <is>
-          <t>This movie was a huge box office success.</t>
+          <t>這部電影票房真的很成功。</t>
         </is>
       </c>
       <c r="M366" s="12" t="inlineStr">
@@ -28960,7 +28960,7 @@
       </c>
       <c r="H367" s="12" t="inlineStr">
         <is>
-          <t>Short for "original soundtrack" — the music featured in a drama or film.</t>
+          <t>「原聲帶」的簡稱——戲劇或電影中收錄的音樂。</t>
         </is>
       </c>
       <c r="I367" s="12" t="inlineStr">
@@ -28980,7 +28980,7 @@
       </c>
       <c r="L367" s="12" t="inlineStr">
         <is>
-          <t>This drama's OST is seriously a masterpiece.</t>
+          <t>這部劇的OST真的是神曲。</t>
         </is>
       </c>
       <c r="M367" s="12" t="inlineStr">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="H368" s="12" t="inlineStr">
         <is>
-          <t>A song featured within a specific episode, distinct from the drama's main theme songs.</t>
+          <t>特定集數中插入使用的歌曲，有別於戲劇主題曲。</t>
         </is>
       </c>
       <c r="I368" s="12" t="inlineStr">
@@ -29057,7 +29057,7 @@
       </c>
       <c r="L368" s="12" t="inlineStr">
         <is>
-          <t>Do you know what the insert song for this episode was?</t>
+          <t>你知道這集的插曲是什麼嗎？</t>
         </is>
       </c>
       <c r="M368" s="12" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="H369" s="12" t="inlineStr">
         <is>
-          <t>The song played during a show's closing credits.</t>
+          <t>節目片尾字幕播放時使用的歌曲，片尾曲。</t>
         </is>
       </c>
       <c r="I369" s="12" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="L369" s="12" t="inlineStr">
         <is>
-          <t>The ending theme leaves a lasting feeling after you hear it.</t>
+          <t>聽完片尾曲會有種餘韻猶存的感覺。</t>
         </is>
       </c>
       <c r="M369" s="12" t="inlineStr">
@@ -29191,7 +29191,7 @@
       </c>
       <c r="H370" s="12" t="inlineStr">
         <is>
-          <t>Watching many episodes of a show back-to-back in one sitting — a common alternative term to 정주행.</t>
+          <t>一口氣連續觀看多集節目，是정주행的常見替代說法。</t>
         </is>
       </c>
       <c r="I370" s="12" t="inlineStr">
@@ -29211,7 +29211,7 @@
       </c>
       <c r="L370" s="12" t="inlineStr">
         <is>
-          <t>I binge-watched it all weekend.</t>
+          <t>整個週末都在追劇馬拉松。</t>
         </is>
       </c>
       <c r="M370" s="12" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="H371" s="12" t="inlineStr">
         <is>
-          <t>Watching video content at faster-than-normal playback speed (like 1.5x or 2x).</t>
+          <t>以快於正常速度（如1.5倍或2倍速）觀看影音內容。</t>
         </is>
       </c>
       <c r="I371" s="12" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="L371" s="12" t="inlineStr">
         <is>
-          <t>These days I can't watch anything without speed-up playback.</t>
+          <t>最近沒有倍速播放就看不下去了。</t>
         </is>
       </c>
       <c r="M371" s="12" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="H372" s="12" t="inlineStr">
         <is>
-          <t>Short for "Over-The-Top" — general term for streaming services like Netflix, Disney+, or local Korean platforms.</t>
+          <t>「Over-The-Top」的簡稱——泛指Netflix、Disney+或韓國本地平台等串流服務。</t>
         </is>
       </c>
       <c r="I372" s="12" t="inlineStr">
@@ -29365,7 +29365,7 @@
       </c>
       <c r="L372" s="12" t="inlineStr">
         <is>
-          <t>What streaming platform are you watching these days?</t>
+          <t>最近都看什麼OTT平台？</t>
         </is>
       </c>
       <c r="M372" s="12" t="inlineStr">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="H373" s="12" t="inlineStr">
         <is>
-          <t>The official age rating assigned to a show or film, indicating suitable audience age.</t>
+          <t>節目或電影官方核定的年齡分級，標示適合觀看的觀眾年齡。</t>
         </is>
       </c>
       <c r="I373" s="12" t="inlineStr">
@@ -29442,7 +29442,7 @@
       </c>
       <c r="L373" s="12" t="inlineStr">
         <is>
-          <t>What's this drama's content rating?</t>
+          <t>這部劇的分級是什麼？</t>
         </is>
       </c>
       <c r="M373" s="12" t="inlineStr">
@@ -29499,7 +29499,7 @@
       </c>
       <c r="H374" s="12" t="inlineStr">
         <is>
-          <t>How absorbed and drawn-in a piece of content makes you feel.</t>
+          <t>內容讓人感到投入、沉浸其中的程度。</t>
         </is>
       </c>
       <c r="I374" s="12" t="inlineStr">
@@ -29519,7 +29519,7 @@
       </c>
       <c r="L374" s="12" t="inlineStr">
         <is>
-          <t>This drama's sense of immersion is seriously amazing.</t>
+          <t>這部劇的沉浸感真的很驚人。</t>
         </is>
       </c>
       <c r="M374" s="12" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="H375" s="12" t="inlineStr">
         <is>
-          <t>A widely acclaimed, classic piece of work.</t>
+          <t>廣受讚譽的經典作品，名作。</t>
         </is>
       </c>
       <c r="I375" s="12" t="inlineStr">
@@ -29596,7 +29596,7 @@
       </c>
       <c r="L375" s="12" t="inlineStr">
         <is>
-          <t>This is truly a masterpiece.</t>
+          <t>這真的是經典之作。</t>
         </is>
       </c>
       <c r="M375" s="12" t="inlineStr">
@@ -29653,7 +29653,7 @@
       </c>
       <c r="H376" s="12" t="inlineStr">
         <is>
-          <t>An episode ending that leaves a tense, unresolved moment to hook viewers for the next one.</t>
+          <t>集數結尾留下緊張未解懸念、吸引觀眾追看下一集的手法。</t>
         </is>
       </c>
       <c r="I376" s="12" t="inlineStr">
@@ -29673,7 +29673,7 @@
       </c>
       <c r="L376" s="12" t="inlineStr">
         <is>
-          <t>I can't stand this episode's cliffhanger.</t>
+          <t>這集的懸念式結尾讓人受不了。</t>
         </is>
       </c>
       <c r="M376" s="12" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="H377" s="12" t="inlineStr">
         <is>
-          <t>A serious, straightforward drama genre, as opposed to comedy or fantasy.</t>
+          <t>嚴肅、正統的戲劇類型，相對於喜劇或奇幻類型而言，正劇。</t>
         </is>
       </c>
       <c r="I377" s="12" t="inlineStr">
@@ -29750,7 +29750,7 @@
       </c>
       <c r="L377" s="12" t="inlineStr">
         <is>
-          <t>This actor is really great at serious drama acting too.</t>
+          <t>這位演員演正劇也演得很好。</t>
         </is>
       </c>
       <c r="M377" s="12" t="inlineStr">
@@ -29807,7 +29807,7 @@
       </c>
       <c r="H378" s="12" t="inlineStr">
         <is>
-          <t>A scene or performance filmed in a single continuous shot without cuts.</t>
+          <t>一鏡到底、不經剪接一次拍完的場景或表演。</t>
         </is>
       </c>
       <c r="I378" s="12" t="inlineStr">
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L378" s="12" t="inlineStr">
         <is>
-          <t>I heard this scene was filmed in one take.</t>
+          <t>聽說這個畫面是一鏡到底拍的。</t>
         </is>
       </c>
       <c r="M378" s="12" t="inlineStr">
@@ -29884,7 +29884,7 @@
       </c>
       <c r="H379" s="12" t="inlineStr">
         <is>
-          <t>How logically coherent and believable a story's plot is — a common point of criticism when missing.</t>
+          <t>故事劇情邏輯是否連貫、可信的程度，常是缺乏時被批評的重點。</t>
         </is>
       </c>
       <c r="I379" s="12" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="L379" s="12" t="inlineStr">
         <is>
-          <t>This drama really lacks plot plausibility.</t>
+          <t>這部劇真的很缺乏劇情合理性。</t>
         </is>
       </c>
       <c r="M379" s="12" t="inlineStr">
@@ -29961,7 +29961,7 @@
       </c>
       <c r="H380" s="12" t="inlineStr">
         <is>
-          <t>"Life character" — an actor's most iconic, career-defining role.</t>
+          <t>「人生角色」——演員演藝生涯中最具代表性、最經典的角色。</t>
         </is>
       </c>
       <c r="I380" s="12" t="inlineStr">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="L380" s="12" t="inlineStr">
         <is>
-          <t>This role is that actor's signature character.</t>
+          <t>這個角色是那位演員的代表作角色。</t>
         </is>
       </c>
       <c r="M380" s="12" t="inlineStr">
@@ -30038,7 +30038,7 @@
       </c>
       <c r="H381" s="12" t="inlineStr">
         <is>
-          <t>A fan of a drama's source novel or webtoon before its adaptation, often critical of changes made.</t>
+          <t>在改編之前就是戲劇原著小說或網漫的粉絲，常對改編內容較為挑剔。</t>
         </is>
       </c>
       <c r="I381" s="12" t="inlineStr">
@@ -30058,7 +30058,7 @@
       </c>
       <c r="L381" s="12" t="inlineStr">
         <is>
-          <t>As a fan of the original, this adaptation is a bit disappointing.</t>
+          <t>身為原作粉絲，這次的改編有點可惜。</t>
         </is>
       </c>
       <c r="M381" s="12" t="inlineStr">
@@ -30115,7 +30115,7 @@
       </c>
       <c r="H382" s="12" t="inlineStr">
         <is>
-          <t>Replacing a show or film's original audio with a translated voice track in another language.</t>
+          <t>將戲劇或電影原音替換成另一種語言的翻譯配音。</t>
         </is>
       </c>
       <c r="I382" s="12" t="inlineStr">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="L382" s="12" t="inlineStr">
         <is>
-          <t>Which is better, the dubbed version or the subtitled one?</t>
+          <t>配音版跟字幕版哪個比較好？</t>
         </is>
       </c>
       <c r="M382" s="12" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="H383" s="12" t="inlineStr">
         <is>
-          <t>A show going on a scheduling break of its own choice, not due to any controversy.</t>
+          <t>節目自行選擇暫停播出，並非因為爭議事件。</t>
         </is>
       </c>
       <c r="I383" s="12" t="inlineStr">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="L383" s="12" t="inlineStr">
         <is>
-          <t>I heard this week is a self-imposed hiatus.</t>
+          <t>聽說這週是自行暫停播出。</t>
         </is>
       </c>
       <c r="M383" s="12" t="inlineStr">
@@ -30269,7 +30269,7 @@
       </c>
       <c r="H384" s="12" t="inlineStr">
         <is>
-          <t>A supporting actor whose performance stands out and steals attention in their scenes.</t>
+          <t>演出格外亮眼、在戲份中搶走觀眾目光的配角演員，搶戲演員。</t>
         </is>
       </c>
       <c r="I384" s="12" t="inlineStr">
@@ -30289,7 +30289,7 @@
       </c>
       <c r="L384" s="12" t="inlineStr">
         <is>
-          <t>This supporting actor is a total scene stealer.</t>
+          <t>這位配角完全是搶戲擔當。</t>
         </is>
       </c>
       <c r="M384" s="12" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="H385" s="12" t="inlineStr">
         <is>
-          <t>"Foot acting" — notably bad, stiff, or unconvincing acting.</t>
+          <t>「腳演技」——特別生硬、不自然、令人尷尬的演技。</t>
         </is>
       </c>
       <c r="I385" s="12" t="inlineStr">
@@ -30366,7 +30366,7 @@
       </c>
       <c r="L385" s="12" t="inlineStr">
         <is>
-          <t>The wooden acting in this scene is really bad.</t>
+          <t>這幕的尷尬演技也太明顯了。</t>
         </is>
       </c>
       <c r="M385" s="12" t="inlineStr">
@@ -30423,7 +30423,7 @@
       </c>
       <c r="H386" s="12" t="inlineStr">
         <is>
-          <t>A deeply committed, passionate acting performance.</t>
+          <t>投入深刻、充滿熱情的演出。</t>
         </is>
       </c>
       <c r="I386" s="12" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="L386" s="12" t="inlineStr">
         <is>
-          <t>They delivered a passionate performance in this work.</t>
+          <t>這次作品中展現了精湛演出。</t>
         </is>
       </c>
       <c r="M386" s="12" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H387" s="12" t="inlineStr">
         <is>
-          <t>A blend of "error" and "over" — describes something excessive, overwhelming, or way over the top.</t>
+          <t>「error」與「over」的結合詞——形容某件事過度、誇張、太超過。</t>
         </is>
       </c>
       <c r="I387" s="12" t="inlineStr">
@@ -30520,7 +30520,7 @@
       </c>
       <c r="L387" s="12" t="inlineStr">
         <is>
-          <t>Five homework assignments, that's just way too much.</t>
+          <t>五個作業真的太誇張了。</t>
         </is>
       </c>
       <c r="M387" s="12" t="inlineStr">
@@ -30577,7 +30577,7 @@
       </c>
       <c r="H388" s="12" t="inlineStr">
         <is>
-          <t>A texting style using only the initial consonants of words, like ㅇㅋ for "okay" or ㄱㅅ for "thanks."</t>
+          <t>只用韓文字詞開頭子音打字的簡訊風格，例如用ㅇㅋ代表「好的」。</t>
         </is>
       </c>
       <c r="I388" s="12" t="inlineStr">
@@ -30597,7 +30597,7 @@
       </c>
       <c r="L388" s="12" t="inlineStr">
         <is>
-          <t>They replied using only consonant-only texting.</t>
+          <t>對方只用子音縮寫回訊息。</t>
         </is>
       </c>
       <c r="M388" s="12" t="inlineStr">
@@ -30654,7 +30654,7 @@
       </c>
       <c r="H389" s="12" t="inlineStr">
         <is>
-          <t>"National drama" — a drama so widely popular it becomes a shared national phenomenon.</t>
+          <t>「國民劇」——廣受歡迎到成為全民共同話題的戲劇。</t>
         </is>
       </c>
       <c r="I389" s="12" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="L389" s="12" t="inlineStr">
         <is>
-          <t>This has truly risen to the ranks of a national drama.</t>
+          <t>這已經真正躋身國民劇的行列了。</t>
         </is>
       </c>
       <c r="M389" s="12" t="inlineStr">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="H390" s="12" t="inlineStr">
         <is>
-          <t>A persona or role a celebrity adopts specifically for variety shows, distinct from their real personality.</t>
+          <t>藝人專為綜藝節目塑造、有別於本人真實個性的人設，綜藝人設。</t>
         </is>
       </c>
       <c r="I390" s="12" t="inlineStr">
@@ -30751,7 +30751,7 @@
       </c>
       <c r="L390" s="12" t="inlineStr">
         <is>
-          <t>That person's variety persona has really taken hold.</t>
+          <t>那個人的綜藝人設已經完全站穩了。</t>
         </is>
       </c>
       <c r="M390" s="12" t="inlineStr">
@@ -30808,7 +30808,7 @@
       </c>
       <c r="H391" s="12" t="inlineStr">
         <is>
-          <t>"Joke power" — someone's skill and quick wit at making funny remarks or comebacks.</t>
+          <t>「哏力」——某人說笑話、接梗反應機智靈活的能力。</t>
         </is>
       </c>
       <c r="I391" s="12" t="inlineStr">
@@ -30828,7 +30828,7 @@
       </c>
       <c r="L391" s="12" t="inlineStr">
         <is>
-          <t>Is that person's joke skill for real?</t>
+          <t>那個人抖包袱的功力真的很厲害。</t>
         </is>
       </c>
       <c r="M391" s="12" t="inlineStr">
@@ -30885,7 +30885,7 @@
       </c>
       <c r="H392" s="12" t="inlineStr">
         <is>
-          <t>"Great losing-your-mind party" — describes an utterly chaotic, over-the-top ridiculous situation.</t>
+          <t>「大崩潰派對」——形容徹底混亂、荒謬到極點的情況。</t>
         </is>
       </c>
       <c r="I392" s="12" t="inlineStr">
@@ -30905,7 +30905,7 @@
       </c>
       <c r="L392" s="12" t="inlineStr">
         <is>
-          <t>This drama's ending was a total chaos party.</t>
+          <t>這部劇的結局完全是大崩潰現場。</t>
         </is>
       </c>
       <c r="M392" s="12" t="inlineStr">
@@ -30962,7 +30962,7 @@
       </c>
       <c r="H393" s="12" t="inlineStr">
         <is>
-          <t>Short for "혼자 코인노래방" (alone at a coin karaoke) — going to a pay-per-song karaoke booth by yourself.</t>
+          <t>「혼자 코인노래방」（獨自去投幣式KTV）的簡稱——自己一個人去按次計費的小型KTV。</t>
         </is>
       </c>
       <c r="I393" s="12" t="inlineStr">
@@ -30982,7 +30982,7 @@
       </c>
       <c r="L393" s="12" t="inlineStr">
         <is>
-          <t>Solo karaoke is the best when I'm stressed.</t>
+          <t>壓力大的時候一個人去投幣式KTV最棒了。</t>
         </is>
       </c>
       <c r="M393" s="12" t="inlineStr">
@@ -44745,7 +44745,7 @@
       </c>
       <c r="H572" s="16" t="inlineStr">
         <is>
-          <t>To be in that ambiguous, pre-dating phase of mutual interest with someone.</t>
+          <t>正式交往前，彼此有好感、關係曖昧不明的階段。</t>
         </is>
       </c>
       <c r="I572" s="16" t="inlineStr">
@@ -44765,7 +44765,7 @@
       </c>
       <c r="L572" s="16" t="inlineStr">
         <is>
-          <t>We've been in the talking stage for a month.</t>
+          <t>我們曖昧一個月了。</t>
         </is>
       </c>
       <c r="M572" s="16" t="inlineStr">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H573" s="16" t="inlineStr">
         <is>
-          <t>Short for "pushing and pulling" — playing a little hard to get in a relationship.</t>
+          <t>「推拉」的簡稱——在感情中欲擒故縱、若即若離。</t>
         </is>
       </c>
       <c r="I573" s="16" t="inlineStr">
@@ -44842,7 +44842,7 @@
       </c>
       <c r="L573" s="16" t="inlineStr">
         <is>
-          <t>Stop playing push-and-pull and just be honest.</t>
+          <t>別再欲擒故縱了，老實說吧。</t>
         </is>
       </c>
       <c r="M573" s="16" t="inlineStr">
@@ -44899,7 +44899,7 @@
       </c>
       <c r="H574" s="16" t="inlineStr">
         <is>
-          <t>"Fish-tank management" — keeping multiple romantic prospects on the line at once without committing.</t>
+          <t>「魚缸管理」——同時吊著好幾個對象、不做出承諾，養魚。</t>
         </is>
       </c>
       <c r="I574" s="16" t="inlineStr">
@@ -44919,7 +44919,7 @@
       </c>
       <c r="L574" s="16" t="inlineStr">
         <is>
-          <t>I think they're totally fish-tanking people, be careful.</t>
+          <t>我覺得他在養魚，小心點。</t>
         </is>
       </c>
       <c r="M574" s="16" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H575" s="16" t="inlineStr">
         <is>
-          <t>A playful pun using "3" (삼) as a step before 사귀다 ("to date," which starts with 사=4) — the talking stage.</t>
+          <t>用數字「3」取代「사귀다」（交往，以4開頭）玩的雙關語，指正式交往前的曖昧階段。</t>
         </is>
       </c>
       <c r="I575" s="16" t="inlineStr">
@@ -44996,7 +44996,7 @@
       </c>
       <c r="L575" s="16" t="inlineStr">
         <is>
-          <t>We're in that pre-dating stage right now.</t>
+          <t>我們現在算是曖昧中的關係。</t>
         </is>
       </c>
       <c r="M575" s="16" t="inlineStr">
@@ -45053,7 +45053,7 @@
       </c>
       <c r="H576" s="16" t="inlineStr">
         <is>
-          <t>"Transfer love" — starting a new relationship right after a breakup, popularized by a reality show of the same name.</t>
+          <t>「轉乘戀愛」——分手後立刻投入新戀情，因同名實境節目而爆紅。</t>
         </is>
       </c>
       <c r="I576" s="16" t="inlineStr">
@@ -45073,7 +45073,7 @@
       </c>
       <c r="L576" s="16" t="inlineStr">
         <is>
-          <t>Isn't that couple a total transfer-love situation?</t>
+          <t>那對情侶根本是轉乘戀愛吧？</t>
         </is>
       </c>
       <c r="M576" s="16" t="inlineStr">
@@ -45130,7 +45130,7 @@
       </c>
       <c r="H577" s="16" t="inlineStr">
         <is>
-          <t>"Diving breakup" — ending a relationship by disappearing without explanation, i.e. ghosting.</t>
+          <t>「潛水式分手」——不做任何說明就人間蒸發結束關係。</t>
         </is>
       </c>
       <c r="I577" s="16" t="inlineStr">
@@ -45150,7 +45150,7 @@
       </c>
       <c r="L577" s="16" t="inlineStr">
         <is>
-          <t>I got ghosted with no explanation at all.</t>
+          <t>毫無音訊就被人間蒸發式分手了。</t>
         </is>
       </c>
       <c r="M577" s="16" t="inlineStr">
@@ -45207,7 +45207,7 @@
       </c>
       <c r="H578" s="16" t="inlineStr">
         <is>
-          <t>A fake "contract relationship" arranged for practical reasons — a very common K-drama plot device.</t>
+          <t>因現實考量而假裝交往的「契約戀愛」，是韓劇非常常見的劇情設定。</t>
         </is>
       </c>
       <c r="I578" s="16" t="inlineStr">
@@ -45227,7 +45227,7 @@
       </c>
       <c r="L578" s="16" t="inlineStr">
         <is>
-          <t>This drama is a contract-relationship story.</t>
+          <t>這部劇是契約戀愛劇情。</t>
         </is>
       </c>
       <c r="M578" s="16" t="inlineStr">
@@ -45284,7 +45284,7 @@
       </c>
       <c r="H579" s="16" t="inlineStr">
         <is>
-          <t>A chaebol — a large, family-controlled business conglomerate, often a K-drama love interest's background.</t>
+          <t>財閥——大型家族控制的企業集團，常是韓劇男女主角的家世背景設定。</t>
         </is>
       </c>
       <c r="I579" s="16" t="inlineStr">
@@ -45304,7 +45304,7 @@
       </c>
       <c r="L579" s="16" t="inlineStr">
         <is>
-          <t>I heard this drama's male lead is a third-generation chaebol heir.</t>
+          <t>聽說這次男主角是財閥三代。</t>
         </is>
       </c>
       <c r="M579" s="16" t="inlineStr">
@@ -45361,7 +45361,7 @@
       </c>
       <c r="H580" s="16" t="inlineStr">
         <is>
-          <t>"End of the mine shaft" — describes an extreme, over-the-top dramatic plot twist.</t>
+          <t>字面意思是「礦坑盡頭」——形容誇張、狗血到極點的劇情轉折。</t>
         </is>
       </c>
       <c r="I580" s="16" t="inlineStr">
@@ -45381,7 +45381,7 @@
       </c>
       <c r="L580" s="16" t="inlineStr">
         <is>
-          <t>This drama's plot has gone completely over the top.</t>
+          <t>這部劇劇情完全狗血。</t>
         </is>
       </c>
       <c r="M580" s="16" t="inlineStr">
@@ -45438,7 +45438,7 @@
       </c>
       <c r="H581" s="16" t="inlineStr">
         <is>
-          <t>What a man calls an older woman — also names the popular "noona romance" drama trope.</t>
+          <t>男性稱呼年長女性的用語，也用來指稱流行的「姊弟戀」劇情套路。</t>
         </is>
       </c>
       <c r="I581" s="16" t="inlineStr">
@@ -45458,7 +45458,7 @@
       </c>
       <c r="L581" s="16" t="inlineStr">
         <is>
-          <t>This drama is a noona romance.</t>
+          <t>這部劇是姊弟戀劇情。</t>
         </is>
       </c>
       <c r="M581" s="16" t="inlineStr">
@@ -45515,7 +45515,7 @@
       </c>
       <c r="H582" s="16" t="inlineStr">
         <is>
-          <t>A cold-and-prickly-on-the-outside, warm-on-the-inside personality type (originally Japanese, widely used in Korean too).</t>
+          <t>外表冷淡尖銳、內心溫暖的性格類型，傲嬌，原為日文用語，在韓國也廣泛使用。</t>
         </is>
       </c>
       <c r="I582" s="16" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="L582" s="16" t="inlineStr">
         <is>
-          <t>That character is a total tsundere.</t>
+          <t>那個角色完全是傲嬌。</t>
         </is>
       </c>
       <c r="M582" s="16" t="inlineStr">
@@ -45592,7 +45592,7 @@
       </c>
       <c r="H583" s="16" t="inlineStr">
         <is>
-          <t>Reuniting with an ex-partner.</t>
+          <t>與前任重新復合。</t>
         </is>
       </c>
       <c r="I583" s="16" t="inlineStr">
@@ -45612,7 +45612,7 @@
       </c>
       <c r="L583" s="16" t="inlineStr">
         <is>
-          <t>I heard that couple got back together in the end.</t>
+          <t>聽說那對情侶最後復合了。</t>
         </is>
       </c>
       <c r="M583" s="16" t="inlineStr">
@@ -45746,7 +45746,7 @@
       </c>
       <c r="H585" s="16" t="inlineStr">
         <is>
-          <t>"Love village" — the classic setting/format used in Korean dating reality shows.</t>
+          <t>「愛情村」——韓國戀愛實境節目經典的場景設定與節目形式。</t>
         </is>
       </c>
       <c r="I585" s="16" t="inlineStr">
@@ -45766,7 +45766,7 @@
       </c>
       <c r="L585" s="16" t="inlineStr">
         <is>
-          <t>Is that couple from the love-village show still together?</t>
+          <t>那對從愛情村出來的情侶還在一起嗎？</t>
         </is>
       </c>
       <c r="M585" s="16" t="inlineStr">
@@ -45823,7 +45823,7 @@
       </c>
       <c r="H586" s="16" t="inlineStr">
         <is>
-          <t>"Heart-thump" — a swoon-worthy, heart-fluttering moment.</t>
+          <t>「心臟砰咚」——令人心動、心跳加速的瞬間。</t>
         </is>
       </c>
       <c r="I586" s="16" t="inlineStr">
@@ -45843,7 +45843,7 @@
       </c>
       <c r="L586" s="16" t="inlineStr">
         <is>
-          <t>That scene was such a heart-flutter moment.</t>
+          <t>那個畫面完全讓人心動。</t>
         </is>
       </c>
       <c r="M586" s="16" t="inlineStr">
@@ -45900,7 +45900,7 @@
       </c>
       <c r="H587" s="16" t="inlineStr">
         <is>
-          <t>One's very first love.</t>
+          <t>一個人生命中最初的戀愛對象，初戀。</t>
         </is>
       </c>
       <c r="I587" s="16" t="inlineStr">
@@ -45920,7 +45920,7 @@
       </c>
       <c r="L587" s="16" t="inlineStr">
         <is>
-          <t>Watching that drama made me think of my first love.</t>
+          <t>看那部劇讓我想起初戀。</t>
         </is>
       </c>
       <c r="M587" s="16" t="inlineStr">
@@ -45977,7 +45977,7 @@
       </c>
       <c r="H588" s="16" t="inlineStr">
         <is>
-          <t>"Nation's first love" — an actress or idol seen as an idealized, universally beloved first-love figure.</t>
+          <t>「國民初戀」——被視為理想化、全民共同初戀形象的女演員或偶像。</t>
         </is>
       </c>
       <c r="I588" s="16" t="inlineStr">
@@ -45997,7 +45997,7 @@
       </c>
       <c r="L588" s="16" t="inlineStr">
         <is>
-          <t>That actress is called the nation's first love.</t>
+          <t>那位演員被稱為國民初戀。</t>
         </is>
       </c>
       <c r="M588" s="16" t="inlineStr">
@@ -46054,7 +46054,7 @@
       </c>
       <c r="H589" s="16" t="inlineStr">
         <is>
-          <t>A warm, wholesome, good-looking man — approachable rather than intimidating.</t>
+          <t>溫暖、樸實、外表出眾的男性，給人親切而非有距離感的印象，暖男。</t>
         </is>
       </c>
       <c r="I589" s="16" t="inlineStr">
@@ -46074,7 +46074,7 @@
       </c>
       <c r="L589" s="16" t="inlineStr">
         <is>
-          <t>That male lead is totally the wholesome good-looking type.</t>
+          <t>那個男主角完全是暖男型。</t>
         </is>
       </c>
       <c r="M589" s="16" t="inlineStr">
@@ -46131,7 +46131,7 @@
       </c>
       <c r="H590" s="16" t="inlineStr">
         <is>
-          <t>The female equivalent of 훈남 — warm, approachable, and good-looking.</t>
+          <t>훈남的女性版本——溫暖、親切又好看的女性。</t>
         </is>
       </c>
       <c r="I590" s="16" t="inlineStr">
@@ -46151,7 +46151,7 @@
       </c>
       <c r="L590" s="16" t="inlineStr">
         <is>
-          <t>That actress is known for her wholesome good-looking image.</t>
+          <t>那位女演員以暖女形象聞名。</t>
         </is>
       </c>
       <c r="M590" s="16" t="inlineStr">
@@ -46208,7 +46208,7 @@
       </c>
       <c r="H591" s="16" t="inlineStr">
         <is>
-          <t>The "bad boy" trope — a cold, dangerous-seeming male lead who softens for the heroine.</t>
+          <t>「壞男人」套路——外表冷酷、帶點危險氣息，卻在女主角面前逐漸軟化的男主角類型。</t>
         </is>
       </c>
       <c r="I591" s="16" t="inlineStr">
@@ -46228,7 +46228,7 @@
       </c>
       <c r="L591" s="16" t="inlineStr">
         <is>
-          <t>Even though it's the bad-boy cliché, I keep watching anyway.</t>
+          <t>雖然是壞男人的老梗，還是會一直看下去。</t>
         </is>
       </c>
       <c r="M591" s="16" t="inlineStr">
@@ -46285,7 +46285,7 @@
       </c>
       <c r="H592" s="16" t="inlineStr">
         <is>
-          <t>A blind date, typically set up by a mutual friend.</t>
+          <t>通常由共同朋友安排的相親約會。</t>
         </is>
       </c>
       <c r="I592" s="16" t="inlineStr">
@@ -46305,7 +46305,7 @@
       </c>
       <c r="L592" s="16" t="inlineStr">
         <is>
-          <t>My friend is setting me up on a blind date.</t>
+          <t>朋友要幫我安排相親。</t>
         </is>
       </c>
       <c r="M592" s="16" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H593" s="16" t="inlineStr">
         <is>
-          <t>Short for "solo since birth" — someone who has never dated anyone.</t>
+          <t>「從娘胎開始就單身」的簡稱——從來沒有交往過的人，母胎單身。</t>
         </is>
       </c>
       <c r="I593" s="16" t="inlineStr">
@@ -46382,7 +46382,7 @@
       </c>
       <c r="L593" s="16" t="inlineStr">
         <is>
-          <t>I'm still someone who's never dated.</t>
+          <t>我還是母胎單身。</t>
         </is>
       </c>
       <c r="M593" s="16" t="inlineStr">
@@ -46439,7 +46439,7 @@
       </c>
       <c r="H594" s="16" t="inlineStr">
         <is>
-          <t>Short for "seeking a natural meeting" — wanting to meet a partner organically rather than through a setup.</t>
+          <t>「追求自然相遇」的簡稱——希望自然而然認識對象，而非透過相親介紹。</t>
         </is>
       </c>
       <c r="I594" s="16" t="inlineStr">
@@ -46459,7 +46459,7 @@
       </c>
       <c r="L594" s="16" t="inlineStr">
         <is>
-          <t>I'm the natural-encounter type, so I don't do blind dates.</t>
+          <t>我是喜歡自然認識的類型，不太相親。</t>
         </is>
       </c>
       <c r="M594" s="16" t="inlineStr">
@@ -46516,7 +46516,7 @@
       </c>
       <c r="H595" s="16" t="inlineStr">
         <is>
-          <t>Short for "female friend" — used to clarify a woman is just a friend, not a romantic interest.</t>
+          <t>「女性朋友」的簡稱——用來澄清某位女性只是朋友、並非戀愛對象。</t>
         </is>
       </c>
       <c r="I595" s="16" t="inlineStr">
@@ -46536,7 +46536,7 @@
       </c>
       <c r="L595" s="16" t="inlineStr">
         <is>
-          <t>She's just a female friend, don't get the wrong idea.</t>
+          <t>只是女性朋友而已，別誤會。</t>
         </is>
       </c>
       <c r="M595" s="16" t="inlineStr">
@@ -46593,7 +46593,7 @@
       </c>
       <c r="H596" s="16" t="inlineStr">
         <is>
-          <t>Short for "male friend" — used to clarify a man is just a friend, not a romantic interest.</t>
+          <t>「男性朋友」的簡稱——用來澄清某位男性只是朋友、並非戀愛對象。</t>
         </is>
       </c>
       <c r="I596" s="16" t="inlineStr">
@@ -46613,7 +46613,7 @@
       </c>
       <c r="L596" s="16" t="inlineStr">
         <is>
-          <t>I went to see a movie with my guy friend.</t>
+          <t>跟男性朋友去看電影了。</t>
         </is>
       </c>
       <c r="M596" s="16" t="inlineStr">
@@ -46670,7 +46670,7 @@
       </c>
       <c r="H597" s="16" t="inlineStr">
         <is>
-          <t>A cute nickname used between romantic partners.</t>
+          <t>情侶之間使用的可愛暱稱。</t>
         </is>
       </c>
       <c r="I597" s="16" t="inlineStr">
@@ -46690,7 +46690,7 @@
       </c>
       <c r="L597" s="16" t="inlineStr">
         <is>
-          <t>Seeing they even have pet names for each other, they must really be dating.</t>
+          <t>看到兩個人連暱稱都有了，看來真的在交往。</t>
         </is>
       </c>
       <c r="M597" s="16" t="inlineStr">
@@ -46747,7 +46747,7 @@
       </c>
       <c r="H598" s="16" t="inlineStr">
         <is>
-          <t>"Love + Instagram" — social media posts where a couple shows off their relationship.</t>
+          <t>「愛情＋Instagram」——情侶在社群媒體上曬恩愛的貼文。</t>
         </is>
       </c>
       <c r="I598" s="16" t="inlineStr">
@@ -46767,7 +46767,7 @@
       </c>
       <c r="L598" s="16" t="inlineStr">
         <is>
-          <t>Seeing their couple posts, they really look happy together.</t>
+          <t>看他們曬恩愛，感覺真的很幸福。</t>
         </is>
       </c>
       <c r="M598" s="16" t="inlineStr">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="H599" s="16" t="inlineStr">
         <is>
-          <t>A plucky, resilient, kind female lead trope who stays positive despite hardship, named after the classic character Candy Candy.</t>
+          <t>堅強樂觀、即使歷經困境仍保持正向的女主角類型，源自經典角色《小甜甜》。</t>
         </is>
       </c>
       <c r="I599" s="16" t="inlineStr">
@@ -46844,7 +46844,7 @@
       </c>
       <c r="L599" s="16" t="inlineStr">
         <is>
-          <t>This drama's female lead is a total Candy-type heroine.</t>
+          <t>這部劇女主角完全是小甜甜類型。</t>
         </is>
       </c>
       <c r="M599" s="16" t="inlineStr">
@@ -46901,7 +46901,7 @@
       </c>
       <c r="H600" s="16" t="inlineStr">
         <is>
-          <t>A classic K-drama plot device where a character's true parentage or origin is secretly hidden and later revealed.</t>
+          <t>韓劇經典劇情套路——角色真實身世或血緣被隱藏、後來才揭曉的設定，出生之謎。</t>
         </is>
       </c>
       <c r="I600" s="16" t="inlineStr">
@@ -46921,7 +46921,7 @@
       </c>
       <c r="L600" s="16" t="inlineStr">
         <is>
-          <t>This drama ended up having a secret-birth twist too.</t>
+          <t>這部劇最後也出現了出生之謎的劇情。</t>
         </is>
       </c>
       <c r="M600" s="16" t="inlineStr">
@@ -46978,7 +46978,7 @@
       </c>
       <c r="H601" s="16" t="inlineStr">
         <is>
-          <t>Tension and conflict between a wife and her mother-in-law, a very common drama theme.</t>
+          <t>妻子與婆婆之間的緊張與衝突，是韓劇非常常見的題材，婆媳問題。</t>
         </is>
       </c>
       <c r="I601" s="16" t="inlineStr">
@@ -46998,7 +46998,7 @@
       </c>
       <c r="L601" s="16" t="inlineStr">
         <is>
-          <t>This drama's mother-in-law conflict is so stressful to watch.</t>
+          <t>這部劇的婆媳問題看得好有壓力。</t>
         </is>
       </c>
       <c r="M601" s="16" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H602" s="16" t="inlineStr">
         <is>
-          <t>A romantic storyline involving three people with overlapping feelings for each other.</t>
+          <t>三個人之間互有情愫、糾葛交織的戀愛劇情，三角關係。</t>
         </is>
       </c>
       <c r="I602" s="16" t="inlineStr">
@@ -47075,7 +47075,7 @@
       </c>
       <c r="L602" s="16" t="inlineStr">
         <is>
-          <t>This drama's love triangle is so frustrating.</t>
+          <t>這部劇的三角關係讓人好鬱悶。</t>
         </is>
       </c>
       <c r="M602" s="16" t="inlineStr">
@@ -47132,7 +47132,7 @@
       </c>
       <c r="H603" s="16" t="inlineStr">
         <is>
-          <t>A drama plot device where a character has a terminal illness, often driving the emotional storyline.</t>
+          <t>角色罹患絕症的劇情設定，常用來推動情感張力，絕症設定。</t>
         </is>
       </c>
       <c r="I603" s="16" t="inlineStr">
@@ -47152,7 +47152,7 @@
       </c>
       <c r="L603" s="16" t="inlineStr">
         <is>
-          <t>Once I found out about the terminal illness twist, I watched it even more sadly.</t>
+          <t>知道是絕症設定之後看得更難過了。</t>
         </is>
       </c>
       <c r="M603" s="16" t="inlineStr">
@@ -47209,7 +47209,7 @@
       </c>
       <c r="H604" s="16" t="inlineStr">
         <is>
-          <t>A marriage arranged for business, family, or political reasons rather than love — a common drama setup.</t>
+          <t>因商業、家族或政治因素而非愛情所安排的婚姻，是韓劇常見的設定，利益聯姻。</t>
         </is>
       </c>
       <c r="I604" s="16" t="inlineStr">
@@ -47229,7 +47229,7 @@
       </c>
       <c r="L604" s="16" t="inlineStr">
         <is>
-          <t>It started as an arranged marriage, but they really fell in love.</t>
+          <t>雖然是利益聯姻開始的，但真的墜入愛河了。</t>
         </is>
       </c>
       <c r="M604" s="16" t="inlineStr">
@@ -47286,7 +47286,7 @@
       </c>
       <c r="H605" s="16" t="inlineStr">
         <is>
-          <t>A story trope where an ordinary or poor character rises into a wealthy or elite world, often through romance.</t>
+          <t>平凡或貧窮的角色透過戀愛躍升進入富裕上流世界的劇情套路，灰姑娘故事。</t>
         </is>
       </c>
       <c r="I605" s="16" t="inlineStr">
@@ -47306,7 +47306,7 @@
       </c>
       <c r="L605" s="16" t="inlineStr">
         <is>
-          <t>It's a total Cinderella story.</t>
+          <t>完全是灰姑娘的故事。</t>
         </is>
       </c>
       <c r="M605" s="16" t="inlineStr">
@@ -47363,7 +47363,7 @@
       </c>
       <c r="H606" s="16" t="inlineStr">
         <is>
-          <t>A person who feels like a perfect emotional match, a soulmate.</t>
+          <t>感覺與自己完美契合的靈魂伴侶。</t>
         </is>
       </c>
       <c r="I606" s="16" t="inlineStr">
@@ -47383,7 +47383,7 @@
       </c>
       <c r="L606" s="16" t="inlineStr">
         <is>
-          <t>Those two seem like total soulmates.</t>
+          <t>那兩個人真的像靈魂伴侶。</t>
         </is>
       </c>
       <c r="M606" s="16" t="inlineStr">
@@ -47440,7 +47440,7 @@
       </c>
       <c r="H607" s="16" t="inlineStr">
         <is>
-          <t>A person's ideal type or preferred qualities in a romantic partner.</t>
+          <t>一個人心目中理想的戀愛對象條件或類型，理想型。</t>
         </is>
       </c>
       <c r="I607" s="16" t="inlineStr">
@@ -47460,7 +47460,7 @@
       </c>
       <c r="L607" s="16" t="inlineStr">
         <is>
-          <t>My ideal type is someone who laughs a lot.</t>
+          <t>我的理想型是很愛笑的人。</t>
         </is>
       </c>
       <c r="M607" s="16" t="inlineStr">
@@ -47517,7 +47517,7 @@
       </c>
       <c r="H608" s="16" t="inlineStr">
         <is>
-          <t>"Ideal type World Cup" — a bracket-style elimination game where you repeatedly pick a favorite between two options.</t>
+          <t>「理想型世界盃」——透過兩兩淘汰的方式反覆選出最愛的錦標賽形式小遊戲。</t>
         </is>
       </c>
       <c r="I608" s="16" t="inlineStr">
@@ -47537,7 +47537,7 @@
       </c>
       <c r="L608" s="16" t="inlineStr">
         <is>
-          <t>I did the ideal-type bracket for my bias and they made it to the finals.</t>
+          <t>玩了本命的理想型世界盃，結果進到決賽了。</t>
         </is>
       </c>
       <c r="M608" s="16" t="inlineStr">
@@ -47594,7 +47594,7 @@
       </c>
       <c r="H609" s="16" t="inlineStr">
         <is>
-          <t>"Hot romance rumor" — a rumor or report that a celebrity is secretly dating someone.</t>
+          <t>「熱戀傳聞」——傳出藝人正在秘密交往的緋聞或報導。</t>
         </is>
       </c>
       <c r="I609" s="16" t="inlineStr">
@@ -47614,7 +47614,7 @@
       </c>
       <c r="L609" s="16" t="inlineStr">
         <is>
-          <t>Did you see the article about the dating rumor breaking?</t>
+          <t>你看到那則戀愛緋聞爆出的新聞了嗎？</t>
         </is>
       </c>
       <c r="M609" s="16" t="inlineStr">
@@ -47671,7 +47671,7 @@
       </c>
       <c r="H610" s="16" t="inlineStr">
         <is>
-          <t>"Love line" — the romantic pairing or storyline within a show.</t>
+          <t>「愛情線」——一部作品中的戀愛配對或感情發展劇情線。</t>
         </is>
       </c>
       <c r="I610" s="16" t="inlineStr">
@@ -47691,7 +47691,7 @@
       </c>
       <c r="L610" s="16" t="inlineStr">
         <is>
-          <t>This season's romance storyline is what I'm most excited for.</t>
+          <t>這季最期待的就是感情線發展。</t>
         </is>
       </c>
       <c r="M610" s="16" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H611" s="16" t="inlineStr">
         <is>
-          <t>"Coupling" — fans pairing up two characters or idols as a romantic match, whether canon or imagined.</t>
+          <t>粉絲將兩個角色或偶像配成一對的戀愛想像，無論是官方認證還是純粉絲腦補。</t>
         </is>
       </c>
       <c r="I611" s="16" t="inlineStr">
@@ -47768,7 +47768,7 @@
       </c>
       <c r="L611" s="16" t="inlineStr">
         <is>
-          <t>This pairing is really popular among fans.</t>
+          <t>這對CP真的超受歡迎。</t>
         </is>
       </c>
       <c r="M611" s="16" t="inlineStr">
@@ -47825,7 +47825,7 @@
       </c>
       <c r="H612" s="16" t="inlineStr">
         <is>
-          <t>Short for "paired-off guy" — the guy someone has a crush on.</t>
+          <t>「配對男」的簡稱——某人暗戀、有好感的男生。</t>
         </is>
       </c>
       <c r="I612" s="16" t="inlineStr">
@@ -47845,7 +47845,7 @@
       </c>
       <c r="L612" s="16" t="inlineStr">
         <is>
-          <t>I totally froze up in front of my crush.</t>
+          <t>在喜歡的男生面前完全僵住了。</t>
         </is>
       </c>
       <c r="M612" s="16" t="inlineStr">
@@ -47902,7 +47902,7 @@
       </c>
       <c r="H613" s="16" t="inlineStr">
         <is>
-          <t>Short for "paired-off girl" — the girl someone has a crush on.</t>
+          <t>「配對女」的簡稱——某人暗戀、有好感的女生。</t>
         </is>
       </c>
       <c r="I613" s="16" t="inlineStr">
@@ -47922,7 +47922,7 @@
       </c>
       <c r="L613" s="16" t="inlineStr">
         <is>
-          <t>I'm stressing over how to talk to my crush.</t>
+          <t>煩惱要怎麼跟喜歡的女生搭話。</t>
         </is>
       </c>
       <c r="M613" s="16" t="inlineStr">
@@ -47979,7 +47979,7 @@
       </c>
       <c r="H614" s="16" t="inlineStr">
         <is>
-          <t>"Dash" — making a romantic move on someone, like asking them out.</t>
+          <t>主動採取行動追求某人，例如開口邀約，主動出擊。</t>
         </is>
       </c>
       <c r="I614" s="16" t="inlineStr">
@@ -47999,7 +47999,7 @@
       </c>
       <c r="L614" s="16" t="inlineStr">
         <is>
-          <t>I finally made a move!</t>
+          <t>終於主動出擊了！</t>
         </is>
       </c>
       <c r="M614" s="16" t="inlineStr">
@@ -48056,7 +48056,7 @@
       </c>
       <c r="H615" s="16" t="inlineStr">
         <is>
-          <t>"After" — a follow-up date arranged after an initial blind date.</t>
+          <t>相親後安排的後續約會。</t>
         </is>
       </c>
       <c r="I615" s="16" t="inlineStr">
@@ -48076,7 +48076,7 @@
       </c>
       <c r="L615" s="16" t="inlineStr">
         <is>
-          <t>I got asked for a follow-up date after the blind date.</t>
+          <t>相親後收到了續攤約會的邀約。</t>
         </is>
       </c>
       <c r="M615" s="16" t="inlineStr">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="H616" s="16" t="inlineStr">
         <is>
-          <t>"Green light" — a signal that someone is romantically interested and open to being pursued.</t>
+          <t>「綠燈」——表示對方對你有意思、可以繼續追求的訊號。</t>
         </is>
       </c>
       <c r="I616" s="16" t="inlineStr">
@@ -48153,7 +48153,7 @@
       </c>
       <c r="L616" s="16" t="inlineStr">
         <is>
-          <t>Isn't that a total green light?</t>
+          <t>那不完全是綠燈訊號嗎？</t>
         </is>
       </c>
       <c r="M616" s="16" t="inlineStr">
@@ -48210,7 +48210,7 @@
       </c>
       <c r="H617" s="16" t="inlineStr">
         <is>
-          <t>Describes a warm, wholesome, feel-good atmosphere or moment — or a warmly attractive appearance.</t>
+          <t>形容溫暖、樸實、讓人感覺舒服的氛圍或瞬間，也可形容外表溫暖有魅力。</t>
         </is>
       </c>
       <c r="I617" s="16" t="inlineStr">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="L617" s="16" t="inlineStr">
         <is>
-          <t>Check out this warm, feel-good story.</t>
+          <t>看看這則暖心的故事。</t>
         </is>
       </c>
       <c r="M617" s="16" t="inlineStr">
@@ -48287,7 +48287,7 @@
       </c>
       <c r="H618" s="16" t="inlineStr">
         <is>
-          <t>The ending of a romantic relationship.</t>
+          <t>一段戀愛關係的結束，分手。</t>
         </is>
       </c>
       <c r="I618" s="16" t="inlineStr">
@@ -48307,7 +48307,7 @@
       </c>
       <c r="L618" s="16" t="inlineStr">
         <is>
-          <t>I had a hard time for a while after the breakup.</t>
+          <t>分手後有一陣子過得很辛苦。</t>
         </is>
       </c>
       <c r="M618" s="16" t="inlineStr">
@@ -48364,7 +48364,7 @@
       </c>
       <c r="H619" s="16" t="inlineStr">
         <is>
-          <t>"Bear + girlfriend," a term for a girlfriend patiently waiting for her boyfriend to complete mandatory military service.</t>
+          <t>「熊＋女友」——耐心等待男友服完兵役的女友暱稱。</t>
         </is>
       </c>
       <c r="I619" s="16" t="inlineStr">
@@ -48384,7 +48384,7 @@
       </c>
       <c r="L619" s="16" t="inlineStr">
         <is>
-          <t>I only have six months left of being a waiting girlfriend.</t>
+          <t>熊女友生活還剩六個月了。</t>
         </is>
       </c>
       <c r="M619" s="16" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H620" s="16" t="inlineStr">
         <is>
-          <t>A romantic relationship where the couple lives far apart from each other.</t>
+          <t>情侶分隔兩地、住得很遠的戀愛關係，遠距離戀愛。</t>
         </is>
       </c>
       <c r="I620" s="16" t="inlineStr">
@@ -48461,7 +48461,7 @@
       </c>
       <c r="L620" s="16" t="inlineStr">
         <is>
-          <t>Long-distance is hard, but we're holding up well.</t>
+          <t>遠距離戀愛雖然辛苦，但撐得很好。</t>
         </is>
       </c>
       <c r="M620" s="16" t="inlineStr">
@@ -48518,7 +48518,7 @@
       </c>
       <c r="H621" s="16" t="inlineStr">
         <is>
-          <t>A phase in a relationship marked by boredom or waning excitement.</t>
+          <t>感情中出現無聊感或熱情消退的階段，倦怠期。</t>
         </is>
       </c>
       <c r="I621" s="16" t="inlineStr">
@@ -48538,7 +48538,7 @@
       </c>
       <c r="L621" s="16" t="inlineStr">
         <is>
-          <t>I think we're going through a relationship rut lately.</t>
+          <t>我們最近好像進入倦怠期了。</t>
         </is>
       </c>
       <c r="M621" s="16" t="inlineStr">
@@ -48595,7 +48595,7 @@
       </c>
       <c r="H622" s="16" t="inlineStr">
         <is>
-          <t>A relationship where one partner is noticeably older (연상) and the other younger (연하) — a common K-drama dynamic.</t>
+          <t>一方明顯年長（연상）、另一方較年輕（연하）的戀愛關係——韓劇常見的組合。</t>
         </is>
       </c>
       <c r="I622" s="16" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="L622" s="16" t="inlineStr">
         <is>
-          <t>This drama has an age-gap couple.</t>
+          <t>這部劇是姊弟戀組合。</t>
         </is>
       </c>
       <c r="M622" s="16" t="inlineStr">
@@ -48672,7 +48672,7 @@
       </c>
       <c r="H623" s="16" t="inlineStr">
         <is>
-          <t>"Romantasy" — a hugely popular web novel and webtoon genre blending romance with a fantasy setting, often featuring reincarnation.</t>
+          <t>「浪漫奇幻」——結合戀愛與奇幻背景設定、常帶有轉生元素的超人氣網路小說與網漫類型。</t>
         </is>
       </c>
       <c r="I623" s="16" t="inlineStr">
@@ -48692,7 +48692,7 @@
       </c>
       <c r="L623" s="16" t="inlineStr">
         <is>
-          <t>I've totally fallen into romance-fantasy webtoons lately.</t>
+          <t>最近完全沉迷浪漫奇幻網漫。</t>
         </is>
       </c>
       <c r="M623" s="16" t="inlineStr">
@@ -48749,7 +48749,7 @@
       </c>
       <c r="H624" s="16" t="inlineStr">
         <is>
-          <t>"Longing illness" — being so consumed by romantic longing for someone that it feels like a sickness.</t>
+          <t>「思念之病」——被對某人的思念淹沒到彷彿生病一般，相思病。</t>
         </is>
       </c>
       <c r="I624" s="16" t="inlineStr">
@@ -48769,7 +48769,7 @@
       </c>
       <c r="L624" s="16" t="inlineStr">
         <is>
-          <t>I think I've totally caught lovesickness.</t>
+          <t>我好像得了相思病。</t>
         </is>
       </c>
       <c r="M624" s="16" t="inlineStr">
@@ -48826,7 +48826,7 @@
       </c>
       <c r="H625" s="16" t="inlineStr">
         <is>
-          <t>Falling in love with someone the very first moment you see them.</t>
+          <t>第一眼看到某人就墜入愛河，一見鍾情。</t>
         </is>
       </c>
       <c r="I625" s="16" t="inlineStr">
@@ -48846,7 +48846,7 @@
       </c>
       <c r="L625" s="16" t="inlineStr">
         <is>
-          <t>I finally understand what love at first sight feels like.</t>
+          <t>現在終於懂一見鍾情是什麼感覺了。</t>
         </is>
       </c>
       <c r="M625" s="16" t="inlineStr">
@@ -48903,7 +48903,7 @@
       </c>
       <c r="H626" s="16" t="inlineStr">
         <is>
-          <t>Confessing romantic feelings to someone.</t>
+          <t>向某人表白自己的戀愛心意，告白。</t>
         </is>
       </c>
       <c r="I626" s="16" t="inlineStr">
@@ -48923,7 +48923,7 @@
       </c>
       <c r="L626" s="16" t="inlineStr">
         <is>
-          <t>I finally confessed my feelings!</t>
+          <t>終於告白了！</t>
         </is>
       </c>
       <c r="M626" s="16" t="inlineStr">
@@ -48980,7 +48980,7 @@
       </c>
       <c r="H627" s="16" t="inlineStr">
         <is>
-          <t>"Date course" — a planned sequence of activities and locations for a date.</t>
+          <t>事先規劃好的約會活動與地點行程，約會行程。</t>
         </is>
       </c>
       <c r="I627" s="16" t="inlineStr">
@@ -49000,7 +49000,7 @@
       </c>
       <c r="L627" s="16" t="inlineStr">
         <is>
-          <t>I already planned out the whole date itinerary.</t>
+          <t>已經規劃好整個約會行程了。</t>
         </is>
       </c>
       <c r="M627" s="16" t="inlineStr">
@@ -49057,7 +49057,7 @@
       </c>
       <c r="H628" s="16" t="inlineStr">
         <is>
-          <t>The 100-day relationship milestone, commonly celebrated by Korean couples.</t>
+          <t>韓國情侶常慶祝的交往一百天紀念日。</t>
         </is>
       </c>
       <c r="I628" s="16" t="inlineStr">
@@ -49077,7 +49077,7 @@
       </c>
       <c r="L628" s="16" t="inlineStr">
         <is>
-          <t>This week is our 100-day anniversary, so I prepared a gift.</t>
+          <t>這禮拜是百日紀念，準備了禮物。</t>
         </is>
       </c>
       <c r="M628" s="16" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H629" s="16" t="inlineStr">
         <is>
-          <t>"Romance cells" — one's inner drive or interest in dating and romance.</t>
+          <t>「戀愛細胞」——一個人對談戀愛、交往的內在動力或興趣。</t>
         </is>
       </c>
       <c r="I629" s="16" t="inlineStr">
@@ -49154,7 +49154,7 @@
       </c>
       <c r="L629" s="16" t="inlineStr">
         <is>
-          <t>I feel like my romance drive has completely died.</t>
+          <t>感覺我的戀愛細胞都死光了。</t>
         </is>
       </c>
       <c r="M629" s="16" t="inlineStr">
@@ -49211,7 +49211,7 @@
       </c>
       <c r="H630" s="16" t="inlineStr">
         <is>
-          <t>"Pure-love comic" — a genre label for sweet, innocent romance stories, often used to describe an idealized real-life romance.</t>
+          <t>「純愛漫畫」——形容甜美、純真的戀愛故事類型，也用來形容如漫畫般理想化的真實戀情。</t>
         </is>
       </c>
       <c r="I630" s="16" t="inlineStr">
@@ -49231,7 +49231,7 @@
       </c>
       <c r="L630" s="16" t="inlineStr">
         <is>
-          <t>That couple is literally a pure-love comic come to life.</t>
+          <t>那對情侶完全就是純愛漫畫本人。</t>
         </is>
       </c>
       <c r="M630" s="16" t="inlineStr">
@@ -49288,7 +49288,7 @@
       </c>
       <c r="H631" s="16" t="inlineStr">
         <is>
-          <t>"Heart sniper" — something that strikes directly at your heart, usually describing a romantic or swoon-worthy moment.</t>
+          <t>「心臟狙擊」——直接命中內心、通常用來形容浪漫或令人心動的瞬間。</t>
         </is>
       </c>
       <c r="I631" s="16" t="inlineStr">
@@ -49308,7 +49308,7 @@
       </c>
       <c r="L631" s="16" t="inlineStr">
         <is>
-          <t>That line was a total heart sniper.</t>
+          <t>那句台詞完全是心臟狙擊。</t>
         </is>
       </c>
       <c r="M631" s="16" t="inlineStr">
@@ -49365,7 +49365,7 @@
       </c>
       <c r="H632" s="16" t="inlineStr">
         <is>
-          <t>Deliberately cute, affectionate speech or behavior — a cutesy voice, pouty expressions, or playful gestures used to charm someone.</t>
+          <t>刻意展現可愛、撒嬌的言行——嗲聲嗲氣、嘟嘴或俏皮動作，用來討人喜歡，撒嬌。</t>
         </is>
       </c>
       <c r="I632" s="16" t="inlineStr">
@@ -49385,7 +49385,7 @@
       </c>
       <c r="L632" s="16" t="inlineStr">
         <is>
-          <t>Do some aegyo for me!</t>
+          <t>撒嬌一下嘛！</t>
         </is>
       </c>
       <c r="M632" s="16" t="inlineStr">
@@ -49442,7 +49442,7 @@
       </c>
       <c r="H633" s="16" t="inlineStr">
         <is>
-          <t>"Love expert" — someone devotedly romantic who dotes openly on their partner.</t>
+          <t>「愛情達人」——全心全意投入戀愛、公開寵愛另一半的人。</t>
         </is>
       </c>
       <c r="I633" s="16" t="inlineStr">
@@ -49462,7 +49462,7 @@
       </c>
       <c r="L633" s="16" t="inlineStr">
         <is>
-          <t>That person is a total devoted romantic.</t>
+          <t>那個人完全是寵愛型戀人。</t>
         </is>
       </c>
       <c r="M633" s="16" t="inlineStr">
@@ -49519,7 +49519,7 @@
       </c>
       <c r="H634" s="16" t="inlineStr">
         <is>
-          <t>"Lovebird couple" — a married couple who are openly and consistently affectionate with each other.</t>
+          <t>「鴛鴦夫妻」——公開且持續展現親密恩愛的夫妻，恩愛夫妻。</t>
         </is>
       </c>
       <c r="I634" s="16" t="inlineStr">
@@ -49539,7 +49539,7 @@
       </c>
       <c r="L634" s="16" t="inlineStr">
         <is>
-          <t>That couple is total lovebirds.</t>
+          <t>那對夫妻完全是恩愛夫妻。</t>
         </is>
       </c>
       <c r="M634" s="16" t="inlineStr">
@@ -49596,7 +49596,7 @@
       </c>
       <c r="H635" s="16" t="inlineStr">
         <is>
-          <t>"Boyfriend look" — a fashion style mimicking oversized, borrowed-looking boyfriend clothing.</t>
+          <t>「男友風」——模仿男友寬鬆、彷彿借穿男友衣服的穿搭風格。</t>
         </is>
       </c>
       <c r="I635" s="16" t="inlineStr">
@@ -49616,7 +49616,7 @@
       </c>
       <c r="L635" s="16" t="inlineStr">
         <is>
-          <t>I tried out the boyfriend-look style today.</t>
+          <t>今天試了男友風穿搭。</t>
         </is>
       </c>
       <c r="M635" s="16" t="inlineStr">
@@ -49673,7 +49673,7 @@
       </c>
       <c r="H636" s="16" t="inlineStr">
         <is>
-          <t>"Marriage angle" — signs or vibes suggesting a couple might be headed toward marriage.</t>
+          <t>「結婚角度」——顯示一對情侶可能正朝向結婚發展的跡象或氛圍。</t>
         </is>
       </c>
       <c r="I636" s="16" t="inlineStr">
@@ -49693,7 +49693,7 @@
       </c>
       <c r="L636" s="16" t="inlineStr">
         <is>
-          <t>Those two have total marriage vibes.</t>
+          <t>兩人完全有結婚跡象。</t>
         </is>
       </c>
       <c r="M636" s="16" t="inlineStr">
@@ -49750,7 +49750,7 @@
       </c>
       <c r="H637" s="16" t="inlineStr">
         <is>
-          <t>"Currently in a hot romance" — actively dating someone, often used in celebrity news.</t>
+          <t>「熱戀中」——正在積極交往中，常用於藝人新聞報導。</t>
         </is>
       </c>
       <c r="I637" s="16" t="inlineStr">
@@ -49770,7 +49770,7 @@
       </c>
       <c r="L637" s="16" t="inlineStr">
         <is>
-          <t>An article came out saying the two of them are dating.</t>
+          <t>有報導說兩人正在熱戀中。</t>
         </is>
       </c>
       <c r="M637" s="16" t="inlineStr">
@@ -49827,7 +49827,7 @@
       </c>
       <c r="H638" s="16" t="inlineStr">
         <is>
-          <t>"Escaping single life" — finally entering a relationship after being single for a while.</t>
+          <t>「逃離單身」——經過一段單身期後終於進入一段感情，脫單。</t>
         </is>
       </c>
       <c r="I638" s="16" t="inlineStr">
@@ -49847,7 +49847,7 @@
       </c>
       <c r="L638" s="16" t="inlineStr">
         <is>
-          <t>I finally escaped single life!</t>
+          <t>終於脫單了！</t>
         </is>
       </c>
       <c r="M638" s="16" t="inlineStr">
@@ -49904,7 +49904,7 @@
       </c>
       <c r="H639" s="16" t="inlineStr">
         <is>
-          <t>Someone skilled and experienced at romance and relationships.</t>
+          <t>在感情與戀愛方面經驗豐富、技巧熟練的人，戀愛高手。</t>
         </is>
       </c>
       <c r="I639" s="16" t="inlineStr">
@@ -49924,7 +49924,7 @@
       </c>
       <c r="L639" s="16" t="inlineStr">
         <is>
-          <t>That person is a real dating master.</t>
+          <t>那個人真的是戀愛高手。</t>
         </is>
       </c>
       <c r="M639" s="16" t="inlineStr">
@@ -49981,7 +49981,7 @@
       </c>
       <c r="H640" s="16" t="inlineStr">
         <is>
-          <t>Openly expressing affection toward a partner, whether verbally or physically.</t>
+          <t>無論是言語或肢體上，公開向伴侶表達愛意。</t>
         </is>
       </c>
       <c r="I640" s="16" t="inlineStr">
@@ -50001,7 +50001,7 @@
       </c>
       <c r="L640" s="16" t="inlineStr">
         <is>
-          <t>Those two show a lot of affection toward each other.</t>
+          <t>兩個人真的很常表達愛意。</t>
         </is>
       </c>
       <c r="M640" s="16" t="inlineStr">
@@ -50058,7 +50058,7 @@
       </c>
       <c r="H641" s="16" t="inlineStr">
         <is>
-          <t>A cute, informal term for a significant other or a close paired friend.</t>
+          <t>對另一半或親密好友的可愛、非正式稱呼。</t>
         </is>
       </c>
       <c r="I641" s="16" t="inlineStr">
@@ -50078,7 +50078,7 @@
       </c>
       <c r="L641" s="16" t="inlineStr">
         <is>
-          <t>I just came back from a date with my sweetheart.</t>
+          <t>剛跟我的另一半約會回來。</t>
         </is>
       </c>
       <c r="M641" s="16" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="H642" s="16" t="inlineStr">
         <is>
-          <t>A cute expression describing a couple being sweetly, playfully affectionate together.</t>
+          <t>形容一對情侶甜蜜、俏皮地相處，甜甜蜜蜜。</t>
         </is>
       </c>
       <c r="I642" s="16" t="inlineStr">
@@ -50155,7 +50155,7 @@
       </c>
       <c r="L642" s="16" t="inlineStr">
         <is>
-          <t>The two of them are doing well, all sweet and lovey-dovey.</t>
+          <t>兩個人甜甜蜜蜜地過得很好。</t>
         </is>
       </c>
       <c r="M642" s="16" t="inlineStr">
@@ -50212,7 +50212,7 @@
       </c>
       <c r="H643" s="16" t="inlineStr">
         <is>
-          <t>"Pink-tinted" — describes a romantic, love-filled mood or atmosphere.</t>
+          <t>「粉紅色調」——形容浪漫、充滿愛意的氛圍或心情。</t>
         </is>
       </c>
       <c r="I643" s="16" t="inlineStr">
@@ -50232,7 +50232,7 @@
       </c>
       <c r="L643" s="16" t="inlineStr">
         <is>
-          <t>There's a rosy romantic vibe flowing between the two of them.</t>
+          <t>兩人之間流動著粉紅氛圍。</t>
         </is>
       </c>
       <c r="M643" s="16" t="inlineStr">
@@ -50289,7 +50289,7 @@
       </c>
       <c r="H644" s="16" t="inlineStr">
         <is>
-          <t>The emotional aftereffects that linger after a relationship ends.</t>
+          <t>一段感情結束後持續存在的情緒後遺症，分手後遺症。</t>
         </is>
       </c>
       <c r="I644" s="16" t="inlineStr">
@@ -50309,7 +50309,7 @@
       </c>
       <c r="L644" s="16" t="inlineStr">
         <is>
-          <t>The breakup aftermath lasted longer than I expected.</t>
+          <t>分手後遺症比想像中持續更久。</t>
         </is>
       </c>
       <c r="M644" s="16" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="H645" s="16" t="inlineStr">
         <is>
-          <t>"Romance front line" — a weather-front-style metaphor for the current state of someone's love life.</t>
+          <t>「戀愛前線」——借用天氣鋒面概念，比喻某人目前的感情狀態。</t>
         </is>
       </c>
       <c r="I645" s="16" t="inlineStr">
@@ -50386,7 +50386,7 @@
       </c>
       <c r="L645" s="16" t="inlineStr">
         <is>
-          <t>How's your love life going these days?</t>
+          <t>最近戀愛前線如何？</t>
         </is>
       </c>
       <c r="M645" s="16" t="inlineStr">
@@ -50443,7 +50443,7 @@
       </c>
       <c r="H646" s="16" t="inlineStr">
         <is>
-          <t>Video content a couple makes together documenting their relationship and daily life.</t>
+          <t>情侶一起拍攝、記錄兩人關係與日常生活的影片內容。</t>
         </is>
       </c>
       <c r="I646" s="16" t="inlineStr">
@@ -50463,7 +50463,7 @@
       </c>
       <c r="L646" s="16" t="inlineStr">
         <is>
-          <t>Watching this couple vlog makes me want to date too.</t>
+          <t>看這個情侶Vlog會讓人也想談戀愛。</t>
         </is>
       </c>
       <c r="M646" s="16" t="inlineStr">
@@ -50520,7 +50520,7 @@
       </c>
       <c r="H647" s="16" t="inlineStr">
         <is>
-          <t>The specific moment or detail that makes you fall for someone or feel butterflies.</t>
+          <t>讓你對某人心動、產生小鹿亂撞感覺的特定瞬間或細節，心動點。</t>
         </is>
       </c>
       <c r="I647" s="16" t="inlineStr">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="L647" s="16" t="inlineStr">
         <is>
-          <t>That smile was my heart-flutter moment.</t>
+          <t>那個微笑就是我的心動點。</t>
         </is>
       </c>
       <c r="M647" s="16" t="inlineStr">
@@ -50597,7 +50597,7 @@
       </c>
       <c r="H648" s="16" t="inlineStr">
         <is>
-          <t>The 1,000-day relationship milestone, a bigger version of the 100-day celebration.</t>
+          <t>交往滿一千天的紀念日，是百日紀念的加強版。</t>
         </is>
       </c>
       <c r="I648" s="16" t="inlineStr">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="L648" s="16" t="inlineStr">
         <is>
-          <t>Next month is our 1,000-day anniversary.</t>
+          <t>下個月是我們的千日紀念。</t>
         </is>
       </c>
       <c r="M648" s="16" t="inlineStr">
@@ -50674,7 +50674,7 @@
       </c>
       <c r="H649" s="16" t="inlineStr">
         <is>
-          <t>When a celebrity couple officially confirms they're dating, often via their agency.</t>
+          <t>名人情侶（常透過經紀公司）正式承認交往關係，承認戀情。</t>
         </is>
       </c>
       <c r="I649" s="16" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="L649" s="16" t="inlineStr">
         <is>
-          <t>They finally confirmed the relationship!</t>
+          <t>最後承認戀情了！</t>
         </is>
       </c>
       <c r="M649" s="16" t="inlineStr">
@@ -50751,7 +50751,7 @@
       </c>
       <c r="H650" s="16" t="inlineStr">
         <is>
-          <t>Dating a coworker at the same company — a common drama trope.</t>
+          <t>與同公司同事交往，是韓劇常見的劇情套路，辦公室戀情。</t>
         </is>
       </c>
       <c r="I650" s="16" t="inlineStr">
@@ -50771,7 +50771,7 @@
       </c>
       <c r="L650" s="16" t="inlineStr">
         <is>
-          <t>This drama's workplace romance storyline is so exciting.</t>
+          <t>這部劇的辦公室戀情發展真的很讓人心動。</t>
         </is>
       </c>
       <c r="M650" s="16" t="inlineStr">
@@ -50828,7 +50828,7 @@
       </c>
       <c r="H651" s="16" t="inlineStr">
         <is>
-          <t>"Burning blind date" — a blind date with intense, immediate chemistry or spark.</t>
+          <t>「燃燒的相親」——雙方一見面就火花四射、氣氛熱烈的相親。</t>
         </is>
       </c>
       <c r="I651" s="16" t="inlineStr">
@@ -50848,7 +50848,7 @@
       </c>
       <c r="L651" s="16" t="inlineStr">
         <is>
-          <t>I heard there's a fiery blind date lined up this week, I'm excited.</t>
+          <t>聽說這禮拜安排了火花四射的相親，好期待。</t>
         </is>
       </c>
       <c r="M651" s="16" t="inlineStr">
@@ -50905,7 +50905,7 @@
       </c>
       <c r="H652" s="16" t="inlineStr">
         <is>
-          <t>Short for "fashion is completed by the face" — a saying that a good-looking face elevates any outfit, no matter how simple.</t>
+          <t>「時尚的完成是臉」的簡稱——意指帥氣或漂亮的長相能撐起任何穿搭。</t>
         </is>
       </c>
       <c r="I652" s="16" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="L652" s="16" t="inlineStr">
         <is>
-          <t>It's true, fashion's finished by the face — they look good in anything.</t>
+          <t>果然臉才是關鍵，穿什麼都好看。</t>
         </is>
       </c>
       <c r="M652" s="16" t="inlineStr">

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$Q$652</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$652</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$652</definedName>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="S130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="S131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="S132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="S133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="S134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="S135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="S137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="S138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="S139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="S140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="S141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="S142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="S143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="S144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="S145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="S146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="S147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="S149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="S150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="S151" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S152" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S153" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="S154" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="S155" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="S156" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="S157" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S158" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="S159" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S160" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="S161" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="S162" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="S163" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="S164" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="S165" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="S166" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="S167" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="S168" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="S169" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="S170" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="S171" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="S172" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="S173" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="S174" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="S175" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="S176" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="S177" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="S178" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="S179" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="S180" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="S181" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="S182" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="S183" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="S184" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="S185" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="S186" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="S187" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="S188" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="S189" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="S190" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="S191" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S192" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="S193" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="S194" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="S195" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="S196" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="S197" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="S198" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S199" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="S200" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="S201" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="S202" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S203" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="S205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="S206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="S209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="S210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="S211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="S212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="S213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="S214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="S215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="S216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="S217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="S218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="S219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="S220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="S221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="S222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="S223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="S224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="S225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="S226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="S227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -22953,7 +22953,7 @@
       </c>
       <c r="S229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="S230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="S231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="S232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="S233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23438,7 +23438,7 @@
       </c>
       <c r="S234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="S236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="S237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="S238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
       </c>
       <c r="S239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="S241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="S242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="S244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="S245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="S246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24699,7 +24699,7 @@
       </c>
       <c r="S247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="S248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="S249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="S250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="S251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25184,7 @@
       </c>
       <c r="S252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="S253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="S254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="S255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="S256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="S258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="S260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="S261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="S262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="S263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="S264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="S265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="S266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="S267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
       </c>
       <c r="S268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26833,7 +26833,7 @@
       </c>
       <c r="S269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="S270" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="S271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="S272" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="S273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="S274" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="S275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
       </c>
       <c r="S276" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="S277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="S278" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="S279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27900,7 @@
       </c>
       <c r="S280" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="S281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="S282" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="S283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S284" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="S285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="S286" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="S287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="S288" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
       </c>
       <c r="S289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S290" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="S291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="S292" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="S293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="S294" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="S295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29452,7 @@
       </c>
       <c r="S296" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="S297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="S298" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="S299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="S300" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="S301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="S302" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="S303" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30228,7 +30228,7 @@
       </c>
       <c r="S304" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30325,7 @@
       </c>
       <c r="S305" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="S306" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S307" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="S308" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="S309" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="S310" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="S311" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="S312" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31101,7 +31101,7 @@
       </c>
       <c r="S313" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31198,7 @@
       </c>
       <c r="S314" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31295,7 @@
       </c>
       <c r="S315" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="S316" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="S317" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31586,7 @@
       </c>
       <c r="S318" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="S319" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="S320" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="S321" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="S322" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="S323" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32168,7 @@
       </c>
       <c r="S324" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="S325" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="S326" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
       </c>
       <c r="S327" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="S328" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="S329" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="S330" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="S331" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="S332" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="S333" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S334" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="S335" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="S336" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
       </c>
       <c r="S337" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="S338" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33623,7 +33623,7 @@
       </c>
       <c r="S339" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="S340" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="S341" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="S342" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S343" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34108,7 @@
       </c>
       <c r="S344" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="S345" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="S346" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34399,7 +34399,7 @@
       </c>
       <c r="S347" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="S348" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34593,7 +34593,7 @@
       </c>
       <c r="S349" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34690,7 +34690,7 @@
       </c>
       <c r="S350" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="S351" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="S352" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="S353" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="S354" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="S355" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35272,7 +35272,7 @@
       </c>
       <c r="S356" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="S357" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35466,7 @@
       </c>
       <c r="S358" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35563,7 +35563,7 @@
       </c>
       <c r="S359" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="S360" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35757,7 +35757,7 @@
       </c>
       <c r="S361" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35854,7 +35854,7 @@
       </c>
       <c r="S362" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="S363" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36048,7 +36048,7 @@
       </c>
       <c r="S364" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36145,7 +36145,7 @@
       </c>
       <c r="S365" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="S366" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36339,7 +36339,7 @@
       </c>
       <c r="S367" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="S368" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="S369" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36630,7 +36630,7 @@
       </c>
       <c r="S370" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36727,7 +36727,7 @@
       </c>
       <c r="S371" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36824,7 +36824,7 @@
       </c>
       <c r="S372" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="S373" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37018,7 +37018,7 @@
       </c>
       <c r="S374" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="S375" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="S376" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37309,7 @@
       </c>
       <c r="S377" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S378" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="S379" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="S380" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="S381" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37794,7 +37794,7 @@
       </c>
       <c r="S382" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="S383" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -37988,7 +37988,7 @@
       </c>
       <c r="S384" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38085,7 +38085,7 @@
       </c>
       <c r="S385" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38182,7 +38182,7 @@
       </c>
       <c r="S386" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="S387" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="S388" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38473,7 +38473,7 @@
       </c>
       <c r="S389" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38570,7 +38570,7 @@
       </c>
       <c r="S390" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
       </c>
       <c r="S391" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="S392" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="S393" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -38958,7 +38958,7 @@
       </c>
       <c r="S394" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39055,7 +39055,7 @@
       </c>
       <c r="S395" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39152,7 +39152,7 @@
       </c>
       <c r="S396" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
       </c>
       <c r="S397" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39346,7 +39346,7 @@
       </c>
       <c r="S398" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39443,7 +39443,7 @@
       </c>
       <c r="S399" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="S400" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="S401" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="S402" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="S403" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="S404" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40025,7 +40025,7 @@
       </c>
       <c r="S405" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="S406" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40219,7 @@
       </c>
       <c r="S407" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="S408" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40413,7 +40413,7 @@
       </c>
       <c r="S409" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40510,7 +40510,7 @@
       </c>
       <c r="S410" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="S411" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40704,7 +40704,7 @@
       </c>
       <c r="S412" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S413" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="S414" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40995,7 +40995,7 @@
       </c>
       <c r="S415" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="S416" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="S417" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41286,7 +41286,7 @@
       </c>
       <c r="S418" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41383,7 @@
       </c>
       <c r="S419" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="S420" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41577,7 +41577,7 @@
       </c>
       <c r="S421" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41674,7 +41674,7 @@
       </c>
       <c r="S422" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41771,7 +41771,7 @@
       </c>
       <c r="S423" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41868,7 +41868,7 @@
       </c>
       <c r="S424" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S425" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="S426" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="S427" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="S428" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42353,7 +42353,7 @@
       </c>
       <c r="S429" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42450,7 +42450,7 @@
       </c>
       <c r="S430" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42547,7 +42547,7 @@
       </c>
       <c r="S431" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42644,7 +42644,7 @@
       </c>
       <c r="S432" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42741,7 +42741,7 @@
       </c>
       <c r="S433" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42838,7 +42838,7 @@
       </c>
       <c r="S434" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -42935,7 +42935,7 @@
       </c>
       <c r="S435" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43032,7 +43032,7 @@
       </c>
       <c r="S436" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="S437" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="S438" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="S439" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43420,7 +43420,7 @@
       </c>
       <c r="S440" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43517,7 @@
       </c>
       <c r="S441" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="S442" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43711,7 @@
       </c>
       <c r="S443" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43808,7 +43808,7 @@
       </c>
       <c r="S444" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -43905,7 +43905,7 @@
       </c>
       <c r="S445" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44002,7 +44002,7 @@
       </c>
       <c r="S446" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44099,7 @@
       </c>
       <c r="S447" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44196,7 +44196,7 @@
       </c>
       <c r="S448" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44293,7 +44293,7 @@
       </c>
       <c r="S449" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44390,7 +44390,7 @@
       </c>
       <c r="S450" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="S451" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="S452" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44681,7 +44681,7 @@
       </c>
       <c r="S453" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="S454" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44875,7 +44875,7 @@
       </c>
       <c r="S455" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -44972,7 +44972,7 @@
       </c>
       <c r="S456" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
       </c>
       <c r="S457" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45166,7 +45166,7 @@
       </c>
       <c r="S458" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45263,7 +45263,7 @@
       </c>
       <c r="S459" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="S460" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45457,7 +45457,7 @@
       </c>
       <c r="S461" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45554,7 +45554,7 @@
       </c>
       <c r="S462" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="S463" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="S464" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="S465" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45942,7 +45942,7 @@
       </c>
       <c r="S466" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46039,7 +46039,7 @@
       </c>
       <c r="S467" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46136,7 +46136,7 @@
       </c>
       <c r="S468" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="S469" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46330,7 +46330,7 @@
       </c>
       <c r="S470" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="S471" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46524,7 +46524,7 @@
       </c>
       <c r="S472" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46621,7 +46621,7 @@
       </c>
       <c r="S473" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46718,7 +46718,7 @@
       </c>
       <c r="S474" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46815,7 +46815,7 @@
       </c>
       <c r="S475" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -46912,7 +46912,7 @@
       </c>
       <c r="S476" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47009,7 +47009,7 @@
       </c>
       <c r="S477" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47106,7 +47106,7 @@
       </c>
       <c r="S478" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47203,7 @@
       </c>
       <c r="S479" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S480" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="S481" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="S482" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47591,7 +47591,7 @@
       </c>
       <c r="S483" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47688,7 +47688,7 @@
       </c>
       <c r="S484" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47785,7 +47785,7 @@
       </c>
       <c r="S485" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="S486" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -47979,7 +47979,7 @@
       </c>
       <c r="S487" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="S488" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48173,7 +48173,7 @@
       </c>
       <c r="S489" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48270,7 +48270,7 @@
       </c>
       <c r="S490" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48367,7 +48367,7 @@
       </c>
       <c r="S491" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48464,7 +48464,7 @@
       </c>
       <c r="S492" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="S493" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48658,7 +48658,7 @@
       </c>
       <c r="S494" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="S495" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48852,7 +48852,7 @@
       </c>
       <c r="S496" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -48949,7 +48949,7 @@
       </c>
       <c r="S497" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49046,7 +49046,7 @@
       </c>
       <c r="S498" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49143,7 +49143,7 @@
       </c>
       <c r="S499" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49240,7 +49240,7 @@
       </c>
       <c r="S500" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49337,7 +49337,7 @@
       </c>
       <c r="S501" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49434,7 +49434,7 @@
       </c>
       <c r="S502" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49531,7 +49531,7 @@
       </c>
       <c r="S503" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49628,7 +49628,7 @@
       </c>
       <c r="S504" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49725,7 +49725,7 @@
       </c>
       <c r="S505" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49822,7 +49822,7 @@
       </c>
       <c r="S506" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -49919,7 +49919,7 @@
       </c>
       <c r="S507" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="S508" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50113,7 +50113,7 @@
       </c>
       <c r="S509" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50210,7 +50210,7 @@
       </c>
       <c r="S510" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50307,7 +50307,7 @@
       </c>
       <c r="S511" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50404,7 +50404,7 @@
       </c>
       <c r="S512" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50501,7 +50501,7 @@
       </c>
       <c r="S513" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50598,7 +50598,7 @@
       </c>
       <c r="S514" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50695,7 +50695,7 @@
       </c>
       <c r="S515" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S516" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50889,7 +50889,7 @@
       </c>
       <c r="S517" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -50986,7 +50986,7 @@
       </c>
       <c r="S518" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51083,7 +51083,7 @@
       </c>
       <c r="S519" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51180,7 +51180,7 @@
       </c>
       <c r="S520" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51277,7 +51277,7 @@
       </c>
       <c r="S521" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="S522" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="S523" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51568,7 +51568,7 @@
       </c>
       <c r="S524" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51665,7 +51665,7 @@
       </c>
       <c r="S525" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51762,7 +51762,7 @@
       </c>
       <c r="S526" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51859,7 +51859,7 @@
       </c>
       <c r="S527" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -51956,7 +51956,7 @@
       </c>
       <c r="S528" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="S529" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52150,7 +52150,7 @@
       </c>
       <c r="S530" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="S531" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="S532" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="S533" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52538,7 +52538,7 @@
       </c>
       <c r="S534" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="S535" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52732,7 +52732,7 @@
       </c>
       <c r="S536" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52829,7 +52829,7 @@
       </c>
       <c r="S537" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -52926,7 +52926,7 @@
       </c>
       <c r="S538" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53023,7 +53023,7 @@
       </c>
       <c r="S539" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53120,7 @@
       </c>
       <c r="S540" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53217,7 +53217,7 @@
       </c>
       <c r="S541" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53314,7 +53314,7 @@
       </c>
       <c r="S542" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53411,7 +53411,7 @@
       </c>
       <c r="S543" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53508,7 +53508,7 @@
       </c>
       <c r="S544" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53605,7 +53605,7 @@
       </c>
       <c r="S545" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53702,7 +53702,7 @@
       </c>
       <c r="S546" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53799,7 +53799,7 @@
       </c>
       <c r="S547" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53896,7 +53896,7 @@
       </c>
       <c r="S548" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -53993,7 +53993,7 @@
       </c>
       <c r="S549" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54090,7 @@
       </c>
       <c r="S550" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54187,7 +54187,7 @@
       </c>
       <c r="S551" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54284,7 +54284,7 @@
       </c>
       <c r="S552" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54381,7 +54381,7 @@
       </c>
       <c r="S553" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54478,7 +54478,7 @@
       </c>
       <c r="S554" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="S555" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="S556" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54769,7 +54769,7 @@
       </c>
       <c r="S557" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="S558" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -54963,7 +54963,7 @@
       </c>
       <c r="S559" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55060,7 +55060,7 @@
       </c>
       <c r="S560" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55157,7 +55157,7 @@
       </c>
       <c r="S561" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55254,7 @@
       </c>
       <c r="S562" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55351,7 +55351,7 @@
       </c>
       <c r="S563" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55448,7 +55448,7 @@
       </c>
       <c r="S564" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55545,7 +55545,7 @@
       </c>
       <c r="S565" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55642,7 +55642,7 @@
       </c>
       <c r="S566" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55739,7 +55739,7 @@
       </c>
       <c r="S567" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55836,7 +55836,7 @@
       </c>
       <c r="S568" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -55933,7 +55933,7 @@
       </c>
       <c r="S569" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56030,7 +56030,7 @@
       </c>
       <c r="S570" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56127,7 +56127,7 @@
       </c>
       <c r="S571" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56224,7 +56224,7 @@
       </c>
       <c r="S572" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56321,7 +56321,7 @@
       </c>
       <c r="S573" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56418,7 +56418,7 @@
       </c>
       <c r="S574" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56515,7 +56515,7 @@
       </c>
       <c r="S575" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56612,7 +56612,7 @@
       </c>
       <c r="S576" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56709,7 +56709,7 @@
       </c>
       <c r="S577" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S578" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -56903,7 +56903,7 @@
       </c>
       <c r="S579" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57000,7 +57000,7 @@
       </c>
       <c r="S580" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="S581" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57194,7 +57194,7 @@
       </c>
       <c r="S582" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57291,7 +57291,7 @@
       </c>
       <c r="S583" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="S584" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="S585" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57582,7 +57582,7 @@
       </c>
       <c r="S586" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57679,7 +57679,7 @@
       </c>
       <c r="S587" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57776,7 +57776,7 @@
       </c>
       <c r="S588" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57873,7 +57873,7 @@
       </c>
       <c r="S589" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -57970,7 +57970,7 @@
       </c>
       <c r="S590" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58067,7 +58067,7 @@
       </c>
       <c r="S591" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58164,7 +58164,7 @@
       </c>
       <c r="S592" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58261,7 +58261,7 @@
       </c>
       <c r="S593" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58358,7 +58358,7 @@
       </c>
       <c r="S594" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58455,7 +58455,7 @@
       </c>
       <c r="S595" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58552,7 +58552,7 @@
       </c>
       <c r="S596" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58649,7 +58649,7 @@
       </c>
       <c r="S597" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58746,7 +58746,7 @@
       </c>
       <c r="S598" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58843,7 +58843,7 @@
       </c>
       <c r="S599" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -58940,7 +58940,7 @@
       </c>
       <c r="S600" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="S601" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59134,7 +59134,7 @@
       </c>
       <c r="S602" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59231,7 +59231,7 @@
       </c>
       <c r="S603" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="S604" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59425,7 +59425,7 @@
       </c>
       <c r="S605" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="S606" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S607" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59716,7 +59716,7 @@
       </c>
       <c r="S608" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59813,7 +59813,7 @@
       </c>
       <c r="S609" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -59910,7 +59910,7 @@
       </c>
       <c r="S610" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60007,7 +60007,7 @@
       </c>
       <c r="S611" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60104,7 +60104,7 @@
       </c>
       <c r="S612" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60201,7 +60201,7 @@
       </c>
       <c r="S613" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S614" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60395,7 +60395,7 @@
       </c>
       <c r="S615" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60492,7 +60492,7 @@
       </c>
       <c r="S616" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60589,7 +60589,7 @@
       </c>
       <c r="S617" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60686,7 +60686,7 @@
       </c>
       <c r="S618" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60783,7 +60783,7 @@
       </c>
       <c r="S619" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60880,7 +60880,7 @@
       </c>
       <c r="S620" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -60977,7 +60977,7 @@
       </c>
       <c r="S621" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61074,7 +61074,7 @@
       </c>
       <c r="S622" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61171,7 +61171,7 @@
       </c>
       <c r="S623" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61268,7 +61268,7 @@
       </c>
       <c r="S624" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61365,7 +61365,7 @@
       </c>
       <c r="S625" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61462,7 +61462,7 @@
       </c>
       <c r="S626" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61559,7 +61559,7 @@
       </c>
       <c r="S627" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="S628" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61753,7 +61753,7 @@
       </c>
       <c r="S629" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61850,7 +61850,7 @@
       </c>
       <c r="S630" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -61947,7 +61947,7 @@
       </c>
       <c r="S631" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62044,7 +62044,7 @@
       </c>
       <c r="S632" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62141,7 +62141,7 @@
       </c>
       <c r="S633" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62238,7 +62238,7 @@
       </c>
       <c r="S634" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62335,7 +62335,7 @@
       </c>
       <c r="S635" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62432,7 +62432,7 @@
       </c>
       <c r="S636" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62529,7 +62529,7 @@
       </c>
       <c r="S637" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62626,7 +62626,7 @@
       </c>
       <c r="S638" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62723,7 +62723,7 @@
       </c>
       <c r="S639" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62820,7 +62820,7 @@
       </c>
       <c r="S640" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -62917,7 +62917,7 @@
       </c>
       <c r="S641" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63014,7 +63014,7 @@
       </c>
       <c r="S642" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63111,7 +63111,7 @@
       </c>
       <c r="S643" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63208,7 +63208,7 @@
       </c>
       <c r="S644" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63305,7 +63305,7 @@
       </c>
       <c r="S645" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63402,7 +63402,7 @@
       </c>
       <c r="S646" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63499,7 +63499,7 @@
       </c>
       <c r="S647" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="S648" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63693,7 +63693,7 @@
       </c>
       <c r="S649" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63790,7 @@
       </c>
       <c r="S650" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63887,7 +63887,7 @@
       </c>
       <c r="S651" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -63984,7 +63984,7 @@
       </c>
       <c r="S652" s="15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="S130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="S131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="S132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="S133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="S134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="S135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="S137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="S138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="S139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="S140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="S141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="S142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="S143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="S144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="S145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="S146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="S147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="S149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="S150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="S151" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S152" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S153" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="S154" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="S155" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="S156" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="S157" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S158" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="S159" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S160" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="S161" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="S162" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="S163" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="S164" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="S165" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="S166" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="S167" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="S168" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="S169" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="S170" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="S171" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="S172" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="S173" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="S174" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="S175" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="S176" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="S177" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="S178" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="S179" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="S180" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="S181" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="S182" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="S183" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="S184" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="S185" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="S186" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="S187" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="S188" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="S189" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="S190" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="S191" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S192" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="S193" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="S194" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="S195" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="S196" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="S197" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="S198" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S199" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="S200" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="S201" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="S202" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S203" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="S205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="S206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="S209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="S210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="S211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="S212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="S213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="S214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="S215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="S216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="S217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="S218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="S219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="S220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="S221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="S222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="S223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="S224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="S225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="S226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="S227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -22953,7 +22953,7 @@
       </c>
       <c r="S229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="S230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="S231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="S232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="S233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23438,7 +23438,7 @@
       </c>
       <c r="S234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="S236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="S237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="S238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
       </c>
       <c r="S239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="S241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="S242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="S244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="S245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="S246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24699,7 +24699,7 @@
       </c>
       <c r="S247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="S248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="S249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="S250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="S251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25184,7 @@
       </c>
       <c r="S252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="S253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="S254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="S255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="S256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="S258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="S260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="S261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="S262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="S263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="S264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="S265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="S266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="S267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
       </c>
       <c r="S268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26833,7 +26833,7 @@
       </c>
       <c r="S269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="S270" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="S271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="S272" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="S273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="S274" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="S275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
       </c>
       <c r="S276" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="S277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="S278" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="S279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27900,7 @@
       </c>
       <c r="S280" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="S281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="S282" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="S283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S284" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="S285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="S286" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="S287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="S288" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
       </c>
       <c r="S289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S290" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="S291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="S292" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="S293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="S294" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="S295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29452,7 @@
       </c>
       <c r="S296" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="S297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="S298" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="S299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="S300" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="S301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="S302" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="S303" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30228,7 +30228,7 @@
       </c>
       <c r="S304" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30325,7 @@
       </c>
       <c r="S305" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="S306" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S307" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="S308" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="S309" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="S310" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="S311" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="S312" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31101,7 +31101,7 @@
       </c>
       <c r="S313" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31198,7 @@
       </c>
       <c r="S314" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31295,7 @@
       </c>
       <c r="S315" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="S316" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="S317" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31586,7 @@
       </c>
       <c r="S318" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="S319" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="S320" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="S321" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="S322" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="S323" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32168,7 @@
       </c>
       <c r="S324" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="S325" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="S326" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
       </c>
       <c r="S327" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="S328" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="S329" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="S330" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="S331" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="S332" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="S333" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S334" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="S335" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="S336" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
       </c>
       <c r="S337" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="S338" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33623,7 +33623,7 @@
       </c>
       <c r="S339" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="S340" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="S341" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="S342" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S343" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34108,7 @@
       </c>
       <c r="S344" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="S345" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="S346" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34399,7 +34399,7 @@
       </c>
       <c r="S347" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="S348" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34593,7 +34593,7 @@
       </c>
       <c r="S349" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34690,7 +34690,7 @@
       </c>
       <c r="S350" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="S351" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="S352" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="S353" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="S354" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="S355" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35272,7 +35272,7 @@
       </c>
       <c r="S356" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="S357" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35466,7 @@
       </c>
       <c r="S358" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35563,7 +35563,7 @@
       </c>
       <c r="S359" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="S360" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35757,7 +35757,7 @@
       </c>
       <c r="S361" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35854,7 +35854,7 @@
       </c>
       <c r="S362" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="S363" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36048,7 +36048,7 @@
       </c>
       <c r="S364" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36145,7 +36145,7 @@
       </c>
       <c r="S365" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="S366" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36339,7 +36339,7 @@
       </c>
       <c r="S367" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="S368" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="S369" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36630,7 +36630,7 @@
       </c>
       <c r="S370" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36727,7 +36727,7 @@
       </c>
       <c r="S371" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36824,7 +36824,7 @@
       </c>
       <c r="S372" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="S373" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37018,7 +37018,7 @@
       </c>
       <c r="S374" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="S375" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="S376" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37309,7 @@
       </c>
       <c r="S377" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S378" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="S379" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="S380" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="S381" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37794,7 +37794,7 @@
       </c>
       <c r="S382" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="S383" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -37988,7 +37988,7 @@
       </c>
       <c r="S384" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38085,7 +38085,7 @@
       </c>
       <c r="S385" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38182,7 +38182,7 @@
       </c>
       <c r="S386" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="S387" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="S388" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38473,7 +38473,7 @@
       </c>
       <c r="S389" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38570,7 +38570,7 @@
       </c>
       <c r="S390" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
       </c>
       <c r="S391" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="S392" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="S393" s="11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -38958,7 +38958,7 @@
       </c>
       <c r="S394" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39055,7 +39055,7 @@
       </c>
       <c r="S395" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39152,7 +39152,7 @@
       </c>
       <c r="S396" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
       </c>
       <c r="S397" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39346,7 +39346,7 @@
       </c>
       <c r="S398" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39443,7 +39443,7 @@
       </c>
       <c r="S399" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="S400" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="S401" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="S402" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="S403" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="S404" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40025,7 +40025,7 @@
       </c>
       <c r="S405" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="S406" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40219,7 @@
       </c>
       <c r="S407" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="S408" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40413,7 +40413,7 @@
       </c>
       <c r="S409" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40510,7 +40510,7 @@
       </c>
       <c r="S410" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="S411" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40704,7 +40704,7 @@
       </c>
       <c r="S412" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S413" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="S414" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -40995,7 +40995,7 @@
       </c>
       <c r="S415" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="S416" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="S417" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41286,7 +41286,7 @@
       </c>
       <c r="S418" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41383,7 @@
       </c>
       <c r="S419" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="S420" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41577,7 +41577,7 @@
       </c>
       <c r="S421" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41674,7 +41674,7 @@
       </c>
       <c r="S422" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41771,7 +41771,7 @@
       </c>
       <c r="S423" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41868,7 +41868,7 @@
       </c>
       <c r="S424" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S425" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="S426" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="S427" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="S428" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42353,7 +42353,7 @@
       </c>
       <c r="S429" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42450,7 +42450,7 @@
       </c>
       <c r="S430" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42547,7 +42547,7 @@
       </c>
       <c r="S431" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42644,7 +42644,7 @@
       </c>
       <c r="S432" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42741,7 +42741,7 @@
       </c>
       <c r="S433" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42838,7 +42838,7 @@
       </c>
       <c r="S434" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -42935,7 +42935,7 @@
       </c>
       <c r="S435" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43032,7 +43032,7 @@
       </c>
       <c r="S436" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="S437" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="S438" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="S439" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43420,7 +43420,7 @@
       </c>
       <c r="S440" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43517,7 @@
       </c>
       <c r="S441" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="S442" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43711,7 @@
       </c>
       <c r="S443" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43808,7 +43808,7 @@
       </c>
       <c r="S444" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -43905,7 +43905,7 @@
       </c>
       <c r="S445" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44002,7 +44002,7 @@
       </c>
       <c r="S446" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44099,7 @@
       </c>
       <c r="S447" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44196,7 +44196,7 @@
       </c>
       <c r="S448" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44293,7 +44293,7 @@
       </c>
       <c r="S449" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44390,7 +44390,7 @@
       </c>
       <c r="S450" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="S451" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="S452" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44681,7 +44681,7 @@
       </c>
       <c r="S453" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="S454" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44875,7 +44875,7 @@
       </c>
       <c r="S455" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -44972,7 +44972,7 @@
       </c>
       <c r="S456" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
       </c>
       <c r="S457" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45166,7 +45166,7 @@
       </c>
       <c r="S458" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45263,7 +45263,7 @@
       </c>
       <c r="S459" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="S460" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45457,7 +45457,7 @@
       </c>
       <c r="S461" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45554,7 +45554,7 @@
       </c>
       <c r="S462" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="S463" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="S464" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="S465" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -45942,7 +45942,7 @@
       </c>
       <c r="S466" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46039,7 +46039,7 @@
       </c>
       <c r="S467" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46136,7 +46136,7 @@
       </c>
       <c r="S468" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="S469" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46330,7 +46330,7 @@
       </c>
       <c r="S470" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="S471" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46524,7 +46524,7 @@
       </c>
       <c r="S472" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46621,7 +46621,7 @@
       </c>
       <c r="S473" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46718,7 +46718,7 @@
       </c>
       <c r="S474" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46815,7 +46815,7 @@
       </c>
       <c r="S475" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -46912,7 +46912,7 @@
       </c>
       <c r="S476" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47009,7 +47009,7 @@
       </c>
       <c r="S477" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47106,7 +47106,7 @@
       </c>
       <c r="S478" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47203,7 @@
       </c>
       <c r="S479" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S480" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="S481" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="S482" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47591,7 +47591,7 @@
       </c>
       <c r="S483" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47688,7 +47688,7 @@
       </c>
       <c r="S484" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47785,7 +47785,7 @@
       </c>
       <c r="S485" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="S486" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -47979,7 +47979,7 @@
       </c>
       <c r="S487" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="S488" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48173,7 +48173,7 @@
       </c>
       <c r="S489" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48270,7 +48270,7 @@
       </c>
       <c r="S490" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48367,7 +48367,7 @@
       </c>
       <c r="S491" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48464,7 +48464,7 @@
       </c>
       <c r="S492" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="S493" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48658,7 +48658,7 @@
       </c>
       <c r="S494" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="S495" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48852,7 +48852,7 @@
       </c>
       <c r="S496" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -48949,7 +48949,7 @@
       </c>
       <c r="S497" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49046,7 +49046,7 @@
       </c>
       <c r="S498" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49143,7 +49143,7 @@
       </c>
       <c r="S499" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49240,7 +49240,7 @@
       </c>
       <c r="S500" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49337,7 +49337,7 @@
       </c>
       <c r="S501" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49434,7 +49434,7 @@
       </c>
       <c r="S502" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49531,7 +49531,7 @@
       </c>
       <c r="S503" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49628,7 +49628,7 @@
       </c>
       <c r="S504" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49725,7 +49725,7 @@
       </c>
       <c r="S505" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49822,7 +49822,7 @@
       </c>
       <c r="S506" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -49919,7 +49919,7 @@
       </c>
       <c r="S507" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="S508" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50113,7 +50113,7 @@
       </c>
       <c r="S509" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50210,7 +50210,7 @@
       </c>
       <c r="S510" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50307,7 +50307,7 @@
       </c>
       <c r="S511" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50404,7 +50404,7 @@
       </c>
       <c r="S512" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50501,7 +50501,7 @@
       </c>
       <c r="S513" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50598,7 +50598,7 @@
       </c>
       <c r="S514" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50695,7 +50695,7 @@
       </c>
       <c r="S515" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S516" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50889,7 +50889,7 @@
       </c>
       <c r="S517" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -50986,7 +50986,7 @@
       </c>
       <c r="S518" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51083,7 +51083,7 @@
       </c>
       <c r="S519" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51180,7 +51180,7 @@
       </c>
       <c r="S520" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51277,7 +51277,7 @@
       </c>
       <c r="S521" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="S522" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="S523" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51568,7 +51568,7 @@
       </c>
       <c r="S524" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51665,7 +51665,7 @@
       </c>
       <c r="S525" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51762,7 +51762,7 @@
       </c>
       <c r="S526" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51859,7 +51859,7 @@
       </c>
       <c r="S527" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -51956,7 +51956,7 @@
       </c>
       <c r="S528" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="S529" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52150,7 +52150,7 @@
       </c>
       <c r="S530" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="S531" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="S532" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="S533" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52538,7 +52538,7 @@
       </c>
       <c r="S534" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="S535" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52732,7 +52732,7 @@
       </c>
       <c r="S536" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52829,7 +52829,7 @@
       </c>
       <c r="S537" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -52926,7 +52926,7 @@
       </c>
       <c r="S538" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53023,7 +53023,7 @@
       </c>
       <c r="S539" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53120,7 @@
       </c>
       <c r="S540" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53217,7 +53217,7 @@
       </c>
       <c r="S541" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53314,7 +53314,7 @@
       </c>
       <c r="S542" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53411,7 +53411,7 @@
       </c>
       <c r="S543" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53508,7 +53508,7 @@
       </c>
       <c r="S544" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53605,7 +53605,7 @@
       </c>
       <c r="S545" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53702,7 +53702,7 @@
       </c>
       <c r="S546" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53799,7 +53799,7 @@
       </c>
       <c r="S547" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53896,7 +53896,7 @@
       </c>
       <c r="S548" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -53993,7 +53993,7 @@
       </c>
       <c r="S549" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54090,7 @@
       </c>
       <c r="S550" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54187,7 +54187,7 @@
       </c>
       <c r="S551" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54284,7 +54284,7 @@
       </c>
       <c r="S552" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54381,7 +54381,7 @@
       </c>
       <c r="S553" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54478,7 +54478,7 @@
       </c>
       <c r="S554" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="S555" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="S556" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54769,7 +54769,7 @@
       </c>
       <c r="S557" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="S558" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -54963,7 +54963,7 @@
       </c>
       <c r="S559" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55060,7 +55060,7 @@
       </c>
       <c r="S560" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55157,7 +55157,7 @@
       </c>
       <c r="S561" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55254,7 @@
       </c>
       <c r="S562" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55351,7 +55351,7 @@
       </c>
       <c r="S563" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55448,7 +55448,7 @@
       </c>
       <c r="S564" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55545,7 +55545,7 @@
       </c>
       <c r="S565" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55642,7 +55642,7 @@
       </c>
       <c r="S566" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55739,7 +55739,7 @@
       </c>
       <c r="S567" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55836,7 +55836,7 @@
       </c>
       <c r="S568" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -55933,7 +55933,7 @@
       </c>
       <c r="S569" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56030,7 +56030,7 @@
       </c>
       <c r="S570" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56127,7 +56127,7 @@
       </c>
       <c r="S571" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56224,7 +56224,7 @@
       </c>
       <c r="S572" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56321,7 +56321,7 @@
       </c>
       <c r="S573" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56418,7 +56418,7 @@
       </c>
       <c r="S574" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56515,7 +56515,7 @@
       </c>
       <c r="S575" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56612,7 +56612,7 @@
       </c>
       <c r="S576" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56709,7 +56709,7 @@
       </c>
       <c r="S577" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S578" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -56903,7 +56903,7 @@
       </c>
       <c r="S579" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57000,7 +57000,7 @@
       </c>
       <c r="S580" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="S581" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57194,7 +57194,7 @@
       </c>
       <c r="S582" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57291,7 +57291,7 @@
       </c>
       <c r="S583" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="S584" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="S585" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57582,7 +57582,7 @@
       </c>
       <c r="S586" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57679,7 +57679,7 @@
       </c>
       <c r="S587" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57776,7 +57776,7 @@
       </c>
       <c r="S588" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57873,7 +57873,7 @@
       </c>
       <c r="S589" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -57970,7 +57970,7 @@
       </c>
       <c r="S590" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58067,7 +58067,7 @@
       </c>
       <c r="S591" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58164,7 +58164,7 @@
       </c>
       <c r="S592" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58261,7 +58261,7 @@
       </c>
       <c r="S593" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58358,7 +58358,7 @@
       </c>
       <c r="S594" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58455,7 +58455,7 @@
       </c>
       <c r="S595" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58552,7 +58552,7 @@
       </c>
       <c r="S596" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58649,7 +58649,7 @@
       </c>
       <c r="S597" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58746,7 +58746,7 @@
       </c>
       <c r="S598" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58843,7 +58843,7 @@
       </c>
       <c r="S599" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -58940,7 +58940,7 @@
       </c>
       <c r="S600" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="S601" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59134,7 +59134,7 @@
       </c>
       <c r="S602" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59231,7 +59231,7 @@
       </c>
       <c r="S603" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="S604" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59425,7 +59425,7 @@
       </c>
       <c r="S605" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="S606" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S607" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59716,7 +59716,7 @@
       </c>
       <c r="S608" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59813,7 +59813,7 @@
       </c>
       <c r="S609" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -59910,7 +59910,7 @@
       </c>
       <c r="S610" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60007,7 +60007,7 @@
       </c>
       <c r="S611" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60104,7 +60104,7 @@
       </c>
       <c r="S612" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60201,7 +60201,7 @@
       </c>
       <c r="S613" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S614" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60395,7 +60395,7 @@
       </c>
       <c r="S615" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60492,7 +60492,7 @@
       </c>
       <c r="S616" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60589,7 +60589,7 @@
       </c>
       <c r="S617" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60686,7 +60686,7 @@
       </c>
       <c r="S618" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60783,7 +60783,7 @@
       </c>
       <c r="S619" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60880,7 +60880,7 @@
       </c>
       <c r="S620" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -60977,7 +60977,7 @@
       </c>
       <c r="S621" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61074,7 +61074,7 @@
       </c>
       <c r="S622" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61171,7 +61171,7 @@
       </c>
       <c r="S623" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61268,7 +61268,7 @@
       </c>
       <c r="S624" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61365,7 +61365,7 @@
       </c>
       <c r="S625" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61462,7 +61462,7 @@
       </c>
       <c r="S626" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61559,7 +61559,7 @@
       </c>
       <c r="S627" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="S628" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61753,7 +61753,7 @@
       </c>
       <c r="S629" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61850,7 +61850,7 @@
       </c>
       <c r="S630" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -61947,7 +61947,7 @@
       </c>
       <c r="S631" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62044,7 +62044,7 @@
       </c>
       <c r="S632" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62141,7 +62141,7 @@
       </c>
       <c r="S633" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62238,7 +62238,7 @@
       </c>
       <c r="S634" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62335,7 +62335,7 @@
       </c>
       <c r="S635" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62432,7 +62432,7 @@
       </c>
       <c r="S636" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62529,7 +62529,7 @@
       </c>
       <c r="S637" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62626,7 +62626,7 @@
       </c>
       <c r="S638" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62723,7 +62723,7 @@
       </c>
       <c r="S639" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62820,7 +62820,7 @@
       </c>
       <c r="S640" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -62917,7 +62917,7 @@
       </c>
       <c r="S641" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63014,7 +63014,7 @@
       </c>
       <c r="S642" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63111,7 +63111,7 @@
       </c>
       <c r="S643" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63208,7 +63208,7 @@
       </c>
       <c r="S644" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63305,7 +63305,7 @@
       </c>
       <c r="S645" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63402,7 +63402,7 @@
       </c>
       <c r="S646" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63499,7 +63499,7 @@
       </c>
       <c r="S647" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="S648" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63693,7 +63693,7 @@
       </c>
       <c r="S649" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63790,7 @@
       </c>
       <c r="S650" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63887,7 +63887,7 @@
       </c>
       <c r="S651" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -63984,7 +63984,7 @@
       </c>
       <c r="S652" s="15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>

--- a/data/kslang-slang-database.xlsx
+++ b/data/kslang-slang-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slang DB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Slang DB'!$A$1:$S$652</definedName>
@@ -934,7 +934,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="S130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="S131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="S132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="S133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="S134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="S135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="S137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="S138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="S139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="S140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="S141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="S142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="S143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="S144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="S145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="S146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="S147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="S149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="S150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="S151" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S152" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S153" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="S154" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="S155" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="S156" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="S157" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S158" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="S159" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S160" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="S161" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="S162" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="S163" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="S164" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="S165" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="S166" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="S167" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="S168" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="S169" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="S170" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="S171" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="S172" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="S173" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="S174" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="S175" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="S176" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="S177" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="S178" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="S179" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="S180" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="S181" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="S182" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="S183" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="S184" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="S185" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="S186" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="S187" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="S188" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="S189" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="S190" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="S191" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S192" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="S193" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="S194" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="S195" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="S196" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="S197" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="S198" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="S199" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="S200" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="S201" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="S202" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S203" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="S205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="S206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="S209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="S210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="S211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="S212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="S213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="S214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="S215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="S216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="S217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="S218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="S219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="S220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="S221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="S222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="S223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="S224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="S225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="S226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="S227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -22953,7 +22953,7 @@
       </c>
       <c r="S229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="S230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="S231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="S232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="S233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23438,7 +23438,7 @@
       </c>
       <c r="S234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="S236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="S237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="S238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -23923,7 +23923,7 @@
       </c>
       <c r="S239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="S241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="S242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="S244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="S245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="S246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24699,7 +24699,7 @@
       </c>
       <c r="S247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="S248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="S249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="S250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="S251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25184,7 @@
       </c>
       <c r="S252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="S253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="S254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="S255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="S256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="S258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="S260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="S261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="S262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="S263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="S264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="S265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
       </c>
       <c r="S266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="S267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26736,7 @@
       </c>
       <c r="S268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26833,7 +26833,7 @@
       </c>
       <c r="S269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -26930,7 +26930,7 @@
       </c>
       <c r="S270" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="S271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="S272" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="S273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="S274" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="S275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
       </c>
       <c r="S276" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="S277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="S278" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="S279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27900,7 @@
       </c>
       <c r="S280" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="S281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="S282" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="S283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S284" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="S285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="S286" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="S287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="S288" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,7 @@
       </c>
       <c r="S289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S290" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="S291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="S292" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="S293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="S294" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="S295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29452,7 @@
       </c>
       <c r="S296" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="S297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="S298" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="S299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="S300" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="S301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="S302" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="S303" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30228,7 +30228,7 @@
       </c>
       <c r="S304" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30325,7 @@
       </c>
       <c r="S305" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="S306" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S307" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="S308" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="S309" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="S310" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="S311" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="S312" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31101,7 +31101,7 @@
       </c>
       <c r="S313" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31198,7 @@
       </c>
       <c r="S314" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31295,7 @@
       </c>
       <c r="S315" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="S316" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="S317" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31586,7 @@
       </c>
       <c r="S318" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="S319" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="S320" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="S321" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="S322" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="S323" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32168,7 @@
       </c>
       <c r="S324" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="S325" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="S326" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
       </c>
       <c r="S327" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="S328" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="S329" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="S330" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="S331" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="S332" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="S333" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S334" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="S335" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="S336" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33429,7 +33429,7 @@
       </c>
       <c r="S337" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="S338" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33623,7 +33623,7 @@
       </c>
       <c r="S339" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="S340" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="S341" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="S342" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S343" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34108,7 @@
       </c>
       <c r="S344" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="S345" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="S346" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34399,7 +34399,7 @@
       </c>
       <c r="S347" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="S348" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34593,7 +34593,7 @@
       </c>
       <c r="S349" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34690,7 +34690,7 @@
       </c>
       <c r="S350" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="S351" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="S352" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="S353" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="S354" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="S355" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35272,7 +35272,7 @@
       </c>
       <c r="S356" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="S357" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35466,7 @@
       </c>
       <c r="S358" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35563,7 +35563,7 @@
       </c>
       <c r="S359" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35660,7 +35660,7 @@
       </c>
       <c r="S360" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35757,7 +35757,7 @@
       </c>
       <c r="S361" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35854,7 +35854,7 @@
       </c>
       <c r="S362" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="S363" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36048,7 +36048,7 @@
       </c>
       <c r="S364" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36145,7 +36145,7 @@
       </c>
       <c r="S365" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="S366" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36339,7 +36339,7 @@
       </c>
       <c r="S367" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="S368" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="S369" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36630,7 +36630,7 @@
       </c>
       <c r="S370" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36727,7 +36727,7 @@
       </c>
       <c r="S371" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36824,7 +36824,7 @@
       </c>
       <c r="S372" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="S373" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37018,7 +37018,7 @@
       </c>
       <c r="S374" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="S375" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="S376" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37309,7 @@
       </c>
       <c r="S377" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S378" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="S379" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="S380" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="S381" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37794,7 +37794,7 @@
       </c>
       <c r="S382" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="S383" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -37988,7 +37988,7 @@
       </c>
       <c r="S384" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38085,7 +38085,7 @@
       </c>
       <c r="S385" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38182,7 +38182,7 @@
       </c>
       <c r="S386" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="S387" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="S388" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38473,7 +38473,7 @@
       </c>
       <c r="S389" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38570,7 +38570,7 @@
       </c>
       <c r="S390" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38667,7 +38667,7 @@
       </c>
       <c r="S391" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="S392" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="S393" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -38958,7 +38958,7 @@
       </c>
       <c r="S394" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39055,7 +39055,7 @@
       </c>
       <c r="S395" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39152,7 +39152,7 @@
       </c>
       <c r="S396" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
       </c>
       <c r="S397" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39346,7 +39346,7 @@
       </c>
       <c r="S398" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39443,7 +39443,7 @@
       </c>
       <c r="S399" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="S400" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="S401" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="S402" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="S403" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="S404" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40025,7 +40025,7 @@
       </c>
       <c r="S405" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="S406" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40219,7 @@
       </c>
       <c r="S407" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="S408" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40413,7 +40413,7 @@
       </c>
       <c r="S409" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40510,7 +40510,7 @@
       </c>
       <c r="S410" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="S411" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40704,7 +40704,7 @@
       </c>
       <c r="S412" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S413" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="S414" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -40995,7 +40995,7 @@
       </c>
       <c r="S415" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="S416" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="S417" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41286,7 +41286,7 @@
       </c>
       <c r="S418" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41383,7 +41383,7 @@
       </c>
       <c r="S419" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="S420" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41577,7 +41577,7 @@
       </c>
       <c r="S421" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41674,7 +41674,7 @@
       </c>
       <c r="S422" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41771,7 +41771,7 @@
       </c>
       <c r="S423" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41868,7 +41868,7 @@
       </c>
       <c r="S424" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S425" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="S426" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="S427" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="S428" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42353,7 +42353,7 @@
       </c>
       <c r="S429" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42450,7 +42450,7 @@
       </c>
       <c r="S430" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42547,7 +42547,7 @@
       </c>
       <c r="S431" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42644,7 +42644,7 @@
       </c>
       <c r="S432" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42741,7 +42741,7 @@
       </c>
       <c r="S433" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42838,7 +42838,7 @@
       </c>
       <c r="S434" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -42935,7 +42935,7 @@
       </c>
       <c r="S435" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43032,7 +43032,7 @@
       </c>
       <c r="S436" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="S437" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="S438" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="S439" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43420,7 +43420,7 @@
       </c>
       <c r="S440" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43517,7 +43517,7 @@
       </c>
       <c r="S441" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="S442" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43711,7 @@
       </c>
       <c r="S443" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43808,7 +43808,7 @@
       </c>
       <c r="S444" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -43905,7 +43905,7 @@
       </c>
       <c r="S445" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44002,7 +44002,7 @@
       </c>
       <c r="S446" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44099,7 @@
       </c>
       <c r="S447" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44196,7 +44196,7 @@
       </c>
       <c r="S448" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44293,7 +44293,7 @@
       </c>
       <c r="S449" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44390,7 +44390,7 @@
       </c>
       <c r="S450" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="S451" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="S452" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44681,7 +44681,7 @@
       </c>
       <c r="S453" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="S454" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44875,7 +44875,7 @@
       </c>
       <c r="S455" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -44972,7 +44972,7 @@
       </c>
       <c r="S456" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
       </c>
       <c r="S457" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45166,7 +45166,7 @@
       </c>
       <c r="S458" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45263,7 +45263,7 @@
       </c>
       <c r="S459" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="S460" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45457,7 +45457,7 @@
       </c>
       <c r="S461" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45554,7 +45554,7 @@
       </c>
       <c r="S462" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="S463" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="S464" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="S465" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -45942,7 +45942,7 @@
       </c>
       <c r="S466" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46039,7 +46039,7 @@
       </c>
       <c r="S467" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46136,7 +46136,7 @@
       </c>
       <c r="S468" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="S469" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46330,7 +46330,7 @@
       </c>
       <c r="S470" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="S471" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46524,7 +46524,7 @@
       </c>
       <c r="S472" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46621,7 +46621,7 @@
       </c>
       <c r="S473" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46718,7 +46718,7 @@
       </c>
       <c r="S474" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46815,7 +46815,7 @@
       </c>
       <c r="S475" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -46912,7 +46912,7 @@
       </c>
       <c r="S476" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47009,7 +47009,7 @@
       </c>
       <c r="S477" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47106,7 +47106,7 @@
       </c>
       <c r="S478" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47203,7 @@
       </c>
       <c r="S479" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S480" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="S481" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="S482" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47591,7 +47591,7 @@
       </c>
       <c r="S483" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47688,7 +47688,7 @@
       </c>
       <c r="S484" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47785,7 +47785,7 @@
       </c>
       <c r="S485" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="S486" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -47979,7 +47979,7 @@
       </c>
       <c r="S487" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="S488" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48173,7 +48173,7 @@
       </c>
       <c r="S489" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48270,7 +48270,7 @@
       </c>
       <c r="S490" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48367,7 +48367,7 @@
       </c>
       <c r="S491" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48464,7 +48464,7 @@
       </c>
       <c r="S492" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="S493" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48658,7 +48658,7 @@
       </c>
       <c r="S494" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="S495" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48852,7 +48852,7 @@
       </c>
       <c r="S496" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -48949,7 +48949,7 @@
       </c>
       <c r="S497" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49046,7 +49046,7 @@
       </c>
       <c r="S498" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49143,7 +49143,7 @@
       </c>
       <c r="S499" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49240,7 +49240,7 @@
       </c>
       <c r="S500" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49337,7 +49337,7 @@
       </c>
       <c r="S501" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49434,7 +49434,7 @@
       </c>
       <c r="S502" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49531,7 +49531,7 @@
       </c>
       <c r="S503" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49628,7 +49628,7 @@
       </c>
       <c r="S504" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49725,7 +49725,7 @@
       </c>
       <c r="S505" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49822,7 +49822,7 @@
       </c>
       <c r="S506" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -49919,7 +49919,7 @@
       </c>
       <c r="S507" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="S508" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50113,7 +50113,7 @@
       </c>
       <c r="S509" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50210,7 +50210,7 @@
       </c>
       <c r="S510" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50307,7 +50307,7 @@
       </c>
       <c r="S511" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50404,7 +50404,7 @@
       </c>
       <c r="S512" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50501,7 +50501,7 @@
       </c>
       <c r="S513" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50598,7 +50598,7 @@
       </c>
       <c r="S514" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50695,7 +50695,7 @@
       </c>
       <c r="S515" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S516" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50889,7 +50889,7 @@
       </c>
       <c r="S517" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -50986,7 +50986,7 @@
       </c>
       <c r="S518" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51083,7 +51083,7 @@
       </c>
       <c r="S519" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51180,7 +51180,7 @@
       </c>
       <c r="S520" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51277,7 +51277,7 @@
       </c>
       <c r="S521" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="S522" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="S523" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51568,7 +51568,7 @@
       </c>
       <c r="S524" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51665,7 +51665,7 @@
       </c>
       <c r="S525" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51762,7 +51762,7 @@
       </c>
       <c r="S526" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51859,7 +51859,7 @@
       </c>
       <c r="S527" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -51956,7 +51956,7 @@
       </c>
       <c r="S528" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="S529" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52150,7 +52150,7 @@
       </c>
       <c r="S530" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="S531" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="S532" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="S533" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52538,7 +52538,7 @@
       </c>
       <c r="S534" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="S535" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52732,7 +52732,7 @@
       </c>
       <c r="S536" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52829,7 +52829,7 @@
       </c>
       <c r="S537" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -52926,7 +52926,7 @@
       </c>
       <c r="S538" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53023,7 +53023,7 @@
       </c>
       <c r="S539" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53120,7 @@
       </c>
       <c r="S540" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53217,7 +53217,7 @@
       </c>
       <c r="S541" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53314,7 +53314,7 @@
       </c>
       <c r="S542" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53411,7 +53411,7 @@
       </c>
       <c r="S543" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53508,7 +53508,7 @@
       </c>
       <c r="S544" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53605,7 +53605,7 @@
       </c>
       <c r="S545" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53702,7 +53702,7 @@
       </c>
       <c r="S546" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53799,7 +53799,7 @@
       </c>
       <c r="S547" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53896,7 +53896,7 @@
       </c>
       <c r="S548" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -53993,7 +53993,7 @@
       </c>
       <c r="S549" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54090,7 +54090,7 @@
       </c>
       <c r="S550" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54187,7 +54187,7 @@
       </c>
       <c r="S551" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54284,7 +54284,7 @@
       </c>
       <c r="S552" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54381,7 +54381,7 @@
       </c>
       <c r="S553" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54478,7 +54478,7 @@
       </c>
       <c r="S554" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="S555" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="S556" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54769,7 +54769,7 @@
       </c>
       <c r="S557" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="S558" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -54963,7 +54963,7 @@
       </c>
       <c r="S559" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55060,7 +55060,7 @@
       </c>
       <c r="S560" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55157,7 +55157,7 @@
       </c>
       <c r="S561" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55254,7 @@
       </c>
       <c r="S562" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55351,7 +55351,7 @@
       </c>
       <c r="S563" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55448,7 +55448,7 @@
       </c>
       <c r="S564" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55545,7 +55545,7 @@
       </c>
       <c r="S565" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55642,7 +55642,7 @@
       </c>
       <c r="S566" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55739,7 +55739,7 @@
       </c>
       <c r="S567" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55836,7 +55836,7 @@
       </c>
       <c r="S568" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -55933,7 +55933,7 @@
       </c>
       <c r="S569" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56030,7 +56030,7 @@
       </c>
       <c r="S570" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56127,7 +56127,7 @@
       </c>
       <c r="S571" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56224,7 +56224,7 @@
       </c>
       <c r="S572" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56321,7 +56321,7 @@
       </c>
       <c r="S573" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56418,7 +56418,7 @@
       </c>
       <c r="S574" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56515,7 +56515,7 @@
       </c>
       <c r="S575" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56612,7 +56612,7 @@
       </c>
       <c r="S576" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56709,7 +56709,7 @@
       </c>
       <c r="S577" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S578" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -56903,7 +56903,7 @@
       </c>
       <c r="S579" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57000,7 +57000,7 @@
       </c>
       <c r="S580" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="S581" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57194,7 +57194,7 @@
       </c>
       <c r="S582" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57291,7 +57291,7 @@
       </c>
       <c r="S583" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="S584" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="S585" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57582,7 +57582,7 @@
       </c>
       <c r="S586" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57679,7 +57679,7 @@
       </c>
       <c r="S587" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57776,7 +57776,7 @@
       </c>
       <c r="S588" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57873,7 +57873,7 @@
       </c>
       <c r="S589" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -57970,7 +57970,7 @@
       </c>
       <c r="S590" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58067,7 +58067,7 @@
       </c>
       <c r="S591" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58164,7 +58164,7 @@
       </c>
       <c r="S592" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58261,7 +58261,7 @@
       </c>
       <c r="S593" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58358,7 +58358,7 @@
       </c>
       <c r="S594" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58455,7 +58455,7 @@
       </c>
       <c r="S595" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58552,7 +58552,7 @@
       </c>
       <c r="S596" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58649,7 +58649,7 @@
       </c>
       <c r="S597" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58746,7 +58746,7 @@
       </c>
       <c r="S598" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58843,7 +58843,7 @@
       </c>
       <c r="S599" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -58940,7 +58940,7 @@
       </c>
       <c r="S600" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="S601" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59134,7 +59134,7 @@
       </c>
       <c r="S602" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59231,7 +59231,7 @@
       </c>
       <c r="S603" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="S604" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59425,7 +59425,7 @@
       </c>
       <c r="S605" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="S606" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S607" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59716,7 +59716,7 @@
       </c>
       <c r="S608" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59813,7 +59813,7 @@
       </c>
       <c r="S609" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -59910,7 +59910,7 @@
       </c>
       <c r="S610" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60007,7 +60007,7 @@
       </c>
       <c r="S611" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60104,7 +60104,7 @@
       </c>
       <c r="S612" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60201,7 +60201,7 @@
       </c>
       <c r="S613" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S614" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60395,7 +60395,7 @@
       </c>
       <c r="S615" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60492,7 +60492,7 @@
       </c>
       <c r="S616" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60589,7 +60589,7 @@
       </c>
       <c r="S617" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60686,7 +60686,7 @@
       </c>
       <c r="S618" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60783,7 +60783,7 @@
       </c>
       <c r="S619" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60880,7 +60880,7 @@
       </c>
       <c r="S620" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -60977,7 +60977,7 @@
       </c>
       <c r="S621" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61074,7 +61074,7 @@
       </c>
       <c r="S622" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61171,7 +61171,7 @@
       </c>
       <c r="S623" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61268,7 +61268,7 @@
       </c>
       <c r="S624" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61365,7 +61365,7 @@
       </c>
       <c r="S625" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61462,7 +61462,7 @@
       </c>
       <c r="S626" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61559,7 +61559,7 @@
       </c>
       <c r="S627" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="S628" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61753,7 +61753,7 @@
       </c>
       <c r="S629" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61850,7 +61850,7 @@
       </c>
       <c r="S630" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -61947,7 +61947,7 @@
       </c>
       <c r="S631" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62044,7 +62044,7 @@
       </c>
       <c r="S632" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62141,7 +62141,7 @@
       </c>
       <c r="S633" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62238,7 +62238,7 @@
       </c>
       <c r="S634" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62335,7 +62335,7 @@
       </c>
       <c r="S635" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62432,7 +62432,7 @@
       </c>
       <c r="S636" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62529,7 +62529,7 @@
       </c>
       <c r="S637" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62626,7 +62626,7 @@
       </c>
       <c r="S638" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62723,7 +62723,7 @@
       </c>
       <c r="S639" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62820,7 +62820,7 @@
       </c>
       <c r="S640" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -62917,7 +62917,7 @@
       </c>
       <c r="S641" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63014,7 +63014,7 @@
       </c>
       <c r="S642" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63111,7 +63111,7 @@
       </c>
       <c r="S643" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63208,7 +63208,7 @@
       </c>
       <c r="S644" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63305,7 +63305,7 @@
       </c>
       <c r="S645" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63402,7 +63402,7 @@
       </c>
       <c r="S646" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63499,7 +63499,7 @@
       </c>
       <c r="S647" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63596,7 +63596,7 @@
       </c>
       <c r="S648" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63693,7 +63693,7 @@
       </c>
       <c r="S649" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63790,7 @@
       </c>
       <c r="S650" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63887,7 +63887,7 @@
       </c>
       <c r="S651" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -63984,7 +63984,7 @@
       </c>
       <c r="S652" s="15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
